--- a/investment-engine/sector/AI/stock-data/investment_data_06152026.xlsx
+++ b/investment-engine/sector/AI/stock-data/investment_data_06152026.xlsx
@@ -878,6 +878,39 @@
           <t>FIX</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>1877.61</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.28044715968262</v>
+      </c>
+      <c r="F2" t="n">
+        <v>66096378264</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1502.088</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1479.77962</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-21.1881263947252</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29.51507767511408</v>
+      </c>
+      <c r="L2" t="n">
+        <v>97.60928961748633</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.002964610242596696</v>
+      </c>
+      <c r="P2" t="n">
+        <v>45.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -885,12 +918,78 @@
           <t>EME</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>823.05</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45.49209998827075</v>
+      </c>
+      <c r="F3" t="n">
+        <v>36652526800</v>
+      </c>
+      <c r="G3" t="n">
+        <v>658.4400000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1094.06</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32.92752566672742</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16.64056499344094</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30.44886626561778</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.007323233169288618</v>
+      </c>
+      <c r="P3" t="n">
+        <v>45.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>STRL</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>858.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>53.82124832804914</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26358927626</v>
+      </c>
+      <c r="G4" t="n">
+        <v>687.192</v>
+      </c>
+      <c r="H4" t="n">
+        <v>915.2</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.543731591753109</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17.69074505755862</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13.77245508982037</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001548128231125331</v>
+      </c>
+      <c r="P4" t="n">
+        <v>37.9</v>
       </c>
     </row>
   </sheetData>
@@ -995,6 +1094,39 @@
           <t>CRWD</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>682.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>55.74085015608213</v>
+      </c>
+      <c r="F2" t="n">
+        <v>173816859096</v>
+      </c>
+      <c r="G2" t="n">
+        <v>546.24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>542.8499999999999</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-20.49648506151143</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21.71124517657724</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-725.9212198221093</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.025371808137232</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1002,6 +1134,30 @@
           <t>PANW</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="C3" t="n">
+        <v>63.26010553616113</v>
+      </c>
+      <c r="F3" t="n">
+        <v>190564196417</v>
+      </c>
+      <c r="G3" t="n">
+        <v>223.696</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14.87387106820305</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-57.67326732673267</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01012991966117194</v>
+      </c>
+      <c r="P3" t="n">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1009,6 +1165,39 @@
           <t>ZS</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="C4" t="n">
+        <v>41.37140579910967</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20944617678</v>
+      </c>
+      <c r="G4" t="n">
+        <v>103.616</v>
+      </c>
+      <c r="H4" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>190.4570722668313</v>
+      </c>
+      <c r="K4" t="n">
+        <v>23.31168744300021</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02828636020519486</v>
+      </c>
+      <c r="P4" t="n">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1016,12 +1205,75 @@
           <t>OKTA</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>116.29</v>
+      </c>
+      <c r="C5" t="n">
+        <v>57.82203130476967</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19318094800</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93.03200000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>148.7746151861725</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11.83908045977012</v>
+      </c>
+      <c r="L5" t="n">
+        <v>688.2352941176471</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02256951342841531</v>
+      </c>
+      <c r="P5" t="n">
+        <v>55.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>RBRK</t>
         </is>
+      </c>
+      <c r="B6" t="n">
+        <v>68.19</v>
+      </c>
+      <c r="C6" t="n">
+        <v>44.15347059351847</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14035312104</v>
+      </c>
+      <c r="G6" t="n">
+        <v>54.552</v>
+      </c>
+      <c r="H6" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>58.0876961431295</v>
+      </c>
+      <c r="K6" t="n">
+        <v>48.46313324550163</v>
+      </c>
+      <c r="L6" t="n">
+        <v>76.20320855614973</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.05347405133841689</v>
+      </c>
+      <c r="P6" t="n">
+        <v>59.4</v>
       </c>
     </row>
   </sheetData>
@@ -1126,6 +1378,39 @@
           <t>AMAT</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>567.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>76.60046560954015</v>
+      </c>
+      <c r="F2" t="n">
+        <v>450373486668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>453.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>465.99344</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-17.85042926399295</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.386223138062997</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3456221198156813</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004240924602668689</v>
+      </c>
+      <c r="P2" t="n">
+        <v>23.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1133,6 +1418,39 @@
           <t>LRCX</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>70.27105315932964</v>
+      </c>
+      <c r="F3" t="n">
+        <v>458721581700</v>
+      </c>
+      <c r="G3" t="n">
+        <v>293.448</v>
+      </c>
+      <c r="H3" t="n">
+        <v>278.96</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-23.9497287424007</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.68408976459919</v>
+      </c>
+      <c r="L3" t="n">
+        <v>43.29896907216494</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003562300238728881</v>
+      </c>
+      <c r="P3" t="n">
+        <v>33.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1140,6 +1458,39 @@
           <t>KLAC</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>254.54</v>
+      </c>
+      <c r="C4" t="n">
+        <v>78.81342629851409</v>
+      </c>
+      <c r="F4" t="n">
+        <v>332500511200</v>
+      </c>
+      <c r="G4" t="n">
+        <v>203.632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>167.816</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-34.07087294727744</v>
+      </c>
+      <c r="K4" t="n">
+        <v>23.88764775285416</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49.58353748162666</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.01205824913029487</v>
+      </c>
+      <c r="P4" t="n">
+        <v>30.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1147,6 +1498,39 @@
           <t>ONTO</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>323.88</v>
+      </c>
+      <c r="C5" t="n">
+        <v>71.37396348704004</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16110946480</v>
+      </c>
+      <c r="G5" t="n">
+        <v>259.104</v>
+      </c>
+      <c r="H5" t="n">
+        <v>359.04</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.85587254538719</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.817240796053158</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-32.02933985330073</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02039880154825019</v>
+      </c>
+      <c r="P5" t="n">
+        <v>25.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1154,6 +1538,39 @@
           <t>ACLS</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>180.12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>66.80815558640113</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5535789528</v>
+      </c>
+      <c r="G6" t="n">
+        <v>144.096</v>
+      </c>
+      <c r="H6" t="n">
+        <v>110.22</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-38.80746169220519</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-17.56785035343587</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-38.24959481361427</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01862823712469728</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1161,6 +1578,39 @@
           <t>PLAB</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="C7" t="n">
+        <v>36.07450545502838</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1873866386</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25.424</v>
+      </c>
+      <c r="H7" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40.18250471994964</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.036112975894692</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.018867924528299</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2595153014287541</v>
+      </c>
+      <c r="P7" t="n">
+        <v>44.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1168,6 +1618,39 @@
           <t>TSM</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>423.93</v>
+      </c>
+      <c r="C8" t="n">
+        <v>52.54069693536469</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2198704466400</v>
+      </c>
+      <c r="G8" t="n">
+        <v>339.144</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2895.992</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>583.1297619890075</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32.96825869948879</v>
+      </c>
+      <c r="L8" t="n">
+        <v>44.30242634315425</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7746715058931123</v>
+      </c>
+      <c r="P8" t="n">
+        <v>59.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1175,6 +1658,39 @@
           <t>GFS</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="C9" t="n">
+        <v>56.64049311373668</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44630129887</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65.104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-15.65495207667731</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6074074074074074</v>
+      </c>
+      <c r="L9" t="n">
+        <v>431.2500000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.003831492322181419</v>
+      </c>
+      <c r="P9" t="n">
+        <v>39.8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1182,12 +1698,78 @@
           <t>INTC</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>124.57</v>
+      </c>
+      <c r="C10" t="n">
+        <v>63.54960300150914</v>
+      </c>
+      <c r="F10" t="n">
+        <v>626088820000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>99.65600000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>99.495</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-20.12924460142891</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.4670345191239336</v>
+      </c>
+      <c r="L10" t="n">
+        <v>98.6552511415525</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.05162206857487089</v>
+      </c>
+      <c r="P10" t="n">
+        <v>36.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>TSEM</t>
         </is>
+      </c>
+      <c r="B11" t="n">
+        <v>262.92</v>
+      </c>
+      <c r="C11" t="n">
+        <v>55.28695757942516</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29383050530</v>
+      </c>
+      <c r="G11" t="n">
+        <v>210.336</v>
+      </c>
+      <c r="H11" t="n">
+        <v>186.45</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-29.08489274303971</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.050902360662953</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.347593582887693</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.002513387775193674</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30.6</v>
       </c>
     </row>
   </sheetData>
@@ -1292,6 +1874,39 @@
           <t>SMCI</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36.95100970898718</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18319192280</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>63.657</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>108.9855548260013</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46.58532304249225</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02134750233649494</v>
+      </c>
+      <c r="P2" t="n">
+        <v>58.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1299,12 +1914,75 @@
           <t>DELL</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>395.57</v>
+      </c>
+      <c r="C3" t="n">
+        <v>62.3936768396651</v>
+      </c>
+      <c r="F3" t="n">
+        <v>262757745523</v>
+      </c>
+      <c r="G3" t="n">
+        <v>316.456</v>
+      </c>
+      <c r="H3" t="n">
+        <v>378.54</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-4.305179867027321</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18.80460828528676</v>
+      </c>
+      <c r="L3" t="n">
+        <v>37.63440860215056</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.07602059440813526</v>
+      </c>
+      <c r="P3" t="n">
+        <v>36.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>HPE</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60.95609391375104</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63786883607</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.536</v>
+      </c>
+      <c r="H4" t="n">
+        <v>91.611</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>90.18268631928586</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14.0614606891047</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-102.2871794871795</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.2869555457948617</v>
+      </c>
+      <c r="P4" t="n">
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>
@@ -1409,6 +2087,39 @@
           <t>NOW</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.67851682436532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>105348112200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>81.72000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>592.7610000000001</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>480.2848751835537</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20.88492352512746</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22.46376811594203</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.004964493326725223</v>
+      </c>
+      <c r="P2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1416,6 +2127,39 @@
           <t>DDOG</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53.049769565106</v>
+      </c>
+      <c r="F3" t="n">
+        <v>81835245382</v>
+      </c>
+      <c r="G3" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>304.85</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32.60113092648979</v>
+      </c>
+      <c r="K3" t="n">
+        <v>27.67536858183308</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-43.63636363636364</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.01385572921187089</v>
+      </c>
+      <c r="P3" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1423,6 +2167,39 @@
           <t>DT</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="C4" t="n">
+        <v>48.649339629541</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11877647000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>375.3374233128834</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.82069815262765</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-66.66666666666666</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07854215569800989</v>
+      </c>
+      <c r="P4" t="n">
+        <v>44.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1430,12 +2207,78 @@
           <t>AI</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>59.57710871757248</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1545524407</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>138.5321100917431</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-35.67301365356144</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-49.55357142857142</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04283141676713748</v>
+      </c>
+      <c r="P5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>MDB</t>
         </is>
+      </c>
+      <c r="B6" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50.93285270383423</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27572064576</v>
+      </c>
+      <c r="G6" t="n">
+        <v>274.24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>830.05</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>142.1382730455076</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22.794268264785</v>
+      </c>
+      <c r="L6" t="n">
+        <v>49.13294797687861</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.038106722008571</v>
+      </c>
+      <c r="P6" t="n">
+        <v>54.8</v>
       </c>
     </row>
   </sheetData>
@@ -1540,6 +2383,39 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>260.22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>46.56538649954902</v>
+      </c>
+      <c r="F2" t="n">
+        <v>74017983331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>208.176</v>
+      </c>
+      <c r="H2" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36.21166705095686</v>
+      </c>
+      <c r="K2" t="n">
+        <v>37.326441660515</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-184.6153846153846</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.007266396297165012</v>
+      </c>
+      <c r="P2" t="n">
+        <v>41.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1547,12 +2423,78 @@
           <t>FLNC</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53.51949595703279</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4375127109</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18.968</v>
+      </c>
+      <c r="H3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>60.69169126950654</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-16.14682189996005</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-305.5555555555556</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.06856120805792114</v>
+      </c>
+      <c r="P3" t="n">
+        <v>31.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>HYLN</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>63.55542925682136</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1319621576</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.920000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2.702702702702717</v>
+      </c>
+      <c r="K4" t="n">
+        <v>130.284956925116</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-10.00000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01406918493730357</v>
+      </c>
+      <c r="P4" t="n">
+        <v>48.4</v>
       </c>
     </row>
   </sheetData>
@@ -1657,6 +2599,39 @@
           <t>MSFT</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32.11976795001584</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2902584738200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>312.592</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1000.35</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>156.0142294108614</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14.93215623240672</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15.51433389544688</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.02823070035530307</v>
+      </c>
+      <c r="P2" t="n">
+        <v>55.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1664,6 +2639,39 @@
           <t>AMZN</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="C3" t="n">
+        <v>30.06701102661019</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2566106205000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>190.84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>578.3570999999999</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>142.4469084049465</v>
+      </c>
+      <c r="K3" t="n">
+        <v>12.37775468329469</v>
+      </c>
+      <c r="L3" t="n">
+        <v>28.79858657243816</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.02578887805619877</v>
+      </c>
+      <c r="P3" t="n">
+        <v>56.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1671,6 +2679,39 @@
           <t>ORCL</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>184.13</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36.78897043336706</v>
+      </c>
+      <c r="F4" t="n">
+        <v>529566349980</v>
+      </c>
+      <c r="G4" t="n">
+        <v>147.304</v>
+      </c>
+      <c r="H4" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>290.2134361592353</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17.35047648913744</v>
+      </c>
+      <c r="L4" t="n">
+        <v>33.18385650224216</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.235853354361955</v>
+      </c>
+      <c r="P4" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1678,6 +2719,39 @@
           <t>CRWV</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>44.03504637470777</v>
+      </c>
+      <c r="F5" t="n">
+        <v>54857101307</v>
+      </c>
+      <c r="G5" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>424.2654</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>321.9447041272999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>167.8777462559243</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-18.02575107296137</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.4716982739424861</v>
+      </c>
+      <c r="P5" t="n">
+        <v>63.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1685,12 +2759,78 @@
           <t>NBIS</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>232.36</v>
+      </c>
+      <c r="C6" t="n">
+        <v>55.66606717328051</v>
+      </c>
+      <c r="F6" t="n">
+        <v>55766400000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>185.888</v>
+      </c>
+      <c r="H6" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.79204682389396</v>
+      </c>
+      <c r="K6" t="n">
+        <v>350.8936161702127</v>
+      </c>
+      <c r="L6" t="n">
+        <v>104.8245614035088</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.02322186836518047</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.59999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
+      </c>
+      <c r="B7" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="C7" t="n">
+        <v>38.23443550576596</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4350282946986</v>
+      </c>
+      <c r="G7" t="n">
+        <v>287.744</v>
+      </c>
+      <c r="H7" t="n">
+        <v>724.0287</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>101.2980149021352</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15.12636492980361</v>
+      </c>
+      <c r="L7" t="n">
+        <v>34.19434194341942</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.006570377225647614</v>
+      </c>
+      <c r="P7" t="n">
+        <v>55.3</v>
       </c>
     </row>
   </sheetData>
@@ -1795,6 +2935,39 @@
           <t>JCI</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="C2" t="n">
+        <v>55.29855678083622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88442357811</v>
+      </c>
+      <c r="G2" t="n">
+        <v>115.968</v>
+      </c>
+      <c r="H2" t="n">
+        <v>192.86674</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.04824779249446</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.805855698849773</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.347826086956535</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.1222378085295164</v>
+      </c>
+      <c r="P2" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1802,12 +2975,78 @@
           <t>CARR</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="C3" t="n">
+        <v>61.65974138881817</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58065877372</v>
+      </c>
+      <c r="G3" t="n">
+        <v>55.928</v>
+      </c>
+      <c r="H3" t="n">
+        <v>98.33999999999999</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.66657130596481</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-3.28648937116428</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-72.11538461538461</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.1914032905900651</v>
+      </c>
+      <c r="P3" t="n">
+        <v>27.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>HON</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49.95997216728615</v>
+      </c>
+      <c r="F4" t="n">
+        <v>139600118647</v>
+      </c>
+      <c r="G4" t="n">
+        <v>176.248</v>
+      </c>
+      <c r="H4" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.08991875085106</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.849180516749719</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-15.52511415525113</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.1582591778153534</v>
+      </c>
+      <c r="P4" t="n">
+        <v>38.3</v>
       </c>
     </row>
   </sheetData>
@@ -1912,6 +3151,39 @@
           <t>XYL</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>110.08</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.47920548332099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26165299709</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88.06400000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>194.504</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>76.6933139534884</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.524410184536324</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.084468664850142</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.02231963732481624</v>
+      </c>
+      <c r="P2" t="n">
+        <v>44.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1919,12 +3191,78 @@
           <t>BMI</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>131.73</v>
+      </c>
+      <c r="C3" t="n">
+        <v>63.01595511661963</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3844615136</v>
+      </c>
+      <c r="G3" t="n">
+        <v>105.384</v>
+      </c>
+      <c r="H3" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39.86942989448114</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.9012313715432</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13.1455399061033</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0587876788715842</v>
+      </c>
+      <c r="P3" t="n">
+        <v>37.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>MWA</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="C4" t="n">
+        <v>53.1733343530544</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4040081220</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20.656</v>
+      </c>
+      <c r="H4" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>59.75987606506584</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.747242716969652</v>
+      </c>
+      <c r="L4" t="n">
+        <v>66.21621621621621</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.004975147504584079</v>
+      </c>
+      <c r="P4" t="n">
+        <v>47.9</v>
       </c>
     </row>
   </sheetData>
@@ -2029,12 +3367,78 @@
           <t>AJG</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>218.69</v>
+      </c>
+      <c r="C2" t="n">
+        <v>63.84261783701408</v>
+      </c>
+      <c r="F2" t="n">
+        <v>56190645980</v>
+      </c>
+      <c r="G2" t="n">
+        <v>174.952</v>
+      </c>
+      <c r="H2" t="n">
+        <v>417.134</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>90.74214641730302</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20.65703727422998</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-12.06636500754148</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.224307796790344</v>
+      </c>
+      <c r="P2" t="n">
+        <v>41.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>RYAN</t>
         </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="C3" t="n">
+        <v>65.72027562083166</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4612322979</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28.512</v>
+      </c>
+      <c r="H3" t="n">
+        <v>66.185</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>85.70426487093155</v>
+      </c>
+      <c r="K3" t="n">
+        <v>21.28289826728836</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-35.8974358974359</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.7311723431673409</v>
+      </c>
+      <c r="P3" t="n">
+        <v>35.5</v>
       </c>
     </row>
   </sheetData>
@@ -2141,121 +3545,448 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CEG</t>
-        </is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>250.81</v>
+      </c>
+      <c r="D2" t="n">
+        <v>64.44619442285625</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46261889451</v>
+      </c>
+      <c r="H2" t="n">
+        <v>200.648</v>
+      </c>
+      <c r="I2" t="n">
+        <v>500</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>99.35409273952394</v>
+      </c>
+      <c r="L2" t="n">
+        <v>205.6759200961594</v>
+      </c>
+      <c r="M2" t="n">
+        <v>754.8387096774193</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.02473601950936451</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>71.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VST</t>
-        </is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>205.19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>42.74811543778459</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4969906990000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>164.152</v>
+      </c>
+      <c r="I3" t="n">
+        <v>900</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>338.6178663677567</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65.4735357900948</v>
+      </c>
+      <c r="M3" t="n">
+        <v>65.99326599326596</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.000162377284247728</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TLN</t>
-        </is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>232.36</v>
+      </c>
+      <c r="D4" t="n">
+        <v>55.66606717328051</v>
+      </c>
+      <c r="G4" t="n">
+        <v>55766400000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>185.888</v>
+      </c>
+      <c r="I4" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>36.79204682389396</v>
+      </c>
+      <c r="L4" t="n">
+        <v>350.8936161702127</v>
+      </c>
+      <c r="M4" t="n">
+        <v>104.8245614035088</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.02322186836518047</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKLO</t>
-        </is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="D5" t="n">
+        <v>38.4627508262627</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1817728590600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>305.656</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>312.2281257361217</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23.87443285376353</v>
+      </c>
+      <c r="M5" t="n">
+        <v>286.6141732283465</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.02693361388117894</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>63.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMR</t>
-        </is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>44.03504637470777</v>
+      </c>
+      <c r="G6" t="n">
+        <v>54857101307</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>424.2654</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>321.9447041272999</v>
+      </c>
+      <c r="L6" t="n">
+        <v>167.8777462559243</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-18.02575107296137</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.4716982739424861</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>63.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NNE</t>
-        </is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>981.61</v>
+      </c>
+      <c r="D7" t="n">
+        <v>59.02601110220585</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1106991045300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>785.288</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2569.14</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>161.7271625187192</v>
+      </c>
+      <c r="L7" t="n">
+        <v>48.85110111106686</v>
+      </c>
+      <c r="M7" t="n">
+        <v>992.8571428571429</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.005091278763210426</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>62.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANET</t>
-        </is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>423.93</v>
+      </c>
+      <c r="D8" t="n">
+        <v>52.54069693536469</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2198704466400</v>
+      </c>
+      <c r="H8" t="n">
+        <v>339.144</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2895.992</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>583.1297619890075</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.96825869948879</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44.30242634315425</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7746715058931123</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>59.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CRDO</t>
-        </is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>511.57</v>
+      </c>
+      <c r="D9" t="n">
+        <v>59.09543105138645</v>
+      </c>
+      <c r="G9" t="n">
+        <v>834166042000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>409.256</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1346.4</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>163.1897882987666</v>
+      </c>
+      <c r="L9" t="n">
+        <v>34.33779329067288</v>
+      </c>
+      <c r="M9" t="n">
+        <v>164.3564356435643</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.001279121836992736</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>59.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALAB</t>
-        </is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>68.19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44.15347059351847</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14035312104</v>
+      </c>
+      <c r="H10" t="n">
+        <v>54.552</v>
+      </c>
+      <c r="I10" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>58.0876961431295</v>
+      </c>
+      <c r="L10" t="n">
+        <v>48.46313324550163</v>
+      </c>
+      <c r="M10" t="n">
+        <v>76.20320855614973</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.05347405133841689</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>59.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COHR</t>
-        </is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.95100970898718</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18319192280</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24.368</v>
+      </c>
+      <c r="I11" t="n">
+        <v>63.657</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>108.9855548260013</v>
+      </c>
+      <c r="L11" t="n">
+        <v>46.58532304249225</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.02134750233649494</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>58.8</v>
       </c>
     </row>
     <row r="12">
@@ -2266,20 +3997,86 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LITE</t>
-        </is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>367.15</v>
+      </c>
+      <c r="D12" t="n">
+        <v>65.82053563831519</v>
+      </c>
+      <c r="G12" t="n">
+        <v>62932424804</v>
+      </c>
+      <c r="H12" t="n">
+        <v>293.72</v>
+      </c>
+      <c r="I12" t="n">
+        <v>346</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-5.760588315402418</v>
+      </c>
+      <c r="L12" t="n">
+        <v>115.1265487395594</v>
+      </c>
+      <c r="M12" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.002104860895040239</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MU</t>
-        </is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>921.5599999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>52.22645222376642</v>
+      </c>
+      <c r="G13" t="n">
+        <v>71697368000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>737.248</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1779.0828</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>93.05121750075959</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.02707474985285</v>
+      </c>
+      <c r="M13" t="n">
+        <v>104.679802955665</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.02911543419557605</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -2293,137 +4090,530 @@
           <t>WDC</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>562.925</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60.95952874013678</v>
+      </c>
+      <c r="G14" t="n">
+        <v>194030114850</v>
+      </c>
+      <c r="H14" t="n">
+        <v>450.34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>918.1799999999999</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>63.10876226850824</v>
+      </c>
+      <c r="L14" t="n">
+        <v>50.70444831407313</v>
+      </c>
+      <c r="M14" t="n">
+        <v>303.448275862069</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.015291440724517</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STX</t>
-        </is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>302.87</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43.64967526772283</v>
+      </c>
+      <c r="G15" t="n">
+        <v>116335037102</v>
+      </c>
+      <c r="H15" t="n">
+        <v>242.296</v>
+      </c>
+      <c r="I15" t="n">
+        <v>444.864</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>46.8828210123155</v>
+      </c>
+      <c r="L15" t="n">
+        <v>27.68541401432886</v>
+      </c>
+      <c r="M15" t="n">
+        <v>164.3939393939394</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.01439806993426578</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>56.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DLR</t>
-        </is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30.06701102661019</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2566106205000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>190.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>578.3570999999999</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>142.4469084049465</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.37775468329469</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.79858657243816</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.02578887805619877</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EQIX</t>
-        </is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>931.04</v>
+      </c>
+      <c r="D17" t="n">
+        <v>63.72236503326052</v>
+      </c>
+      <c r="G17" t="n">
+        <v>208766168160</v>
+      </c>
+      <c r="H17" t="n">
+        <v>744.832</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1634.58</v>
+      </c>
+      <c r="K17" t="n">
+        <v>75.56495961505412</v>
+      </c>
+      <c r="L17" t="n">
+        <v>38.86429552740039</v>
+      </c>
+      <c r="M17" t="n">
+        <v>333.125</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.0196583576552244</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>56.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APLD</t>
-        </is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="D18" t="n">
+        <v>41.37140579910967</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20944617678</v>
+      </c>
+      <c r="H18" t="n">
+        <v>103.616</v>
+      </c>
+      <c r="I18" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>190.4570722668313</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.31168744300021</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.02828636020519486</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IRM</t>
-        </is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>116.29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57.82203130476967</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19318094800</v>
+      </c>
+      <c r="H19" t="n">
+        <v>93.03200000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>148.7746151861725</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.83908045977012</v>
+      </c>
+      <c r="M19" t="n">
+        <v>688.2352941176471</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.02256951342841531</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>55.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VRT</t>
-        </is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="D20" t="n">
+        <v>38.23443550576596</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4350282946986</v>
+      </c>
+      <c r="H20" t="n">
+        <v>287.744</v>
+      </c>
+      <c r="I20" t="n">
+        <v>724.0287</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>101.2980149021352</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15.12636492980361</v>
+      </c>
+      <c r="M20" t="n">
+        <v>34.19434194341942</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.006570377225647614</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>55.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOD</t>
-        </is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="D21" t="n">
+        <v>32.11976795001584</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2902584738200</v>
+      </c>
+      <c r="H21" t="n">
+        <v>312.592</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000.35</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>156.0142294108614</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14.93215623240672</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15.51433389544688</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.02823070035530307</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>55.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AAON</t>
-        </is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>184.13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>36.78897043336706</v>
+      </c>
+      <c r="G22" t="n">
+        <v>529566349980</v>
+      </c>
+      <c r="H22" t="n">
+        <v>147.304</v>
+      </c>
+      <c r="I22" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>290.2134361592353</v>
+      </c>
+      <c r="L22" t="n">
+        <v>17.35047648913744</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33.18385650224216</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.235853354361955</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>54.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PWR</t>
-        </is>
+          <t>MDB</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>50.93285270383423</v>
+      </c>
+      <c r="G23" t="n">
+        <v>27572064576</v>
+      </c>
+      <c r="H23" t="n">
+        <v>274.24</v>
+      </c>
+      <c r="I23" t="n">
+        <v>830.05</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>142.1382730455076</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.794268264785</v>
+      </c>
+      <c r="M23" t="n">
+        <v>49.13294797687861</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.038106722008571</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>54.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEV</t>
-        </is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>279.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>61.54754090804533</v>
+      </c>
+      <c r="G24" t="n">
+        <v>244681560000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>223.76</v>
+      </c>
+      <c r="I24" t="n">
+        <v>423</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>51.2334644261709</v>
+      </c>
+      <c r="L24" t="n">
+        <v>42.08728521145076</v>
+      </c>
+      <c r="M24" t="n">
+        <v>403.9215686274509</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.00879306147958187</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>54.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NVT</t>
-        </is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>42.67851682436532</v>
+      </c>
+      <c r="G25" t="n">
+        <v>105348112200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>81.72000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>592.7610000000001</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>480.2848751835537</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.88492352512746</v>
+      </c>
+      <c r="M25" t="n">
+        <v>22.46376811594203</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.004964493326725223</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -2434,116 +4624,437 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POWL</t>
-        </is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>940.66</v>
+      </c>
+      <c r="D26" t="n">
+        <v>44.45652103668439</v>
+      </c>
+      <c r="G26" t="n">
+        <v>252774155200</v>
+      </c>
+      <c r="H26" t="n">
+        <v>752.528</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1350.20825</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>43.53839325579914</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8.943135964284691</v>
+      </c>
+      <c r="M26" t="n">
+        <v>217.7304964539007</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.03500357856205388</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>52.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Electrical Infrastructure</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETN</t>
-        </is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>165.84</v>
+      </c>
+      <c r="D27" t="n">
+        <v>51.44100556280434</v>
+      </c>
+      <c r="G27" t="n">
+        <v>26819644800</v>
+      </c>
+      <c r="H27" t="n">
+        <v>132.672</v>
+      </c>
+      <c r="I27" t="n">
+        <v>214.875</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29.56765557163533</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.50666977146469</v>
+      </c>
+      <c r="M27" t="n">
+        <v>118</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.05501191425175027</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>52.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FIX</t>
-        </is>
+          <t>HYLN</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>63.55542925682136</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1319621576</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.920000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-2.702702702702717</v>
+      </c>
+      <c r="L28" t="n">
+        <v>130.284956925116</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-10.00000000000001</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.01406918493730357</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>48.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EME</t>
-        </is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>163.24</v>
+      </c>
+      <c r="D29" t="n">
+        <v>56.73286174667845</v>
+      </c>
+      <c r="G29" t="n">
+        <v>205546819059</v>
+      </c>
+      <c r="H29" t="n">
+        <v>130.592</v>
+      </c>
+      <c r="I29" t="n">
+        <v>283.4304</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>73.62803234501345</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28.59590752666676</v>
+      </c>
+      <c r="M29" t="n">
+        <v>22.90748898678414</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.009554514192877311</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>48.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>STRL</t>
-        </is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="D30" t="n">
+        <v>52.87739463677856</v>
+      </c>
+      <c r="G30" t="n">
+        <v>61056177684</v>
+      </c>
+      <c r="H30" t="n">
+        <v>308.024</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.41758842132274</v>
+      </c>
+      <c r="M30" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.0488805246775559</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>48.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRWD</t>
-        </is>
+          <t>MWA</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="D31" t="n">
+        <v>53.1733343530544</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4040081220</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20.656</v>
+      </c>
+      <c r="I31" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>59.75987606506584</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8.747242716969652</v>
+      </c>
+      <c r="M31" t="n">
+        <v>66.21621621621621</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-0.004975147504584079</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>47.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PANW</t>
-        </is>
+          <t>FIX</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1877.61</v>
+      </c>
+      <c r="D32" t="n">
+        <v>53.28044715968262</v>
+      </c>
+      <c r="G32" t="n">
+        <v>66096378264</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1502.088</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1479.77962</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-21.1881263947252</v>
+      </c>
+      <c r="L32" t="n">
+        <v>29.51507767511408</v>
+      </c>
+      <c r="M32" t="n">
+        <v>97.60928961748633</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.002964610242596696</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>45.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZS</t>
-        </is>
+          <t>EME</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>823.05</v>
+      </c>
+      <c r="D33" t="n">
+        <v>45.49209998827075</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36652526800</v>
+      </c>
+      <c r="H33" t="n">
+        <v>658.4400000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1094.06</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>32.92752566672742</v>
+      </c>
+      <c r="L33" t="n">
+        <v>16.64056499344094</v>
+      </c>
+      <c r="M33" t="n">
+        <v>30.44886626561778</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.007323233169288618</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>45.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OKTA</t>
-        </is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="D34" t="n">
+        <v>48.649339629541</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11877647000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>375.3374233128834</v>
+      </c>
+      <c r="L34" t="n">
+        <v>18.82069815262765</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-66.66666666666666</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.07854215569800989</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>44.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RBRK</t>
-        </is>
+          <t>XYL</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>110.08</v>
+      </c>
+      <c r="D35" t="n">
+        <v>49.47920548332099</v>
+      </c>
+      <c r="G35" t="n">
+        <v>26165299709</v>
+      </c>
+      <c r="H35" t="n">
+        <v>88.06400000000001</v>
+      </c>
+      <c r="I35" t="n">
+        <v>194.504</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>76.6933139534884</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.524410184536324</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.084468664850142</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-0.02231963732481624</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>44.3</v>
       </c>
     </row>
     <row r="36">
@@ -2554,92 +5065,356 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMAT</t>
-        </is>
+          <t>PLAB</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="D36" t="n">
+        <v>36.07450545502838</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1873866386</v>
+      </c>
+      <c r="H36" t="n">
+        <v>25.424</v>
+      </c>
+      <c r="I36" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>40.18250471994964</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-2.036112975894692</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8.018867924528299</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2595153014287541</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>44.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Electrical Infrastructure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LRCX</t>
-        </is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="D37" t="n">
+        <v>45.54758688717234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>151976737000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>313.112</v>
+      </c>
+      <c r="I37" t="n">
+        <v>589.375</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>50.58509415161348</v>
+      </c>
+      <c r="L37" t="n">
+        <v>10.33041241257336</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9.958071278826008</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-0.06939877910393615</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>43.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KLAC</t>
-        </is>
+          <t>TLN</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="D38" t="n">
+        <v>48.68513013486872</v>
+      </c>
+      <c r="G38" t="n">
+        <v>16474877103</v>
+      </c>
+      <c r="H38" t="n">
+        <v>288.432</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1164.9572</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>223.1145503966272</v>
+      </c>
+      <c r="L38" t="n">
+        <v>21.80414857694163</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-126.0467645459489</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.3683790757319132</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ONTO</t>
-        </is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>50.19293882203778</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12202359315</v>
+      </c>
+      <c r="H39" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-69.67213114754098</v>
+      </c>
+      <c r="L39" t="n">
+        <v>57.74348914491502</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11.45038167938932</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-0.0482658299756845</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>42.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ACLS</t>
-        </is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>43.96457275320387</v>
+      </c>
+      <c r="G40" t="n">
+        <v>64728985200</v>
+      </c>
+      <c r="H40" t="n">
+        <v>147.36</v>
+      </c>
+      <c r="I40" t="n">
+        <v>109.2924</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-40.66644951140065</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10.04009384032455</v>
+      </c>
+      <c r="M40" t="n">
+        <v>114.367816091954</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.320267356825486</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>42.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PLAB</t>
-        </is>
+          <t>MOD</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>49.52976867480221</v>
+      </c>
+      <c r="G41" t="n">
+        <v>14497932983</v>
+      </c>
+      <c r="H41" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>449.49212</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>63.74940619307833</v>
+      </c>
+      <c r="L41" t="n">
+        <v>23.13141087671763</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-35.71428571428572</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-0.03494291224783764</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>41.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TSM</t>
-        </is>
+          <t>AJG</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>218.69</v>
+      </c>
+      <c r="D42" t="n">
+        <v>63.84261783701408</v>
+      </c>
+      <c r="G42" t="n">
+        <v>56190645980</v>
+      </c>
+      <c r="H42" t="n">
+        <v>174.952</v>
+      </c>
+      <c r="I42" t="n">
+        <v>417.134</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>90.74214641730302</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20.65703727422998</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-12.06636500754148</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.224307796790344</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>41.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GFS</t>
-        </is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>260.22</v>
+      </c>
+      <c r="D43" t="n">
+        <v>46.56538649954902</v>
+      </c>
+      <c r="G43" t="n">
+        <v>74017983331</v>
+      </c>
+      <c r="H43" t="n">
+        <v>208.176</v>
+      </c>
+      <c r="I43" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>36.21166705095686</v>
+      </c>
+      <c r="L43" t="n">
+        <v>37.326441660515</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-184.6153846153846</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-0.007266396297165012</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>41.1</v>
       </c>
     </row>
     <row r="44">
@@ -2650,68 +5425,266 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INTC</t>
-        </is>
+          <t>GFS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="D44" t="n">
+        <v>56.64049311373668</v>
+      </c>
+      <c r="G44" t="n">
+        <v>44630129887</v>
+      </c>
+      <c r="H44" t="n">
+        <v>65.104</v>
+      </c>
+      <c r="I44" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-15.65495207667731</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.6074074074074074</v>
+      </c>
+      <c r="M44" t="n">
+        <v>431.2500000000001</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.003831492322181419</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>39.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TSEM</t>
-        </is>
+          <t>EQIX</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1055.85</v>
+      </c>
+      <c r="D45" t="n">
+        <v>45.56696073083926</v>
+      </c>
+      <c r="G45" t="n">
+        <v>104132361570</v>
+      </c>
+      <c r="H45" t="n">
+        <v>844.6799999999999</v>
+      </c>
+      <c r="I45" t="n">
+        <v>869.4</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-17.65875834635601</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5.852766346593507</v>
+      </c>
+      <c r="M45" t="n">
+        <v>61.47540983606557</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-0.2016568114215294</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMCI</t>
-        </is>
+          <t>MSI</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>51.89357274675201</v>
+      </c>
+      <c r="G46" t="n">
+        <v>68431851000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>443.74792</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>7.64048999393571</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.996671905334196</v>
+      </c>
+      <c r="M46" t="n">
+        <v>36.82539682539684</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-0.1256870868508292</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>38.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DELL</t>
-        </is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="D47" t="n">
+        <v>49.95997216728615</v>
+      </c>
+      <c r="G47" t="n">
+        <v>139600118647</v>
+      </c>
+      <c r="H47" t="n">
+        <v>176.248</v>
+      </c>
+      <c r="I47" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>49.08991875085106</v>
+      </c>
+      <c r="L47" t="n">
+        <v>7.849180516749719</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-15.52511415525113</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0.1582591778153534</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>38.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HPE</t>
-        </is>
+          <t>STRL</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>858.99</v>
+      </c>
+      <c r="D48" t="n">
+        <v>53.82124832804914</v>
+      </c>
+      <c r="G48" t="n">
+        <v>26358927626</v>
+      </c>
+      <c r="H48" t="n">
+        <v>687.192</v>
+      </c>
+      <c r="I48" t="n">
+        <v>915.2</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6.543731591753109</v>
+      </c>
+      <c r="L48" t="n">
+        <v>17.69074505755862</v>
+      </c>
+      <c r="M48" t="n">
+        <v>13.77245508982037</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.001548128231125331</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>37.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NOW</t>
-        </is>
+          <t>BMI</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>131.73</v>
+      </c>
+      <c r="D49" t="n">
+        <v>63.01595511661963</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3844615136</v>
+      </c>
+      <c r="H49" t="n">
+        <v>105.384</v>
+      </c>
+      <c r="I49" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>39.86942989448114</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10.9012313715432</v>
+      </c>
+      <c r="M49" t="n">
+        <v>13.1455399061033</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.0587876788715842</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>37.9</v>
       </c>
     </row>
     <row r="50">
@@ -2725,316 +5698,1147 @@
           <t>DDOG</t>
         </is>
       </c>
+      <c r="C50" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="D50" t="n">
+        <v>53.049769565106</v>
+      </c>
+      <c r="G50" t="n">
+        <v>81835245382</v>
+      </c>
+      <c r="H50" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="I50" t="n">
+        <v>304.85</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>32.60113092648979</v>
+      </c>
+      <c r="L50" t="n">
+        <v>27.67536858183308</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-43.63636363636364</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0.01385572921187089</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>37.3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DT</t>
-        </is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>707.74</v>
+      </c>
+      <c r="D51" t="n">
+        <v>51.40483678925918</v>
+      </c>
+      <c r="G51" t="n">
+        <v>106203464400</v>
+      </c>
+      <c r="H51" t="n">
+        <v>566.192</v>
+      </c>
+      <c r="I51" t="n">
+        <v>656.0500000000001</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-7.303529544748062</v>
+      </c>
+      <c r="L51" t="n">
+        <v>19.76398224206309</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11.52597402597403</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-0.05630179800424665</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>36.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AI</t>
-        </is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="D52" t="n">
+        <v>60.95609391375104</v>
+      </c>
+      <c r="G52" t="n">
+        <v>63786883607</v>
+      </c>
+      <c r="H52" t="n">
+        <v>38.536</v>
+      </c>
+      <c r="I52" t="n">
+        <v>91.611</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>90.18268631928586</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14.0614606891047</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-102.2871794871795</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-0.2869555457948617</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>36.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MDB</t>
-        </is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>124.57</v>
+      </c>
+      <c r="D53" t="n">
+        <v>63.54960300150914</v>
+      </c>
+      <c r="G53" t="n">
+        <v>626088820000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>99.65600000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>99.495</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-20.12924460142891</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.4670345191239336</v>
+      </c>
+      <c r="M53" t="n">
+        <v>98.6552511415525</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0.05162206857487089</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>36.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BE</t>
-        </is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="D54" t="n">
+        <v>47.07700216251646</v>
+      </c>
+      <c r="G54" t="n">
+        <v>49909748913</v>
+      </c>
+      <c r="H54" t="n">
+        <v>118.416</v>
+      </c>
+      <c r="I54" t="n">
+        <v>365.82172</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>147.1434400756654</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-12.41162202611343</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-69.1340782122905</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0.3922880885281363</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>36.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FLNC</t>
-        </is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>395.57</v>
+      </c>
+      <c r="D55" t="n">
+        <v>62.3936768396651</v>
+      </c>
+      <c r="G55" t="n">
+        <v>262757745523</v>
+      </c>
+      <c r="H55" t="n">
+        <v>316.456</v>
+      </c>
+      <c r="I55" t="n">
+        <v>378.54</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-4.305179867027321</v>
+      </c>
+      <c r="L55" t="n">
+        <v>18.80460828528676</v>
+      </c>
+      <c r="M55" t="n">
+        <v>37.63440860215056</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0.07602059440813526</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>36.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HYLN</t>
-        </is>
+          <t>ALRM</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="D56" t="n">
+        <v>66.04922606230821</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2307336990</v>
+      </c>
+      <c r="H56" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="I56" t="n">
+        <v>70.17999999999999</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>50.43944265809216</v>
+      </c>
+      <c r="L56" t="n">
+        <v>7.592886775970471</v>
+      </c>
+      <c r="M56" t="n">
+        <v>6.400000000000006</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0.07392331538012573</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>36.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MSFT</t>
-        </is>
+          <t>JCI</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>144.96</v>
+      </c>
+      <c r="D57" t="n">
+        <v>55.29855678083622</v>
+      </c>
+      <c r="G57" t="n">
+        <v>88442357811</v>
+      </c>
+      <c r="H57" t="n">
+        <v>115.968</v>
+      </c>
+      <c r="I57" t="n">
+        <v>192.86674</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>33.04824779249446</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.805855698849773</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.347826086956535</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0.1222378085295164</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMZN</t>
-        </is>
+          <t>RYAN</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="D58" t="n">
+        <v>65.72027562083166</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4612322979</v>
+      </c>
+      <c r="H58" t="n">
+        <v>28.512</v>
+      </c>
+      <c r="I58" t="n">
+        <v>66.185</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>85.70426487093155</v>
+      </c>
+      <c r="L58" t="n">
+        <v>21.28289826728836</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-35.8974358974359</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0.7311723431673409</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>35.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ORCL</t>
-        </is>
+          <t>AAON</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="D59" t="n">
+        <v>44.85644056546728</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10418349123</v>
+      </c>
+      <c r="H59" t="n">
+        <v>101.752</v>
+      </c>
+      <c r="I59" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.825536598789222</v>
+      </c>
+      <c r="L59" t="n">
+        <v>20.10944208689568</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-36.23188405797101</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0.04075818490883184</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CRWV</t>
-        </is>
+          <t>POWL</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="D60" t="n">
+        <v>54.64875419262177</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10738214100</v>
+      </c>
+      <c r="H60" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-20.52586938083122</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9.083958607446393</v>
+      </c>
+      <c r="M60" t="n">
+        <v>19.74420463629097</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.04182026879125086</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>33.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NBIS</t>
-        </is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="D61" t="n">
+        <v>70.27105315932964</v>
+      </c>
+      <c r="G61" t="n">
+        <v>458721581700</v>
+      </c>
+      <c r="H61" t="n">
+        <v>293.448</v>
+      </c>
+      <c r="I61" t="n">
+        <v>278.96</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-23.9497287424007</v>
+      </c>
+      <c r="L61" t="n">
+        <v>23.68408976459919</v>
+      </c>
+      <c r="M61" t="n">
+        <v>43.29896907216494</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.003562300238728881</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>33.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GOOGL</t>
-        </is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D62" t="n">
+        <v>40.90433077762285</v>
+      </c>
+      <c r="G62" t="n">
+        <v>10002741843</v>
+      </c>
+      <c r="H62" t="n">
+        <v>45.992</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9.731479999999999</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-83.07274308575406</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.264812575574363</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.07867792774745512</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JCI</t>
-        </is>
+          <t>IRM</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="D63" t="n">
+        <v>53.73108403269065</v>
+      </c>
+      <c r="G63" t="n">
+        <v>37857040410</v>
+      </c>
+      <c r="H63" t="n">
+        <v>101.792</v>
+      </c>
+      <c r="L63" t="n">
+        <v>12.2250264190901</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-19.67213114754098</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0.4990617543100221</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CARR</t>
-        </is>
+          <t>FLNC</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="D64" t="n">
+        <v>53.51949595703279</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4375127109</v>
+      </c>
+      <c r="H64" t="n">
+        <v>18.968</v>
+      </c>
+      <c r="I64" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>60.69169126950654</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-16.14682189996005</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-305.5555555555556</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.06856120805792114</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HON</t>
-        </is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>254.54</v>
+      </c>
+      <c r="D65" t="n">
+        <v>78.81342629851409</v>
+      </c>
+      <c r="G65" t="n">
+        <v>332500511200</v>
+      </c>
+      <c r="H65" t="n">
+        <v>203.632</v>
+      </c>
+      <c r="I65" t="n">
+        <v>167.816</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-34.07087294727744</v>
+      </c>
+      <c r="L65" t="n">
+        <v>23.88764775285416</v>
+      </c>
+      <c r="M65" t="n">
+        <v>49.58353748162666</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0.01205824913029487</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>XYL</t>
-        </is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>262.92</v>
+      </c>
+      <c r="D66" t="n">
+        <v>55.28695757942516</v>
+      </c>
+      <c r="G66" t="n">
+        <v>29383050530</v>
+      </c>
+      <c r="H66" t="n">
+        <v>210.336</v>
+      </c>
+      <c r="I66" t="n">
+        <v>186.45</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-29.08489274303971</v>
+      </c>
+      <c r="L66" t="n">
+        <v>9.050902360662953</v>
+      </c>
+      <c r="M66" t="n">
+        <v>5.347593582887693</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.002513387775193674</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>30.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BMI</t>
-        </is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>59.57710871757248</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1545524407</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="I67" t="n">
+        <v>26</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>138.5321100917431</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-35.67301365356144</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-49.55357142857142</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.04283141676713748</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MWA</t>
-        </is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>682.8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>55.74085015608213</v>
+      </c>
+      <c r="G68" t="n">
+        <v>173816859096</v>
+      </c>
+      <c r="H68" t="n">
+        <v>546.24</v>
+      </c>
+      <c r="I68" t="n">
+        <v>542.8499999999999</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-20.49648506151143</v>
+      </c>
+      <c r="L68" t="n">
+        <v>21.71124517657724</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-725.9212198221093</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.025371808137232</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>28.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AJG</t>
-        </is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="D69" t="n">
+        <v>41.97066885629098</v>
+      </c>
+      <c r="G69" t="n">
+        <v>963885433</v>
+      </c>
+      <c r="H69" t="n">
+        <v>18.544</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-67.53999999999999</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-391.3718723037101</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-171.7948717948718</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.2079806407863828</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>28.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RYAN</t>
-        </is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="D70" t="n">
+        <v>63.26010553616113</v>
+      </c>
+      <c r="G70" t="n">
+        <v>190564196417</v>
+      </c>
+      <c r="H70" t="n">
+        <v>223.696</v>
+      </c>
+      <c r="L70" t="n">
+        <v>14.87387106820305</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-57.67326732673267</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.01012991966117194</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>27.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MSI</t>
-        </is>
+          <t>CARR</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="D71" t="n">
+        <v>61.65974138881817</v>
+      </c>
+      <c r="G71" t="n">
+        <v>58065877372</v>
+      </c>
+      <c r="H71" t="n">
+        <v>55.928</v>
+      </c>
+      <c r="I71" t="n">
+        <v>98.33999999999999</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>40.66657130596481</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-3.28648937116428</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-72.11538461538461</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-0.1914032905900651</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>27.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ALRM</t>
-        </is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="D72" t="n">
+        <v>38.82083527167553</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2948979807</v>
+      </c>
+      <c r="H72" t="n">
+        <v>7.912000000000001</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.924</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-109.3427704752275</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-15.02496963152922</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-47.61904761904761</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.2836292734235057</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>26.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NVDA</t>
-        </is>
+          <t>ONTO</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>323.88</v>
+      </c>
+      <c r="D73" t="n">
+        <v>71.37396348704004</v>
+      </c>
+      <c r="G73" t="n">
+        <v>16110946480</v>
+      </c>
+      <c r="H73" t="n">
+        <v>259.104</v>
+      </c>
+      <c r="I73" t="n">
+        <v>359.04</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>10.85587254538719</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.817240796053158</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-32.02933985330073</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.02039880154825019</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>25.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AMD</t>
-        </is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>567.25</v>
+      </c>
+      <c r="D74" t="n">
+        <v>76.60046560954015</v>
+      </c>
+      <c r="G74" t="n">
+        <v>450373486668</v>
+      </c>
+      <c r="H74" t="n">
+        <v>453.8</v>
+      </c>
+      <c r="I74" t="n">
+        <v>465.99344</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-17.85042926399295</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.386223138062997</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.3456221198156813</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.0004240924602668689</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>23.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AVGO</t>
-        </is>
+          <t>ACLS</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>180.12</v>
+      </c>
+      <c r="D75" t="n">
+        <v>66.80815558640113</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5535789528</v>
+      </c>
+      <c r="H75" t="n">
+        <v>144.096</v>
+      </c>
+      <c r="I75" t="n">
+        <v>110.22</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-38.80746169220519</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-17.56785035343587</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-38.24959481361427</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.01862823712469728</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>17.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CEG</t>
         </is>
       </c>
     </row>
@@ -3140,12 +6944,78 @@
           <t>MSI</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.89357274675201</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68431851000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>443.74792</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7.64048999393571</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.996671905334196</v>
+      </c>
+      <c r="L2" t="n">
+        <v>36.82539682539684</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.1256870868508292</v>
+      </c>
+      <c r="P2" t="n">
+        <v>38.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>ALRM</t>
         </is>
+      </c>
+      <c r="B3" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="C3" t="n">
+        <v>66.04922606230821</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2307336990</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="H3" t="n">
+        <v>70.17999999999999</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50.43944265809216</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.592886775970471</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.400000000000006</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.07392331538012573</v>
+      </c>
+      <c r="P3" t="n">
+        <v>36.2</v>
       </c>
     </row>
   </sheetData>
@@ -3250,6 +7120,39 @@
           <t>NVDA</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>205.19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>42.74811543778459</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4969906990000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>164.152</v>
+      </c>
+      <c r="H2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>338.6178663677567</v>
+      </c>
+      <c r="K2" t="n">
+        <v>65.4735357900948</v>
+      </c>
+      <c r="L2" t="n">
+        <v>65.99326599326596</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.000162377284247728</v>
+      </c>
+      <c r="P2" t="n">
+        <v>67.59999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3257,6 +7160,39 @@
           <t>AMD</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>511.57</v>
+      </c>
+      <c r="C3" t="n">
+        <v>59.09543105138645</v>
+      </c>
+      <c r="F3" t="n">
+        <v>834166042000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>409.256</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1346.4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>163.1897882987666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>34.33779329067288</v>
+      </c>
+      <c r="L3" t="n">
+        <v>164.3564356435643</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001279121836992736</v>
+      </c>
+      <c r="P3" t="n">
+        <v>59.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3264,12 +7200,78 @@
           <t>AVGO</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="C4" t="n">
+        <v>38.4627508262627</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1817728590600</v>
+      </c>
+      <c r="G4" t="n">
+        <v>305.656</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1575</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>312.2281257361217</v>
+      </c>
+      <c r="K4" t="n">
+        <v>23.87443285376353</v>
+      </c>
+      <c r="L4" t="n">
+        <v>286.6141732283465</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.02693361388117894</v>
+      </c>
+      <c r="P4" t="n">
+        <v>63.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>MRVL</t>
         </is>
+      </c>
+      <c r="B5" t="n">
+        <v>279.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61.54754090804533</v>
+      </c>
+      <c r="F5" t="n">
+        <v>244681560000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>223.76</v>
+      </c>
+      <c r="H5" t="n">
+        <v>423</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51.2334644261709</v>
+      </c>
+      <c r="K5" t="n">
+        <v>42.08728521145076</v>
+      </c>
+      <c r="L5" t="n">
+        <v>403.9215686274509</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.00879306147958187</v>
+      </c>
+      <c r="P5" t="n">
+        <v>54.6</v>
       </c>
     </row>
   </sheetData>
@@ -3381,6 +7383,39 @@
           <t>VST</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47.07700216251646</v>
+      </c>
+      <c r="F3" t="n">
+        <v>49909748913</v>
+      </c>
+      <c r="G3" t="n">
+        <v>118.416</v>
+      </c>
+      <c r="H3" t="n">
+        <v>365.82172</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>147.1434400756654</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-12.41162202611343</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-69.1340782122905</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.3922880885281363</v>
+      </c>
+      <c r="P3" t="n">
+        <v>36.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3388,6 +7423,39 @@
           <t>TLN</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="C4" t="n">
+        <v>48.68513013486872</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16474877103</v>
+      </c>
+      <c r="G4" t="n">
+        <v>288.432</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1164.9572</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>223.1145503966272</v>
+      </c>
+      <c r="K4" t="n">
+        <v>21.80414857694163</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-126.0467645459489</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.3683790757319132</v>
+      </c>
+      <c r="P4" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3395,6 +7463,39 @@
           <t>OKLO</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40.90433077762285</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10002741843</v>
+      </c>
+      <c r="G5" t="n">
+        <v>45.992</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.731479999999999</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-83.07274308575406</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.264812575574363</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.07867792774745512</v>
+      </c>
+      <c r="P5" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3402,12 +7503,72 @@
           <t>SMR</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38.82083527167553</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2948979807</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.912000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.924</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-109.3427704752275</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-15.02496963152922</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-47.61904761904761</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2836292734235057</v>
+      </c>
+      <c r="P6" t="n">
+        <v>26.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>NNE</t>
         </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>41.97066885629098</v>
+      </c>
+      <c r="F7" t="n">
+        <v>963885433</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.544</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-67.53999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-391.3718723037101</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-171.7948717948718</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2079806407863828</v>
+      </c>
+      <c r="P7" t="n">
+        <v>28.2</v>
       </c>
     </row>
   </sheetData>
@@ -3512,6 +7673,39 @@
           <t>ANET</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>163.24</v>
+      </c>
+      <c r="C2" t="n">
+        <v>56.73286174667845</v>
+      </c>
+      <c r="F2" t="n">
+        <v>205546819059</v>
+      </c>
+      <c r="G2" t="n">
+        <v>130.592</v>
+      </c>
+      <c r="H2" t="n">
+        <v>283.4304</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>73.62803234501345</v>
+      </c>
+      <c r="K2" t="n">
+        <v>28.59590752666676</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22.90748898678414</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.009554514192877311</v>
+      </c>
+      <c r="P2" t="n">
+        <v>48.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3519,6 +7713,39 @@
           <t>CRDO</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>250.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>64.44619442285625</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46261889451</v>
+      </c>
+      <c r="G3" t="n">
+        <v>200.648</v>
+      </c>
+      <c r="H3" t="n">
+        <v>500</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>99.35409273952394</v>
+      </c>
+      <c r="K3" t="n">
+        <v>205.6759200961594</v>
+      </c>
+      <c r="L3" t="n">
+        <v>754.8387096774193</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02473601950936451</v>
+      </c>
+      <c r="P3" t="n">
+        <v>71.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3526,6 +7753,39 @@
           <t>ALAB</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>367.15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>65.82053563831519</v>
+      </c>
+      <c r="F4" t="n">
+        <v>62932424804</v>
+      </c>
+      <c r="G4" t="n">
+        <v>293.72</v>
+      </c>
+      <c r="H4" t="n">
+        <v>346</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-5.760588315402418</v>
+      </c>
+      <c r="K4" t="n">
+        <v>115.1265487395594</v>
+      </c>
+      <c r="L4" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.002104860895040239</v>
+      </c>
+      <c r="P4" t="n">
+        <v>58.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3533,12 +7793,69 @@
           <t>COHR</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="C5" t="n">
+        <v>52.87739463677856</v>
+      </c>
+      <c r="F5" t="n">
+        <v>61056177684</v>
+      </c>
+      <c r="G5" t="n">
+        <v>308.024</v>
+      </c>
+      <c r="K5" t="n">
+        <v>23.41758842132274</v>
+      </c>
+      <c r="L5" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.0488805246775559</v>
+      </c>
+      <c r="P5" t="n">
+        <v>48.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>LITE</t>
         </is>
+      </c>
+      <c r="B6" t="n">
+        <v>921.5599999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>52.22645222376642</v>
+      </c>
+      <c r="F6" t="n">
+        <v>71697368000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>737.248</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1779.0828</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>93.05121750075959</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21.02707474985285</v>
+      </c>
+      <c r="L6" t="n">
+        <v>104.679802955665</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.02911543419557605</v>
+      </c>
+      <c r="P6" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3643,6 +7960,39 @@
           <t>MU</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>981.61</v>
+      </c>
+      <c r="C2" t="n">
+        <v>59.02601110220585</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1106991045300</v>
+      </c>
+      <c r="G2" t="n">
+        <v>785.288</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2569.14</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>161.7271625187192</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48.85110111106686</v>
+      </c>
+      <c r="L2" t="n">
+        <v>992.8571428571429</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.005091278763210426</v>
+      </c>
+      <c r="P2" t="n">
+        <v>62.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3650,12 +8000,75 @@
           <t>WDC</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>562.925</v>
+      </c>
+      <c r="C3" t="n">
+        <v>60.95952874013678</v>
+      </c>
+      <c r="F3" t="n">
+        <v>194030114850</v>
+      </c>
+      <c r="G3" t="n">
+        <v>450.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>918.1799999999999</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>63.10876226850824</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50.70444831407313</v>
+      </c>
+      <c r="L3" t="n">
+        <v>303.448275862069</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.015291440724517</v>
+      </c>
+      <c r="P3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>STX</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>931.04</v>
+      </c>
+      <c r="C4" t="n">
+        <v>63.72236503326052</v>
+      </c>
+      <c r="F4" t="n">
+        <v>208766168160</v>
+      </c>
+      <c r="G4" t="n">
+        <v>744.832</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1634.58</v>
+      </c>
+      <c r="J4" t="n">
+        <v>75.56495961505412</v>
+      </c>
+      <c r="K4" t="n">
+        <v>38.86429552740039</v>
+      </c>
+      <c r="L4" t="n">
+        <v>333.125</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0196583576552244</v>
+      </c>
+      <c r="P4" t="n">
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
@@ -3760,6 +8173,39 @@
           <t>DLR</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.96457275320387</v>
+      </c>
+      <c r="F2" t="n">
+        <v>64728985200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>147.36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>109.2924</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-40.66644951140065</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.04009384032455</v>
+      </c>
+      <c r="L2" t="n">
+        <v>114.367816091954</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.320267356825486</v>
+      </c>
+      <c r="P2" t="n">
+        <v>42.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3767,6 +8213,39 @@
           <t>EQIX</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>1055.85</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45.56696073083926</v>
+      </c>
+      <c r="F3" t="n">
+        <v>104132361570</v>
+      </c>
+      <c r="G3" t="n">
+        <v>844.6799999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>869.4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-17.65875834635601</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.852766346593507</v>
+      </c>
+      <c r="L3" t="n">
+        <v>61.47540983606557</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.2016568114215294</v>
+      </c>
+      <c r="P3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3774,12 +8253,69 @@
           <t>APLD</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50.19293882203778</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12202359315</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-69.67213114754098</v>
+      </c>
+      <c r="K4" t="n">
+        <v>57.74348914491502</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.45038167938932</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.0482658299756845</v>
+      </c>
+      <c r="P4" t="n">
+        <v>42.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>IRM</t>
         </is>
+      </c>
+      <c r="B5" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>53.73108403269065</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37857040410</v>
+      </c>
+      <c r="G5" t="n">
+        <v>101.792</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12.2250264190901</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-19.67213114754098</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.4990617543100221</v>
+      </c>
+      <c r="P5" t="n">
+        <v>31.3</v>
       </c>
     </row>
   </sheetData>
@@ -3884,6 +8420,39 @@
           <t>VRT</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>302.87</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43.64967526772283</v>
+      </c>
+      <c r="F2" t="n">
+        <v>116335037102</v>
+      </c>
+      <c r="G2" t="n">
+        <v>242.296</v>
+      </c>
+      <c r="H2" t="n">
+        <v>444.864</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.8828210123155</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.68541401432886</v>
+      </c>
+      <c r="L2" t="n">
+        <v>164.3939393939394</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.01439806993426578</v>
+      </c>
+      <c r="P2" t="n">
+        <v>56.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3891,12 +8460,78 @@
           <t>MOD</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49.52976867480221</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14497932983</v>
+      </c>
+      <c r="G3" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>449.49212</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>63.74940619307833</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.13141087671763</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-35.71428571428572</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.03494291224783764</v>
+      </c>
+      <c r="P3" t="n">
+        <v>41.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>AAON</t>
         </is>
+      </c>
+      <c r="B4" t="n">
+        <v>127.19</v>
+      </c>
+      <c r="C4" t="n">
+        <v>44.85644056546728</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10418349123</v>
+      </c>
+      <c r="G4" t="n">
+        <v>101.752</v>
+      </c>
+      <c r="H4" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.825536598789222</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20.10944208689568</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-36.23188405797101</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.04075818490883184</v>
+      </c>
+      <c r="P4" t="n">
+        <v>35.2</v>
       </c>
     </row>
   </sheetData>
@@ -4001,6 +8636,39 @@
           <t>PWR</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>707.74</v>
+      </c>
+      <c r="C2" t="n">
+        <v>51.40483678925918</v>
+      </c>
+      <c r="F2" t="n">
+        <v>106203464400</v>
+      </c>
+      <c r="G2" t="n">
+        <v>566.192</v>
+      </c>
+      <c r="H2" t="n">
+        <v>656.0500000000001</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-7.303529544748062</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.76398224206309</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11.52597402597403</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.05630179800424665</v>
+      </c>
+      <c r="P2" t="n">
+        <v>36.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4008,6 +8676,39 @@
           <t>GEV</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>940.66</v>
+      </c>
+      <c r="C3" t="n">
+        <v>44.45652103668439</v>
+      </c>
+      <c r="F3" t="n">
+        <v>252774155200</v>
+      </c>
+      <c r="G3" t="n">
+        <v>752.528</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1350.20825</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.53839325579914</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.943135964284691</v>
+      </c>
+      <c r="L3" t="n">
+        <v>217.7304964539007</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03500357856205388</v>
+      </c>
+      <c r="P3" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4015,12 +8716,78 @@
           <t>NVT</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>165.84</v>
+      </c>
+      <c r="C4" t="n">
+        <v>51.44100556280434</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26819644800</v>
+      </c>
+      <c r="G4" t="n">
+        <v>132.672</v>
+      </c>
+      <c r="H4" t="n">
+        <v>214.875</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.56765557163533</v>
+      </c>
+      <c r="K4" t="n">
+        <v>29.50666977146469</v>
+      </c>
+      <c r="L4" t="n">
+        <v>118</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.05501191425175027</v>
+      </c>
+      <c r="P4" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>POWL</t>
         </is>
+      </c>
+      <c r="B5" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="C5" t="n">
+        <v>54.64875419262177</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10738214100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-20.52586938083122</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.083958607446393</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19.74420463629097</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04182026879125086</v>
+      </c>
+      <c r="P5" t="n">
+        <v>33.5</v>
       </c>
     </row>
   </sheetData>
@@ -4125,6 +8892,39 @@
           <t>ETN</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45.54758688717234</v>
+      </c>
+      <c r="F2" t="n">
+        <v>151976737000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>313.112</v>
+      </c>
+      <c r="H2" t="n">
+        <v>589.375</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50.58509415161348</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.33041241257336</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.958071278826008</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.06939877910393615</v>
+      </c>
+      <c r="P2" t="n">
+        <v>43.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/investment-engine/sector/AI/stock-data/investment_data_06152026.xlsx
+++ b/investment-engine/sector/AI/stock-data/investment_data_06152026.xlsx
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>205.19</v>
+        <v>212.45</v>
       </c>
       <c r="D2" t="n">
-        <v>45.24</v>
+        <v>51.29</v>
       </c>
       <c r="E2" t="n">
-        <v>31.42</v>
+        <v>32.54</v>
       </c>
       <c r="F2" t="n">
-        <v>19.59</v>
+        <v>20.28</v>
       </c>
       <c r="G2" t="n">
-        <v>4965598060000</v>
+        <v>5141289930000</v>
       </c>
       <c r="H2" t="n">
-        <v>164.15</v>
+        <v>169.96</v>
       </c>
       <c r="I2" t="n">
         <v>309.93</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>51.05</v>
+        <v>45.88</v>
       </c>
       <c r="L2" t="n">
         <v>85.23</v>
@@ -609,214 +609,214 @@
         <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>74.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>981.61</v>
+        <v>30.85</v>
       </c>
       <c r="D3" t="n">
-        <v>60.77</v>
+        <v>41.77</v>
       </c>
       <c r="E3" t="n">
-        <v>46.34</v>
+        <v>16.27</v>
       </c>
       <c r="F3" t="n">
-        <v>19.05</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1106994960000</v>
+        <v>18553760000</v>
       </c>
       <c r="H3" t="n">
-        <v>785.29</v>
+        <v>24.68</v>
       </c>
       <c r="I3" t="n">
-        <v>921.02</v>
+        <v>35.87</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.17</v>
+        <v>16.27</v>
       </c>
       <c r="L3" t="n">
-        <v>196.29</v>
+        <v>122.68</v>
       </c>
       <c r="M3" t="n">
-        <v>756.34</v>
+        <v>314.07</v>
       </c>
       <c r="N3" t="n">
-        <v>58.54</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>41.49</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0.15</v>
+        <v>1.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0.44</v>
+        <v>13.87</v>
       </c>
       <c r="S3" t="n">
-        <v>78.14</v>
+        <v>57.79</v>
       </c>
       <c r="T3" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>65.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.46</v>
+        <v>1087.99</v>
       </c>
       <c r="D4" t="n">
-        <v>41.12</v>
+        <v>66.56</v>
       </c>
       <c r="E4" t="n">
-        <v>16.07</v>
+        <v>51.37</v>
       </c>
       <c r="F4" t="n">
-        <v>0.54</v>
+        <v>21.11</v>
       </c>
       <c r="G4" t="n">
-        <v>18319210000</v>
+        <v>1226963310000</v>
       </c>
       <c r="H4" t="n">
-        <v>24.37</v>
+        <v>870.39</v>
       </c>
       <c r="I4" t="n">
-        <v>35.87</v>
+        <v>942.02</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>17.76</v>
+        <v>-13.42</v>
       </c>
       <c r="L4" t="n">
-        <v>122.68</v>
+        <v>196.29</v>
       </c>
       <c r="M4" t="n">
-        <v>314.07</v>
+        <v>756.34</v>
       </c>
       <c r="N4" t="n">
-        <v>8.390000000000001</v>
+        <v>58.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>41.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.21</v>
+        <v>0.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="R4" t="n">
-        <v>13.87</v>
+        <v>0.44</v>
       </c>
       <c r="S4" t="n">
-        <v>57.79</v>
+        <v>78.14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="U4" t="n">
-        <v>65.3</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PLAB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>390.74</v>
+        <v>32.74</v>
       </c>
       <c r="D5" t="n">
-        <v>37.09</v>
+        <v>38.43</v>
       </c>
       <c r="E5" t="n">
-        <v>23.27</v>
+        <v>11.99</v>
       </c>
       <c r="F5" t="n">
-        <v>9.119999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2902586450000</v>
+        <v>1930480000</v>
       </c>
       <c r="H5" t="n">
-        <v>312.59</v>
+        <v>26.19</v>
       </c>
       <c r="I5" t="n">
-        <v>559.29</v>
+        <v>43</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>43.14</v>
+        <v>31.34</v>
       </c>
       <c r="L5" t="n">
-        <v>18.3</v>
+        <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>23.32</v>
+        <v>268.2</v>
       </c>
       <c r="N5" t="n">
-        <v>68.31</v>
+        <v>33.77</v>
       </c>
       <c r="O5" t="n">
-        <v>39.34</v>
+        <v>18.47</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>4.06</v>
       </c>
       <c r="S5" t="n">
-        <v>74.78</v>
+        <v>95.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>64.2</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="6">
@@ -827,134 +827,134 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>359.68</v>
+        <v>399.76</v>
       </c>
       <c r="D6" t="n">
-        <v>42.37</v>
+        <v>42.72</v>
       </c>
       <c r="E6" t="n">
-        <v>27.44</v>
+        <v>23.81</v>
       </c>
       <c r="F6" t="n">
-        <v>10.28</v>
+        <v>9.33</v>
       </c>
       <c r="G6" t="n">
-        <v>4349630750000</v>
+        <v>2969591070000</v>
       </c>
       <c r="H6" t="n">
-        <v>287.74</v>
+        <v>319.81</v>
       </c>
       <c r="I6" t="n">
-        <v>434.43</v>
+        <v>559.29</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20.78</v>
+        <v>39.91</v>
       </c>
       <c r="L6" t="n">
-        <v>22.34</v>
+        <v>18.3</v>
       </c>
       <c r="M6" t="n">
-        <v>81.95999999999999</v>
+        <v>23.32</v>
       </c>
       <c r="N6" t="n">
-        <v>60.43</v>
+        <v>68.31</v>
       </c>
       <c r="O6" t="n">
-        <v>37.86</v>
+        <v>39.34</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="R6" t="n">
-        <v>52.1</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>38.87</v>
+        <v>74.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="U6" t="n">
-        <v>64</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLAB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.78</v>
+        <v>369.35</v>
       </c>
       <c r="D7" t="n">
-        <v>36.04</v>
+        <v>49.84</v>
       </c>
       <c r="E7" t="n">
-        <v>11.64</v>
+        <v>28.18</v>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>10.56</v>
       </c>
       <c r="G7" t="n">
-        <v>1873870000</v>
+        <v>4466570780000</v>
       </c>
       <c r="H7" t="n">
-        <v>25.42</v>
+        <v>295.48</v>
       </c>
       <c r="I7" t="n">
-        <v>43</v>
+        <v>434.43</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>35.31</v>
+        <v>17.62</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5</v>
+        <v>22.34</v>
       </c>
       <c r="M7" t="n">
-        <v>268.2</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>33.77</v>
+        <v>60.43</v>
       </c>
       <c r="O7" t="n">
-        <v>18.47</v>
+        <v>37.86</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>4.06</v>
+        <v>52.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.67</v>
+        <v>38.87</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="U7" t="n">
-        <v>63.5</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="8">
@@ -969,22 +969,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>250.81</v>
+        <v>259.41</v>
       </c>
       <c r="D8" t="n">
-        <v>63.85</v>
+        <v>65.95</v>
       </c>
       <c r="E8" t="n">
-        <v>101.04</v>
+        <v>104.51</v>
       </c>
       <c r="F8" t="n">
-        <v>34.65</v>
+        <v>35.84</v>
       </c>
       <c r="G8" t="n">
-        <v>46261890000</v>
+        <v>47848160000</v>
       </c>
       <c r="H8" t="n">
-        <v>200.65</v>
+        <v>207.53</v>
       </c>
       <c r="I8" t="n">
         <v>266.44</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.23</v>
+        <v>2.71</v>
       </c>
       <c r="L8" t="n">
         <v>157.02</v>
@@ -1011,7 +1011,7 @@
         <v>0.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="R8" t="n">
         <v>10.33</v>
@@ -1023,76 +1023,76 @@
         <v>1.15</v>
       </c>
       <c r="U8" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>238.55</v>
+        <v>866.67</v>
       </c>
       <c r="D9" t="n">
-        <v>34.76</v>
+        <v>56.29</v>
       </c>
       <c r="E9" t="n">
-        <v>28.51</v>
+        <v>77.48</v>
       </c>
       <c r="F9" t="n">
-        <v>3.45</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2566108470000</v>
+        <v>26594600000</v>
       </c>
       <c r="H9" t="n">
-        <v>190.84</v>
+        <v>693.34</v>
       </c>
       <c r="I9" t="n">
-        <v>317.34</v>
+        <v>956.4299999999999</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33.03</v>
+        <v>10.36</v>
       </c>
       <c r="L9" t="n">
-        <v>16.61</v>
+        <v>91.59</v>
       </c>
       <c r="M9" t="n">
-        <v>75.33</v>
+        <v>141.86</v>
       </c>
       <c r="N9" t="n">
-        <v>50.6</v>
+        <v>22.43</v>
       </c>
       <c r="O9" t="n">
-        <v>12.22</v>
+        <v>12.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="R9" t="n">
-        <v>8.949999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="S9" t="n">
-        <v>66.63</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>61.9</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>382.07</v>
+        <v>393.94</v>
       </c>
       <c r="D10" t="n">
-        <v>41.4</v>
+        <v>45.28</v>
       </c>
       <c r="E10" t="n">
-        <v>63.6</v>
+        <v>65.58</v>
       </c>
       <c r="F10" t="n">
-        <v>24.09</v>
+        <v>24.84</v>
       </c>
       <c r="G10" t="n">
-        <v>1817728660000</v>
+        <v>1874201110000</v>
       </c>
       <c r="H10" t="n">
-        <v>305.66</v>
+        <v>315.15</v>
       </c>
       <c r="I10" t="n">
         <v>524.1799999999999</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>37.19</v>
+        <v>33.06</v>
       </c>
       <c r="L10" t="n">
         <v>47.87</v>
@@ -1161,208 +1161,208 @@
         <v>1.33</v>
       </c>
       <c r="U10" t="n">
-        <v>61.7</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>253.76</v>
+        <v>409.07</v>
       </c>
       <c r="D11" t="n">
-        <v>39.88</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>22.04</v>
+        <v>32.51</v>
       </c>
       <c r="F11" t="n">
-        <v>3.22</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
-        <v>91655590000</v>
+        <v>265121539999</v>
       </c>
       <c r="H11" t="n">
-        <v>203.01</v>
+        <v>327.26</v>
       </c>
       <c r="I11" t="n">
-        <v>371.22</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
+        <v>496.76</v>
       </c>
       <c r="K11" t="n">
-        <v>46.29</v>
+        <v>21.44</v>
       </c>
       <c r="L11" t="n">
-        <v>23.45</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>1095.18</v>
+        <v>281.26</v>
       </c>
       <c r="N11" t="n">
-        <v>13.18</v>
+        <v>19.09</v>
       </c>
       <c r="O11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.67</v>
+        <v>6.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="R11" t="n">
-        <v>6.48</v>
+        <v>53.54</v>
       </c>
       <c r="S11" t="n">
-        <v>73.70999999999999</v>
+        <v>39.86</v>
       </c>
       <c r="T11" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>395.57</v>
+        <v>246.02</v>
       </c>
       <c r="D12" t="n">
-        <v>64.53</v>
+        <v>43.22</v>
       </c>
       <c r="E12" t="n">
-        <v>31.43</v>
+        <v>29.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>3.56</v>
       </c>
       <c r="G12" t="n">
-        <v>256372080000</v>
+        <v>2646464090000</v>
       </c>
       <c r="H12" t="n">
-        <v>316.46</v>
+        <v>196.82</v>
       </c>
       <c r="I12" t="n">
-        <v>496.76</v>
+        <v>317.34</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>25.58</v>
+        <v>28.99</v>
       </c>
       <c r="L12" t="n">
-        <v>87.48999999999999</v>
+        <v>16.61</v>
       </c>
       <c r="M12" t="n">
-        <v>281.26</v>
+        <v>75.33</v>
       </c>
       <c r="N12" t="n">
-        <v>19.09</v>
+        <v>50.6</v>
       </c>
       <c r="O12" t="n">
-        <v>6.27</v>
+        <v>12.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>53.54</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>39.86</v>
+        <v>66.63</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="U12" t="n">
-        <v>60.9</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STRL</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>858.99</v>
+        <v>262.35</v>
       </c>
       <c r="D13" t="n">
-        <v>55.67</v>
+        <v>45.06</v>
       </c>
       <c r="E13" t="n">
-        <v>76.8</v>
+        <v>22.78</v>
       </c>
       <c r="F13" t="n">
-        <v>9.140000000000001</v>
+        <v>3.32</v>
       </c>
       <c r="G13" t="n">
-        <v>26358930000</v>
+        <v>94758220000</v>
       </c>
       <c r="H13" t="n">
-        <v>687.1900000000001</v>
+        <v>209.88</v>
       </c>
       <c r="I13" t="n">
-        <v>956.4299999999999</v>
+        <v>368.94</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11.34</v>
+        <v>40.63</v>
       </c>
       <c r="L13" t="n">
-        <v>91.59</v>
+        <v>23.45</v>
       </c>
       <c r="M13" t="n">
-        <v>141.86</v>
+        <v>1095.18</v>
       </c>
       <c r="N13" t="n">
-        <v>22.43</v>
+        <v>13.18</v>
       </c>
       <c r="O13" t="n">
-        <v>12.02</v>
+        <v>13.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="R13" t="n">
-        <v>2.43</v>
+        <v>6.48</v>
       </c>
       <c r="S13" t="n">
-        <v>93.26000000000001</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="U13" t="n">
-        <v>60.7</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="14">
@@ -1377,22 +1377,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>423.93</v>
+        <v>441.4</v>
       </c>
       <c r="D14" t="n">
-        <v>53.77</v>
+        <v>59.42</v>
       </c>
       <c r="E14" t="n">
-        <v>35.23</v>
+        <v>36.69</v>
       </c>
       <c r="F14" t="n">
-        <v>16.55</v>
+        <v>17.23</v>
       </c>
       <c r="G14" t="n">
-        <v>2198704430000</v>
+        <v>2289312240000</v>
       </c>
       <c r="H14" t="n">
-        <v>339.14</v>
+        <v>353.12</v>
       </c>
       <c r="I14" t="n">
         <v>460.4</v>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>40.49</v>
@@ -1428,10 +1428,10 @@
         <v>15.17</v>
       </c>
       <c r="T14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="U14" t="n">
-        <v>59.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="15">
@@ -1446,22 +1446,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>940.66</v>
+        <v>979.0700000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>44.11</v>
+        <v>50.19</v>
       </c>
       <c r="E15" t="n">
-        <v>27.41</v>
+        <v>28.53</v>
       </c>
       <c r="F15" t="n">
-        <v>6.42</v>
+        <v>6.69</v>
       </c>
       <c r="G15" t="n">
-        <v>252774150000</v>
+        <v>263095690000</v>
       </c>
       <c r="H15" t="n">
-        <v>752.53</v>
+        <v>783.26</v>
       </c>
       <c r="I15" t="n">
         <v>1245.84</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>32.44</v>
+        <v>27.25</v>
       </c>
       <c r="L15" t="n">
         <v>15.98</v>
@@ -1488,7 +1488,7 @@
         <v>0.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="R15" t="n">
         <v>0.15</v>
@@ -1500,340 +1500,346 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>59.6</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>562.92</v>
+        <v>215.74</v>
       </c>
       <c r="D16" t="n">
-        <v>61.39</v>
+        <v>56.51</v>
       </c>
       <c r="E16" t="n">
-        <v>33.6</v>
+        <v>34.82</v>
       </c>
       <c r="F16" t="n">
-        <v>16.48</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>194030180000</v>
+        <v>55423610000</v>
       </c>
       <c r="H16" t="n">
-        <v>450.34</v>
+        <v>172.59</v>
       </c>
       <c r="I16" t="n">
-        <v>552.96</v>
+        <v>263.79</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.77</v>
+        <v>22.27</v>
       </c>
       <c r="L16" t="n">
-        <v>45.47</v>
+        <v>27.65</v>
       </c>
       <c r="M16" t="n">
-        <v>483.37</v>
+        <v>16.52</v>
       </c>
       <c r="N16" t="n">
-        <v>45.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>54.28</v>
+        <v>10.76</v>
       </c>
       <c r="P16" t="n">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>0.51</v>
       </c>
       <c r="R16" t="n">
-        <v>0.95</v>
+        <v>1.92</v>
       </c>
       <c r="S16" t="n">
-        <v>97.73</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>58.7</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1877.61</v>
+        <v>354.18</v>
       </c>
       <c r="D17" t="n">
-        <v>53.21</v>
-      </c>
-      <c r="E17" t="n">
-        <v>54.19</v>
+        <v>56.16</v>
       </c>
       <c r="F17" t="n">
-        <v>6.52</v>
+        <v>10.95</v>
       </c>
       <c r="G17" t="n">
-        <v>66096429999</v>
+        <v>28487380000</v>
       </c>
       <c r="H17" t="n">
-        <v>1502.09</v>
+        <v>283.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2115.29</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
+        <v>399.82</v>
       </c>
       <c r="K17" t="n">
-        <v>12.66</v>
+        <v>12.89</v>
       </c>
       <c r="L17" t="n">
-        <v>56.47</v>
+        <v>25.25</v>
       </c>
       <c r="M17" t="n">
-        <v>120.98</v>
+        <v>111.72</v>
       </c>
       <c r="N17" t="n">
-        <v>24.51</v>
+        <v>71.67</v>
       </c>
       <c r="O17" t="n">
-        <v>12.07</v>
+        <v>-1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>4.01</v>
       </c>
       <c r="S17" t="n">
-        <v>94.91</v>
+        <v>90.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>58.2</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>342.8</v>
+        <v>1952.02</v>
       </c>
       <c r="D18" t="n">
-        <v>53.33</v>
+        <v>58.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>56.34</v>
       </c>
       <c r="F18" t="n">
-        <v>10.59</v>
+        <v>6.78</v>
       </c>
       <c r="G18" t="n">
-        <v>27572060000</v>
+        <v>68715840000</v>
       </c>
       <c r="H18" t="n">
-        <v>274.24</v>
+        <v>1561.62</v>
       </c>
       <c r="I18" t="n">
-        <v>399.82</v>
+        <v>2115.29</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>16.63</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>25.25</v>
+        <v>56.47</v>
       </c>
       <c r="M18" t="n">
-        <v>111.72</v>
+        <v>120.98</v>
       </c>
       <c r="N18" t="n">
-        <v>71.67</v>
+        <v>24.51</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.12</v>
+        <v>12.07</v>
       </c>
       <c r="P18" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>4.01</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>90.66</v>
+        <v>94.91</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="U18" t="n">
-        <v>57.9</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>360.54</v>
+        <v>389.2</v>
       </c>
       <c r="D19" t="n">
-        <v>49.22</v>
+        <v>69.93000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>262.33</v>
       </c>
       <c r="F19" t="n">
-        <v>3.51</v>
+        <v>66.62</v>
       </c>
       <c r="G19" t="n">
-        <v>16366720000</v>
+        <v>66711979999</v>
       </c>
       <c r="H19" t="n">
-        <v>288.43</v>
+        <v>311.36</v>
       </c>
       <c r="I19" t="n">
-        <v>478.62</v>
+        <v>253.06</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>32.75</v>
+        <v>-34.98</v>
       </c>
       <c r="L19" t="n">
-        <v>21.64</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>145.11</v>
+        <v>148.21</v>
       </c>
       <c r="N19" t="n">
-        <v>63.43</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.45</v>
+        <v>26.72</v>
       </c>
       <c r="P19" t="n">
-        <v>6.34</v>
+        <v>0.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>3.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>18.28</v>
       </c>
       <c r="S19" t="n">
-        <v>103.78</v>
+        <v>71.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>367.15</v>
+        <v>49.02</v>
       </c>
       <c r="D20" t="n">
-        <v>66.63</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>247.47</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
-        <v>62.84</v>
+        <v>1.67</v>
       </c>
       <c r="G20" t="n">
-        <v>62932430000</v>
+        <v>64912460000</v>
       </c>
       <c r="H20" t="n">
-        <v>293.72</v>
+        <v>39.22</v>
       </c>
       <c r="I20" t="n">
-        <v>253.06</v>
+        <v>68.59</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-31.07</v>
+        <v>39.92</v>
       </c>
       <c r="L20" t="n">
-        <v>93.40000000000001</v>
+        <v>40.64</v>
       </c>
       <c r="M20" t="n">
-        <v>148.21</v>
+        <v>150.91</v>
       </c>
       <c r="N20" t="n">
-        <v>75.98999999999999</v>
+        <v>31.36</v>
       </c>
       <c r="O20" t="n">
-        <v>26.72</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0.03</v>
+        <v>0.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.83</v>
+        <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>18.28</v>
+        <v>0.38</v>
       </c>
       <c r="S20" t="n">
-        <v>71.3</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>56.1</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="21">
@@ -1848,22 +1854,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>921.5599999999999</v>
+        <v>957.24</v>
       </c>
       <c r="D21" t="n">
-        <v>51.7</v>
+        <v>54.43</v>
       </c>
       <c r="E21" t="n">
-        <v>171.04</v>
+        <v>177.66</v>
       </c>
       <c r="F21" t="n">
-        <v>28.81</v>
+        <v>29.93</v>
       </c>
       <c r="G21" t="n">
-        <v>71697370000</v>
+        <v>74473270000</v>
       </c>
       <c r="H21" t="n">
-        <v>737.25</v>
+        <v>765.79</v>
       </c>
       <c r="I21" t="n">
         <v>1132.81</v>
@@ -1872,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>22.92</v>
+        <v>18.34</v>
       </c>
       <c r="L21" t="n">
         <v>90.12</v>
@@ -1890,7 +1896,7 @@
         <v>1.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R21" t="n">
         <v>2.57</v>
@@ -1902,421 +1908,415 @@
         <v>1.5</v>
       </c>
       <c r="U21" t="n">
-        <v>56.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>184.13</v>
+        <v>311.93</v>
       </c>
       <c r="D22" t="n">
-        <v>42.09</v>
+        <v>48.7</v>
       </c>
       <c r="E22" t="n">
-        <v>31.6</v>
+        <v>78.31</v>
       </c>
       <c r="F22" t="n">
-        <v>7.86</v>
+        <v>11.05</v>
       </c>
       <c r="G22" t="n">
-        <v>529566350000</v>
+        <v>119815070000</v>
       </c>
       <c r="H22" t="n">
-        <v>147.3</v>
+        <v>249.54</v>
       </c>
       <c r="I22" t="n">
-        <v>255.87</v>
+        <v>380.63</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>38.96</v>
+        <v>22.02</v>
       </c>
       <c r="L22" t="n">
-        <v>20.63</v>
+        <v>30.13</v>
       </c>
       <c r="M22" t="n">
-        <v>21.47</v>
+        <v>135.9</v>
       </c>
       <c r="N22" t="n">
-        <v>73.55</v>
+        <v>35</v>
       </c>
       <c r="O22" t="n">
-        <v>25.21</v>
+        <v>14.37</v>
       </c>
       <c r="P22" t="n">
-        <v>3.63</v>
+        <v>0.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="R22" t="n">
-        <v>40.54</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>43.84</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="U22" t="n">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>48.17</v>
+        <v>653.53</v>
       </c>
       <c r="D23" t="n">
-        <v>63.46</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>46.18</v>
+        <v>39.01</v>
       </c>
       <c r="F23" t="n">
-        <v>1.64</v>
+        <v>19.13</v>
       </c>
       <c r="G23" t="n">
-        <v>63786880000</v>
+        <v>225260120000</v>
       </c>
       <c r="H23" t="n">
-        <v>38.54</v>
+        <v>522.8200000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>68.59</v>
+        <v>560</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>42.39</v>
+        <v>-14.31</v>
       </c>
       <c r="L23" t="n">
-        <v>40.64</v>
+        <v>45.47</v>
       </c>
       <c r="M23" t="n">
-        <v>150.91</v>
+        <v>483.37</v>
       </c>
       <c r="N23" t="n">
-        <v>31.36</v>
+        <v>45.39</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>54.28</v>
       </c>
       <c r="P23" t="n">
-        <v>0.84</v>
+        <v>0.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0.38</v>
+        <v>0.95</v>
       </c>
       <c r="S23" t="n">
-        <v>92.45999999999999</v>
+        <v>97.73</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>56</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>218.69</v>
+        <v>192.64</v>
       </c>
       <c r="D24" t="n">
-        <v>60.69</v>
+        <v>46.65</v>
       </c>
       <c r="E24" t="n">
-        <v>35.29</v>
+        <v>33.07</v>
       </c>
       <c r="F24" t="n">
-        <v>3.75</v>
+        <v>8.23</v>
       </c>
       <c r="G24" t="n">
-        <v>56181460000</v>
+        <v>554041490000</v>
       </c>
       <c r="H24" t="n">
-        <v>174.95</v>
+        <v>154.11</v>
       </c>
       <c r="I24" t="n">
-        <v>263.79</v>
+        <v>255.87</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>20.62</v>
+        <v>32.82</v>
       </c>
       <c r="L24" t="n">
-        <v>27.65</v>
+        <v>20.63</v>
       </c>
       <c r="M24" t="n">
-        <v>16.52</v>
+        <v>21.47</v>
       </c>
       <c r="N24" t="n">
-        <v>90.81999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="O24" t="n">
-        <v>10.76</v>
+        <v>25.21</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>40.54</v>
       </c>
       <c r="S24" t="n">
-        <v>92.40000000000001</v>
+        <v>43.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="U24" t="n">
-        <v>55.9</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>302.87</v>
+        <v>104.15</v>
       </c>
       <c r="D25" t="n">
-        <v>44.67</v>
+        <v>48.1</v>
       </c>
       <c r="E25" t="n">
-        <v>76.03</v>
+        <v>61.95</v>
       </c>
       <c r="F25" t="n">
-        <v>10.73</v>
+        <v>7.69</v>
       </c>
       <c r="G25" t="n">
-        <v>116335040000</v>
+        <v>107410730000</v>
       </c>
       <c r="H25" t="n">
-        <v>242.3</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>380.63</v>
+        <v>140.76</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>25.67</v>
+        <v>35.15</v>
       </c>
       <c r="L25" t="n">
-        <v>30.13</v>
+        <v>22.09</v>
       </c>
       <c r="M25" t="n">
-        <v>135.9</v>
+        <v>2.64</v>
       </c>
       <c r="N25" t="n">
-        <v>35</v>
+        <v>76.56</v>
       </c>
       <c r="O25" t="n">
-        <v>14.37</v>
+        <v>12.59</v>
       </c>
       <c r="P25" t="n">
-        <v>0.77</v>
+        <v>0.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>0.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.71</v>
+        <v>0.91</v>
       </c>
       <c r="S25" t="n">
-        <v>84.73999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>55.7</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>232.36</v>
+        <v>386.21</v>
       </c>
       <c r="D26" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="E26" t="n">
-        <v>77.52</v>
+        <v>57.36</v>
       </c>
       <c r="F26" t="n">
-        <v>66.61</v>
+        <v>3.76</v>
       </c>
       <c r="G26" t="n">
-        <v>58473500000</v>
+        <v>17532010000</v>
       </c>
       <c r="H26" t="n">
-        <v>185.89</v>
+        <v>308.97</v>
       </c>
       <c r="I26" t="n">
-        <v>255.29</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
+        <v>478.62</v>
       </c>
       <c r="K26" t="n">
-        <v>9.869999999999999</v>
+        <v>23.93</v>
       </c>
       <c r="L26" t="n">
-        <v>621.52</v>
+        <v>21.64</v>
       </c>
       <c r="M26" t="n">
-        <v>521.4</v>
+        <v>145.11</v>
       </c>
       <c r="N26" t="n">
-        <v>7.48</v>
+        <v>63.43</v>
       </c>
       <c r="O26" t="n">
-        <v>95.27</v>
+        <v>-0.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.31</v>
+        <v>6.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.39</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>19.73</v>
+        <v>1.84</v>
       </c>
       <c r="S26" t="n">
-        <v>50.26</v>
+        <v>103.78</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="U26" t="n">
-        <v>55.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>102.15</v>
+        <v>260.07</v>
       </c>
       <c r="D27" t="n">
-        <v>46.25</v>
+        <v>64.11</v>
       </c>
       <c r="E27" t="n">
-        <v>60.76</v>
+        <v>86.77</v>
       </c>
       <c r="F27" t="n">
-        <v>7.55</v>
+        <v>74.55</v>
       </c>
       <c r="G27" t="n">
-        <v>105348110000</v>
+        <v>65446740000</v>
       </c>
       <c r="H27" t="n">
-        <v>81.72</v>
+        <v>208.06</v>
       </c>
       <c r="I27" t="n">
-        <v>140.63</v>
+        <v>255.29</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>37.67</v>
+        <v>-1.84</v>
       </c>
       <c r="L27" t="n">
-        <v>22.09</v>
+        <v>621.52</v>
       </c>
       <c r="M27" t="n">
-        <v>2.64</v>
+        <v>521.4</v>
       </c>
       <c r="N27" t="n">
-        <v>76.56</v>
+        <v>7.48</v>
       </c>
       <c r="O27" t="n">
-        <v>12.59</v>
+        <v>95.27</v>
       </c>
       <c r="P27" t="n">
-        <v>0.21</v>
+        <v>1.31</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.97</v>
+        <v>4.36</v>
       </c>
       <c r="R27" t="n">
-        <v>0.91</v>
+        <v>19.73</v>
       </c>
       <c r="S27" t="n">
-        <v>86.3</v>
+        <v>50.26</v>
       </c>
       <c r="T27" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>54.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="28">
@@ -2331,22 +2331,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>163.24</v>
+        <v>169.09</v>
       </c>
       <c r="D28" t="n">
-        <v>55.54</v>
+        <v>59.42</v>
       </c>
       <c r="E28" t="n">
-        <v>55.9</v>
+        <v>57.9</v>
       </c>
       <c r="F28" t="n">
-        <v>21.17</v>
+        <v>21.93</v>
       </c>
       <c r="G28" t="n">
-        <v>205552250000</v>
+        <v>212918570000</v>
       </c>
       <c r="H28" t="n">
-        <v>130.59</v>
+        <v>135.27</v>
       </c>
       <c r="I28" t="n">
         <v>189.42</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>16.04</v>
+        <v>12.02</v>
       </c>
       <c r="L28" t="n">
         <v>35.13</v>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R28" t="n">
         <v>17.09</v>
@@ -2385,7 +2385,7 @@
         <v>1.09</v>
       </c>
       <c r="U28" t="n">
-        <v>54.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="29">
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>274.5</v>
+        <v>285.72</v>
       </c>
       <c r="D29" t="n">
-        <v>50.88</v>
+        <v>54.63</v>
       </c>
       <c r="E29" t="n">
-        <v>122.63</v>
+        <v>127.64</v>
       </c>
       <c r="F29" t="n">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="G29" t="n">
-        <v>14497930000</v>
+        <v>15090520000</v>
       </c>
       <c r="H29" t="n">
-        <v>219.6</v>
+        <v>228.58</v>
       </c>
       <c r="I29" t="n">
         <v>351.75</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>28.14</v>
+        <v>23.11</v>
       </c>
       <c r="L29" t="n">
         <v>47.47</v>
@@ -2454,208 +2454,208 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>53.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>127.19</v>
+        <v>130.42</v>
       </c>
       <c r="D30" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="E30" t="n">
-        <v>89.47</v>
+        <v>43.4</v>
       </c>
       <c r="F30" t="n">
-        <v>6.44</v>
+        <v>6.65</v>
       </c>
       <c r="G30" t="n">
-        <v>10418350000</v>
+        <v>21090160000</v>
       </c>
       <c r="H30" t="n">
-        <v>101.75</v>
+        <v>104.34</v>
       </c>
       <c r="I30" t="n">
-        <v>149.75</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
+        <v>192.67</v>
       </c>
       <c r="K30" t="n">
-        <v>17.74</v>
+        <v>47.73</v>
       </c>
       <c r="L30" t="n">
-        <v>54.3</v>
+        <v>25.43</v>
       </c>
       <c r="M30" t="n">
-        <v>36.23</v>
+        <v>-224.81</v>
       </c>
       <c r="N30" t="n">
-        <v>24.54</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>7.3</v>
+        <v>-2.44</v>
       </c>
       <c r="P30" t="n">
-        <v>0.49</v>
+        <v>0.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.41</v>
+        <v>0.97</v>
       </c>
       <c r="R30" t="n">
-        <v>16.68</v>
+        <v>35.18</v>
       </c>
       <c r="S30" t="n">
-        <v>88.28</v>
+        <v>54.21</v>
       </c>
       <c r="T30" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="U30" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>823.05</v>
+        <v>45.47</v>
       </c>
       <c r="D31" t="n">
-        <v>45.54</v>
+        <v>52.34</v>
       </c>
       <c r="E31" t="n">
-        <v>27.54</v>
+        <v>18.87</v>
       </c>
       <c r="F31" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="G31" t="n">
-        <v>36576570000</v>
+        <v>2248980000</v>
       </c>
       <c r="H31" t="n">
-        <v>658.4400000000001</v>
+        <v>36.38</v>
       </c>
       <c r="I31" t="n">
-        <v>1000.14</v>
+        <v>59</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>21.52</v>
+        <v>29.76</v>
       </c>
       <c r="L31" t="n">
-        <v>19.67</v>
+        <v>11.04</v>
       </c>
       <c r="M31" t="n">
-        <v>30.04</v>
+        <v>-10.25</v>
       </c>
       <c r="N31" t="n">
-        <v>19.29</v>
+        <v>62.66</v>
       </c>
       <c r="O31" t="n">
-        <v>7.54</v>
+        <v>12.36</v>
       </c>
       <c r="P31" t="n">
-        <v>0.13</v>
+        <v>0.66</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="R31" t="n">
-        <v>0.74</v>
+        <v>5.93</v>
       </c>
       <c r="S31" t="n">
-        <v>96.41</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="T31" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>52.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>129.52</v>
+        <v>184.9</v>
       </c>
       <c r="D32" t="n">
-        <v>42.78</v>
+        <v>45.23</v>
+      </c>
+      <c r="E32" t="n">
+        <v>48.91</v>
       </c>
       <c r="F32" t="n">
-        <v>6.6</v>
+        <v>10.12</v>
       </c>
       <c r="G32" t="n">
-        <v>20944620000</v>
+        <v>64974980000</v>
       </c>
       <c r="H32" t="n">
-        <v>103.62</v>
+        <v>147.92</v>
       </c>
       <c r="I32" t="n">
-        <v>192.67</v>
+        <v>219.17</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>48.76</v>
+        <v>18.53</v>
       </c>
       <c r="L32" t="n">
-        <v>25.43</v>
+        <v>16.16</v>
       </c>
       <c r="M32" t="n">
-        <v>-224.81</v>
+        <v>67.62</v>
       </c>
       <c r="N32" t="n">
-        <v>76.29000000000001</v>
+        <v>25.66</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.44</v>
+        <v>20.83</v>
       </c>
       <c r="P32" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="R32" t="n">
-        <v>35.18</v>
+        <v>0.03</v>
       </c>
       <c r="S32" t="n">
-        <v>54.21</v>
+        <v>99.48</v>
       </c>
       <c r="T32" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="U32" t="n">
-        <v>52.6</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="33">
@@ -2670,22 +2670,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>110.08</v>
+        <v>110.97</v>
       </c>
       <c r="D33" t="n">
-        <v>46.76</v>
+        <v>49.31</v>
       </c>
       <c r="E33" t="n">
-        <v>27.35</v>
+        <v>27.57</v>
       </c>
       <c r="F33" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G33" t="n">
-        <v>26165300000</v>
+        <v>26376850000</v>
       </c>
       <c r="H33" t="n">
-        <v>88.06</v>
+        <v>88.78</v>
       </c>
       <c r="I33" t="n">
         <v>152.31</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>38.36</v>
+        <v>37.25</v>
       </c>
       <c r="L33" t="n">
         <v>2.71</v>
@@ -2724,214 +2724,214 @@
         <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>MWA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>184.2</v>
+        <v>25.79</v>
       </c>
       <c r="D34" t="n">
-        <v>44.09</v>
+        <v>49.14</v>
       </c>
       <c r="E34" t="n">
-        <v>48.72</v>
+        <v>19.57</v>
       </c>
       <c r="F34" t="n">
-        <v>10.09</v>
+        <v>2.76</v>
       </c>
       <c r="G34" t="n">
-        <v>64729000000</v>
+        <v>4035390000</v>
       </c>
       <c r="H34" t="n">
-        <v>147.36</v>
+        <v>20.63</v>
       </c>
       <c r="I34" t="n">
-        <v>219.17</v>
+        <v>32.2</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>18.98</v>
+        <v>24.85</v>
       </c>
       <c r="L34" t="n">
-        <v>16.16</v>
+        <v>5.52</v>
       </c>
       <c r="M34" t="n">
-        <v>67.62</v>
+        <v>15.29</v>
       </c>
       <c r="N34" t="n">
-        <v>25.66</v>
+        <v>37.58</v>
       </c>
       <c r="O34" t="n">
-        <v>20.83</v>
+        <v>14.17</v>
       </c>
       <c r="P34" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0.03</v>
+        <v>0.91</v>
       </c>
       <c r="S34" t="n">
-        <v>99.48</v>
+        <v>95.95</v>
       </c>
       <c r="T34" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="U34" t="n">
-        <v>52.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>148.02</v>
+        <v>131.26</v>
       </c>
       <c r="D35" t="n">
-        <v>47.05</v>
+        <v>52.38</v>
       </c>
       <c r="E35" t="n">
-        <v>24.72</v>
+        <v>92.33</v>
       </c>
       <c r="F35" t="n">
-        <v>3.03</v>
+        <v>6.65</v>
       </c>
       <c r="G35" t="n">
-        <v>49909750000</v>
+        <v>10751730000</v>
       </c>
       <c r="H35" t="n">
-        <v>118.42</v>
+        <v>105.01</v>
       </c>
       <c r="I35" t="n">
-        <v>233.19</v>
+        <v>149.75</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>57.54</v>
+        <v>14.09</v>
       </c>
       <c r="L35" t="n">
-        <v>-10</v>
+        <v>54.3</v>
       </c>
       <c r="M35" t="n">
-        <v>407.29</v>
+        <v>36.23</v>
       </c>
       <c r="N35" t="n">
-        <v>14.65</v>
+        <v>24.54</v>
       </c>
       <c r="O35" t="n">
-        <v>12.45</v>
+        <v>7.3</v>
       </c>
       <c r="P35" t="n">
-        <v>3.56</v>
+        <v>0.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R35" t="n">
-        <v>0.97</v>
+        <v>16.68</v>
       </c>
       <c r="S35" t="n">
-        <v>90.03</v>
+        <v>88.28</v>
       </c>
       <c r="T35" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="U35" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MWA</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25.82</v>
+        <v>842.3</v>
       </c>
       <c r="D36" t="n">
-        <v>49.5</v>
+        <v>50.31</v>
       </c>
       <c r="E36" t="n">
-        <v>19.59</v>
+        <v>28.19</v>
       </c>
       <c r="F36" t="n">
-        <v>2.76</v>
+        <v>2.11</v>
       </c>
       <c r="G36" t="n">
-        <v>4040080000</v>
+        <v>37432050000</v>
       </c>
       <c r="H36" t="n">
-        <v>20.66</v>
+        <v>673.84</v>
       </c>
       <c r="I36" t="n">
-        <v>32.2</v>
+        <v>1000.14</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>24.71</v>
+        <v>18.74</v>
       </c>
       <c r="L36" t="n">
-        <v>5.52</v>
+        <v>19.67</v>
       </c>
       <c r="M36" t="n">
-        <v>15.29</v>
+        <v>30.04</v>
       </c>
       <c r="N36" t="n">
-        <v>37.58</v>
+        <v>19.29</v>
       </c>
       <c r="O36" t="n">
-        <v>14.17</v>
+        <v>7.54</v>
       </c>
       <c r="P36" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="R36" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="S36" t="n">
-        <v>95.95</v>
+        <v>96.41</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="37">
@@ -2946,31 +2946,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>229.9</v>
+        <v>233.09</v>
       </c>
       <c r="D37" t="n">
-        <v>57.63</v>
+        <v>59.08</v>
       </c>
       <c r="E37" t="n">
-        <v>613.5599999999999</v>
+        <v>622.0700000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>22.29</v>
+        <v>22.6</v>
       </c>
       <c r="G37" t="n">
-        <v>81835250000</v>
+        <v>82970760000</v>
       </c>
       <c r="H37" t="n">
-        <v>183.92</v>
+        <v>186.47</v>
       </c>
       <c r="I37" t="n">
-        <v>236.41</v>
+        <v>238.91</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="L37" t="n">
         <v>32.15</v>
@@ -2997,412 +2997,403 @@
         <v>81.39</v>
       </c>
       <c r="T37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U37" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>260.22</v>
+        <v>126.28</v>
       </c>
       <c r="D38" t="n">
-        <v>48.3</v>
+        <v>52.38</v>
+      </c>
+      <c r="E38" t="n">
+        <v>138.66</v>
       </c>
       <c r="F38" t="n">
-        <v>30.22</v>
+        <v>5.19</v>
       </c>
       <c r="G38" t="n">
-        <v>74017990000</v>
+        <v>37571420000</v>
       </c>
       <c r="H38" t="n">
-        <v>208.18</v>
+        <v>101.02</v>
       </c>
       <c r="I38" t="n">
-        <v>270.51</v>
+        <v>131.55</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>4.17</v>
       </c>
       <c r="L38" t="n">
-        <v>130.37</v>
+        <v>21.58</v>
       </c>
       <c r="M38" t="n">
-        <v>313.73</v>
+        <v>787.08</v>
       </c>
       <c r="N38" t="n">
-        <v>31.08</v>
+        <v>40.39</v>
       </c>
       <c r="O38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.77</v>
+        <v>1.22</v>
       </c>
       <c r="R38" t="n">
-        <v>6.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>85.98999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="T38" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="U38" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>127.24</v>
+        <v>153.52</v>
       </c>
       <c r="D39" t="n">
-        <v>54.3</v>
+        <v>52.31</v>
       </c>
       <c r="E39" t="n">
-        <v>139.72</v>
+        <v>25.63</v>
       </c>
       <c r="F39" t="n">
-        <v>5.23</v>
+        <v>3.15</v>
       </c>
       <c r="G39" t="n">
-        <v>37857040000</v>
+        <v>51764250000</v>
       </c>
       <c r="H39" t="n">
-        <v>101.79</v>
+        <v>122.82</v>
       </c>
       <c r="I39" t="n">
-        <v>131.55</v>
+        <v>233.38</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>3.39</v>
+        <v>52.02</v>
       </c>
       <c r="L39" t="n">
-        <v>21.58</v>
+        <v>-10</v>
       </c>
       <c r="M39" t="n">
-        <v>787.08</v>
+        <v>407.29</v>
       </c>
       <c r="N39" t="n">
-        <v>40.39</v>
+        <v>14.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.76</v>
+        <v>12.45</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="R39" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="S39" t="n">
-        <v>87.14</v>
+        <v>90.03</v>
       </c>
       <c r="T39" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="U39" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46.65</v>
+        <v>274.5</v>
       </c>
       <c r="D40" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="E40" t="n">
-        <v>19.36</v>
+        <v>52.3</v>
       </c>
       <c r="F40" t="n">
-        <v>2.22</v>
+        <v>31.88</v>
       </c>
       <c r="G40" t="n">
-        <v>2307340000</v>
+        <v>78079850000</v>
       </c>
       <c r="H40" t="n">
-        <v>37.32</v>
+        <v>219.6</v>
       </c>
       <c r="I40" t="n">
-        <v>59</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
+        <v>270.51</v>
       </c>
       <c r="K40" t="n">
-        <v>26.47</v>
+        <v>-1.45</v>
       </c>
       <c r="L40" t="n">
-        <v>11.04</v>
+        <v>130.37</v>
       </c>
       <c r="M40" t="n">
-        <v>-10.25</v>
+        <v>313.73</v>
       </c>
       <c r="N40" t="n">
-        <v>62.66</v>
+        <v>31.08</v>
       </c>
       <c r="O40" t="n">
-        <v>12.36</v>
+        <v>0.25</v>
       </c>
       <c r="P40" t="n">
-        <v>0.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.77</v>
+        <v>3.76</v>
       </c>
       <c r="R40" t="n">
-        <v>5.93</v>
+        <v>6.31</v>
       </c>
       <c r="S40" t="n">
-        <v>97.51000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="T40" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="U40" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>385.03</v>
+        <v>146.06</v>
       </c>
       <c r="D41" t="n">
-        <v>53.61</v>
+        <v>55.98</v>
       </c>
       <c r="E41" t="n">
-        <v>183.82</v>
+        <v>26.12</v>
       </c>
       <c r="F41" t="n">
-        <v>11.41</v>
+        <v>3.65</v>
       </c>
       <c r="G41" t="n">
-        <v>75327010000</v>
+        <v>89113480000</v>
       </c>
       <c r="H41" t="n">
-        <v>308.02</v>
+        <v>116.85</v>
       </c>
       <c r="I41" t="n">
-        <v>388.09</v>
+        <v>157.1</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.79</v>
+        <v>7.56</v>
       </c>
       <c r="L41" t="n">
-        <v>20.55</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>990.95</v>
+        <v>38.05</v>
       </c>
       <c r="N41" t="n">
-        <v>37.93</v>
+        <v>36.49</v>
       </c>
       <c r="O41" t="n">
-        <v>6.07</v>
+        <v>14.45</v>
       </c>
       <c r="P41" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="R41" t="n">
-        <v>4.45</v>
+        <v>0.34</v>
       </c>
       <c r="S41" t="n">
-        <v>88.13</v>
+        <v>92.83</v>
       </c>
       <c r="T41" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="U41" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>144.96</v>
+        <v>692.91</v>
       </c>
       <c r="D42" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="E42" t="n">
-        <v>25.93</v>
+        <v>60.21</v>
       </c>
       <c r="F42" t="n">
-        <v>3.62</v>
+        <v>34.63</v>
       </c>
       <c r="G42" t="n">
-        <v>88442360000</v>
+        <v>176390510000</v>
       </c>
       <c r="H42" t="n">
-        <v>115.97</v>
+        <v>554.33</v>
       </c>
       <c r="I42" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
+        <v>720.9299999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>8.369999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="L42" t="n">
-        <v>8.210000000000001</v>
+        <v>25.57</v>
       </c>
       <c r="M42" t="n">
-        <v>38.05</v>
+        <v>124.28</v>
       </c>
       <c r="N42" t="n">
-        <v>36.49</v>
+        <v>74.89</v>
       </c>
       <c r="O42" t="n">
-        <v>14.45</v>
+        <v>-0.89</v>
       </c>
       <c r="P42" t="n">
-        <v>0.7</v>
+        <v>0.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="R42" t="n">
-        <v>0.34</v>
+        <v>3.53</v>
       </c>
       <c r="S42" t="n">
-        <v>92.83</v>
+        <v>71.22</v>
       </c>
       <c r="T42" t="n">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="U42" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>RYAN</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>511.57</v>
+        <v>35.34</v>
       </c>
       <c r="D43" t="n">
-        <v>60.45</v>
+        <v>59.61</v>
       </c>
       <c r="E43" t="n">
-        <v>167.9</v>
+        <v>48.02</v>
       </c>
       <c r="F43" t="n">
-        <v>22.27</v>
+        <v>2.94</v>
       </c>
       <c r="G43" t="n">
-        <v>834166350000</v>
+        <v>9317720000</v>
       </c>
       <c r="H43" t="n">
-        <v>409.26</v>
+        <v>28.27</v>
       </c>
       <c r="I43" t="n">
-        <v>494.82</v>
+        <v>41.56</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.27</v>
+        <v>17.6</v>
       </c>
       <c r="L43" t="n">
-        <v>37.85</v>
+        <v>14.57</v>
       </c>
       <c r="M43" t="n">
-        <v>92.25</v>
-      </c>
-      <c r="N43" t="n">
-        <v>47.09</v>
+        <v>158.3</v>
       </c>
       <c r="O43" t="n">
-        <v>13.37</v>
+        <v>3.43</v>
       </c>
       <c r="P43" t="n">
-        <v>0.06</v>
+        <v>5.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.49</v>
+        <v>0.6</v>
       </c>
       <c r="R43" t="n">
-        <v>0.49</v>
+        <v>12.64</v>
       </c>
       <c r="S43" t="n">
-        <v>68.29000000000001</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>1.49</v>
+        <v>2.29</v>
       </c>
       <c r="U43" t="n">
-        <v>49.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="44">
@@ -3413,260 +3404,272 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>682.8</v>
+        <v>118.12</v>
       </c>
       <c r="D44" t="n">
-        <v>58.72</v>
+        <v>61.34</v>
+      </c>
+      <c r="E44" t="n">
+        <v>85.79000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>34.12</v>
+        <v>6.85</v>
       </c>
       <c r="G44" t="n">
-        <v>173816860000</v>
+        <v>20530130000</v>
       </c>
       <c r="H44" t="n">
-        <v>546.24</v>
+        <v>94.5</v>
       </c>
       <c r="I44" t="n">
-        <v>720.9299999999999</v>
+        <v>119.83</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>5.58</v>
+        <v>1.45</v>
       </c>
       <c r="L44" t="n">
-        <v>25.57</v>
+        <v>11.19</v>
       </c>
       <c r="M44" t="n">
-        <v>124.28</v>
+        <v>20.1</v>
       </c>
       <c r="N44" t="n">
-        <v>74.89</v>
+        <v>77.44</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.89</v>
+        <v>8.24</v>
       </c>
       <c r="P44" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.26</v>
+        <v>0.8</v>
       </c>
       <c r="R44" t="n">
-        <v>3.53</v>
+        <v>5.01</v>
       </c>
       <c r="S44" t="n">
-        <v>71.22</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="T44" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="U44" t="n">
-        <v>49.2</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>100.55</v>
+        <v>413.84</v>
       </c>
       <c r="D45" t="n">
-        <v>45.24</v>
+        <v>59.02</v>
+      </c>
+      <c r="E45" t="n">
+        <v>197.57</v>
       </c>
       <c r="F45" t="n">
-        <v>8.81</v>
+        <v>12.26</v>
       </c>
       <c r="G45" t="n">
-        <v>54857100000</v>
+        <v>80963380000</v>
       </c>
       <c r="H45" t="n">
-        <v>80.44</v>
+        <v>331.07</v>
       </c>
       <c r="I45" t="n">
-        <v>138.91</v>
+        <v>388.09</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>38.15</v>
+        <v>-6.22</v>
       </c>
       <c r="L45" t="n">
-        <v>111.69</v>
+        <v>20.55</v>
       </c>
       <c r="M45" t="n">
-        <v>-76.43000000000001</v>
+        <v>990.95</v>
       </c>
       <c r="N45" t="n">
-        <v>34.82</v>
+        <v>37.93</v>
       </c>
       <c r="O45" t="n">
-        <v>-25.58</v>
+        <v>6.07</v>
       </c>
       <c r="P45" t="n">
-        <v>7.39</v>
+        <v>0.32</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>2.03</v>
       </c>
       <c r="R45" t="n">
-        <v>38.09</v>
+        <v>4.45</v>
       </c>
       <c r="S45" t="n">
-        <v>44.69</v>
+        <v>88.13</v>
       </c>
       <c r="T45" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="U45" t="n">
-        <v>49</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Electrical Infrastructure</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>391.39</v>
+        <v>169</v>
       </c>
       <c r="D46" t="n">
-        <v>46.69</v>
+        <v>56.17</v>
       </c>
       <c r="E46" t="n">
-        <v>38.26</v>
+        <v>56.83</v>
       </c>
       <c r="F46" t="n">
-        <v>5.33</v>
+        <v>6.32</v>
       </c>
       <c r="G46" t="n">
-        <v>151976740000</v>
+        <v>27330760000</v>
       </c>
       <c r="H46" t="n">
-        <v>313.11</v>
+        <v>135.2</v>
       </c>
       <c r="I46" t="n">
-        <v>463.71</v>
+        <v>193.29</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>18.48</v>
+        <v>14.37</v>
       </c>
       <c r="L46" t="n">
-        <v>16.84</v>
+        <v>53.47</v>
       </c>
       <c r="M46" t="n">
-        <v>-9.15</v>
+        <v>-60.21</v>
       </c>
       <c r="N46" t="n">
-        <v>36.89</v>
+        <v>37.01</v>
       </c>
       <c r="O46" t="n">
-        <v>13.99</v>
+        <v>11.26</v>
       </c>
       <c r="P46" t="n">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="S46" t="n">
-        <v>86.56999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="T46" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="U46" t="n">
-        <v>48.7</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>116.29</v>
+        <v>547.26</v>
       </c>
       <c r="D47" t="n">
-        <v>60.11</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>84.45999999999999</v>
+        <v>179.61</v>
       </c>
       <c r="F47" t="n">
-        <v>6.75</v>
+        <v>23.83</v>
       </c>
       <c r="G47" t="n">
-        <v>20212060000</v>
+        <v>892362490000</v>
       </c>
       <c r="H47" t="n">
-        <v>93.03</v>
+        <v>437.81</v>
       </c>
       <c r="I47" t="n">
-        <v>119.83</v>
+        <v>494.82</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>3.04</v>
+        <v>-9.58</v>
       </c>
       <c r="L47" t="n">
-        <v>11.19</v>
+        <v>37.85</v>
       </c>
       <c r="M47" t="n">
-        <v>20.1</v>
+        <v>92.25</v>
       </c>
       <c r="N47" t="n">
-        <v>77.44</v>
+        <v>47.09</v>
       </c>
       <c r="O47" t="n">
-        <v>8.24</v>
+        <v>13.37</v>
       </c>
       <c r="P47" t="n">
         <v>0.06</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.8</v>
+        <v>2.49</v>
       </c>
       <c r="R47" t="n">
-        <v>5.01</v>
+        <v>0.49</v>
       </c>
       <c r="S47" t="n">
-        <v>93.40000000000001</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T47" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="U47" t="n">
-        <v>48.6</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="48">
@@ -3677,476 +3680,473 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>165.84</v>
+        <v>724.35</v>
       </c>
       <c r="D48" t="n">
-        <v>53.27</v>
+        <v>55.05</v>
       </c>
       <c r="E48" t="n">
-        <v>55.77</v>
+        <v>99.38</v>
       </c>
       <c r="F48" t="n">
-        <v>6.2</v>
+        <v>3.61</v>
       </c>
       <c r="G48" t="n">
-        <v>26819720000</v>
+        <v>108696070000</v>
       </c>
       <c r="H48" t="n">
-        <v>132.67</v>
+        <v>579.48</v>
       </c>
       <c r="I48" t="n">
-        <v>193.29</v>
+        <v>802.79</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>16.55</v>
+        <v>10.83</v>
       </c>
       <c r="L48" t="n">
-        <v>53.47</v>
+        <v>26.33</v>
       </c>
       <c r="M48" t="n">
-        <v>-60.21</v>
+        <v>51.81</v>
       </c>
       <c r="N48" t="n">
-        <v>37.01</v>
+        <v>13.3</v>
       </c>
       <c r="O48" t="n">
-        <v>11.26</v>
+        <v>3.67</v>
       </c>
       <c r="P48" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="R48" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S48" t="n">
-        <v>93.67</v>
+        <v>93.23</v>
       </c>
       <c r="T48" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="U48" t="n">
-        <v>48.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>707.74</v>
+        <v>41.19</v>
       </c>
       <c r="D49" t="n">
-        <v>51.59</v>
+        <v>52.92</v>
       </c>
       <c r="E49" t="n">
-        <v>97.09999999999999</v>
+        <v>76.83</v>
       </c>
       <c r="F49" t="n">
-        <v>3.53</v>
+        <v>5.95</v>
       </c>
       <c r="G49" t="n">
-        <v>106203570000</v>
+        <v>12005890000</v>
       </c>
       <c r="H49" t="n">
-        <v>566.1900000000001</v>
+        <v>32.95</v>
       </c>
       <c r="I49" t="n">
-        <v>802.79</v>
+        <v>43.97</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>13.43</v>
+        <v>6.75</v>
       </c>
       <c r="L49" t="n">
-        <v>26.33</v>
+        <v>19.44</v>
       </c>
       <c r="M49" t="n">
-        <v>51.81</v>
+        <v>-54.84</v>
       </c>
       <c r="N49" t="n">
-        <v>13.3</v>
+        <v>81.56</v>
       </c>
       <c r="O49" t="n">
-        <v>3.67</v>
+        <v>8.06</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7</v>
+        <v>0.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="R49" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="S49" t="n">
-        <v>93.23</v>
+        <v>101.95</v>
       </c>
       <c r="T49" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="U49" t="n">
-        <v>48.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RYAN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35.64</v>
+        <v>106.71</v>
       </c>
       <c r="D50" t="n">
-        <v>61.18</v>
-      </c>
-      <c r="E50" t="n">
-        <v>48.43</v>
+        <v>50.51</v>
       </c>
       <c r="F50" t="n">
-        <v>2.97</v>
+        <v>9.35</v>
       </c>
       <c r="G50" t="n">
-        <v>9396820000</v>
+        <v>58217810000</v>
       </c>
       <c r="H50" t="n">
-        <v>28.51</v>
+        <v>85.37</v>
       </c>
       <c r="I50" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
+        <v>138.91</v>
       </c>
       <c r="K50" t="n">
-        <v>16.61</v>
+        <v>30.18</v>
       </c>
       <c r="L50" t="n">
-        <v>14.57</v>
+        <v>111.69</v>
       </c>
       <c r="M50" t="n">
-        <v>158.3</v>
+        <v>-76.43000000000001</v>
+      </c>
+      <c r="N50" t="n">
+        <v>34.82</v>
       </c>
       <c r="O50" t="n">
-        <v>3.43</v>
+        <v>-25.58</v>
       </c>
       <c r="P50" t="n">
-        <v>5.88</v>
+        <v>7.39</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.61</v>
+        <v>6.99</v>
       </c>
       <c r="R50" t="n">
-        <v>12.64</v>
+        <v>38.09</v>
       </c>
       <c r="S50" t="n">
-        <v>87.93000000000001</v>
+        <v>44.69</v>
       </c>
       <c r="T50" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="U50" t="n">
-        <v>48</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Electrical Infrastructure</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>40.75</v>
+        <v>407.06</v>
       </c>
       <c r="D51" t="n">
-        <v>51.18</v>
+        <v>52.88</v>
       </c>
       <c r="E51" t="n">
-        <v>76.01000000000001</v>
+        <v>39.79</v>
       </c>
       <c r="F51" t="n">
-        <v>5.88</v>
+        <v>5.54</v>
       </c>
       <c r="G51" t="n">
-        <v>11877640000</v>
+        <v>158061390000</v>
       </c>
       <c r="H51" t="n">
-        <v>32.6</v>
+        <v>325.65</v>
       </c>
       <c r="I51" t="n">
-        <v>43.91</v>
+        <v>463.71</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>7.75</v>
+        <v>13.92</v>
       </c>
       <c r="L51" t="n">
-        <v>19.44</v>
+        <v>16.84</v>
       </c>
       <c r="M51" t="n">
-        <v>-54.84</v>
+        <v>-9.15</v>
       </c>
       <c r="N51" t="n">
-        <v>81.56</v>
+        <v>36.89</v>
       </c>
       <c r="O51" t="n">
-        <v>8.06</v>
+        <v>13.99</v>
       </c>
       <c r="P51" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="R51" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="S51" t="n">
-        <v>101.95</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="T51" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="U51" t="n">
-        <v>47.7</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>931.04</v>
+        <v>411.72</v>
       </c>
       <c r="D52" t="n">
-        <v>64.28</v>
+        <v>49.22</v>
       </c>
       <c r="E52" t="n">
-        <v>88.38</v>
+        <v>33.19</v>
       </c>
       <c r="F52" t="n">
-        <v>18.96</v>
+        <v>5.76</v>
       </c>
       <c r="G52" t="n">
-        <v>208766150000</v>
+        <v>68343700000</v>
       </c>
       <c r="H52" t="n">
-        <v>744.83</v>
+        <v>329.38</v>
       </c>
       <c r="I52" t="n">
-        <v>891.36</v>
+        <v>509.2</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.26</v>
+        <v>23.68</v>
       </c>
       <c r="L52" t="n">
-        <v>44.07</v>
+        <v>7.36</v>
       </c>
       <c r="M52" t="n">
-        <v>107.51</v>
+        <v>-13.97</v>
       </c>
       <c r="N52" t="n">
-        <v>41.54</v>
+        <v>49.07</v>
       </c>
       <c r="O52" t="n">
-        <v>21.6</v>
+        <v>17.61</v>
       </c>
       <c r="P52" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.08</v>
+        <v>0.88</v>
       </c>
       <c r="R52" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="S52" t="n">
-        <v>84.98</v>
+        <v>88.89</v>
       </c>
       <c r="T52" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="U52" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TSEM</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>262.92</v>
+        <v>1018.8</v>
       </c>
       <c r="D53" t="n">
-        <v>55.22</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>122.12</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>18.12</v>
+        <v>20.75</v>
       </c>
       <c r="G53" t="n">
-        <v>29383050000</v>
+        <v>228444490000</v>
       </c>
       <c r="H53" t="n">
-        <v>210.34</v>
+        <v>815.04</v>
       </c>
       <c r="I53" t="n">
-        <v>313.83</v>
+        <v>903.55</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>19.36</v>
+        <v>-11.31</v>
       </c>
       <c r="L53" t="n">
-        <v>15.48</v>
+        <v>44.07</v>
       </c>
       <c r="M53" t="n">
-        <v>60.32</v>
+        <v>107.51</v>
       </c>
       <c r="N53" t="n">
-        <v>24.77</v>
+        <v>41.54</v>
       </c>
       <c r="O53" t="n">
-        <v>15.13</v>
+        <v>21.6</v>
       </c>
       <c r="P53" t="n">
-        <v>0.05</v>
+        <v>3.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.87</v>
+        <v>2.07</v>
       </c>
       <c r="R53" t="n">
-        <v>6.3</v>
+        <v>0.27</v>
       </c>
       <c r="S53" t="n">
-        <v>70.56</v>
+        <v>84.98</v>
       </c>
       <c r="T53" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="U53" t="n">
-        <v>46.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>412.25</v>
+        <v>286.86</v>
       </c>
       <c r="D54" t="n">
-        <v>49.64</v>
+        <v>61.5</v>
       </c>
       <c r="E54" t="n">
-        <v>33.24</v>
+        <v>133.24</v>
       </c>
       <c r="F54" t="n">
-        <v>5.77</v>
+        <v>19.77</v>
       </c>
       <c r="G54" t="n">
-        <v>68431679999</v>
+        <v>32058500000</v>
       </c>
       <c r="H54" t="n">
-        <v>329.8</v>
+        <v>229.49</v>
       </c>
       <c r="I54" t="n">
-        <v>509.2</v>
+        <v>313.83</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>23.52</v>
+        <v>9.4</v>
       </c>
       <c r="L54" t="n">
-        <v>7.36</v>
+        <v>15.48</v>
       </c>
       <c r="M54" t="n">
-        <v>-13.97</v>
+        <v>60.32</v>
       </c>
       <c r="N54" t="n">
-        <v>49.07</v>
+        <v>24.77</v>
       </c>
       <c r="O54" t="n">
-        <v>17.61</v>
+        <v>15.13</v>
       </c>
       <c r="P54" t="n">
-        <v>3.77</v>
+        <v>0.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="R54" t="n">
-        <v>0.41</v>
+        <v>6.3</v>
       </c>
       <c r="S54" t="n">
-        <v>88.89</v>
+        <v>70.56</v>
       </c>
       <c r="T54" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U54" t="n">
-        <v>46.1</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="55">
@@ -4157,59 +4157,65 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.7</v>
+        <v>1064.38</v>
       </c>
       <c r="D55" t="n">
-        <v>51.53</v>
+        <v>50.18</v>
+      </c>
+      <c r="E55" t="n">
+        <v>73.61</v>
       </c>
       <c r="F55" t="n">
-        <v>34.33</v>
+        <v>11.12</v>
       </c>
       <c r="G55" t="n">
-        <v>12202360000</v>
+        <v>104973680000</v>
       </c>
       <c r="H55" t="n">
-        <v>34.16</v>
+        <v>851.5</v>
       </c>
       <c r="I55" t="n">
-        <v>70.75</v>
+        <v>1204.61</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>65.69</v>
+        <v>13.17</v>
       </c>
       <c r="L55" t="n">
-        <v>139.29</v>
+        <v>9.84</v>
       </c>
       <c r="M55" t="n">
-        <v>-120.39</v>
+        <v>19.96</v>
       </c>
       <c r="N55" t="n">
-        <v>27.07</v>
+        <v>27.71</v>
       </c>
       <c r="O55" t="n">
-        <v>-54.12</v>
+        <v>15.07</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.66</v>
+        <v>0.97</v>
       </c>
       <c r="R55" t="n">
-        <v>9.48</v>
+        <v>0.33</v>
       </c>
       <c r="S55" t="n">
-        <v>70.27</v>
+        <v>99.02</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="U55" t="n">
-        <v>45.2</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="56">
@@ -4224,31 +4230,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>366.81</v>
+        <v>388.92</v>
       </c>
       <c r="D56" t="n">
-        <v>68.54000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="E56" t="n">
-        <v>69.23</v>
+        <v>73.41</v>
       </c>
       <c r="F56" t="n">
-        <v>21.16</v>
+        <v>22.43</v>
       </c>
       <c r="G56" t="n">
-        <v>458721960000</v>
+        <v>486372110000</v>
       </c>
       <c r="H56" t="n">
-        <v>293.45</v>
+        <v>311.14</v>
       </c>
       <c r="I56" t="n">
-        <v>330.97</v>
+        <v>333.38</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.77</v>
+        <v>-14.28</v>
       </c>
       <c r="L56" t="n">
         <v>23.76</v>
@@ -4266,7 +4272,7 @@
         <v>0.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R56" t="n">
         <v>0.34</v>
@@ -4278,214 +4284,208 @@
         <v>1.57</v>
       </c>
       <c r="U56" t="n">
-        <v>44.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1055.85</v>
+        <v>585.78</v>
       </c>
       <c r="D57" t="n">
-        <v>46.94</v>
+        <v>76.11</v>
       </c>
       <c r="E57" t="n">
-        <v>73.02</v>
+        <v>55.04</v>
       </c>
       <c r="F57" t="n">
-        <v>11.04</v>
+        <v>16.02</v>
       </c>
       <c r="G57" t="n">
-        <v>104132410000</v>
+        <v>465085570000</v>
       </c>
       <c r="H57" t="n">
-        <v>844.6799999999999</v>
+        <v>468.62</v>
       </c>
       <c r="I57" t="n">
-        <v>1204.61</v>
+        <v>526.48</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>14.09</v>
+        <v>-10.12</v>
       </c>
       <c r="L57" t="n">
-        <v>9.84</v>
+        <v>11.41</v>
       </c>
       <c r="M57" t="n">
-        <v>19.96</v>
+        <v>33.44</v>
       </c>
       <c r="N57" t="n">
-        <v>27.71</v>
+        <v>48.96</v>
       </c>
       <c r="O57" t="n">
-        <v>15.07</v>
+        <v>29.31</v>
       </c>
       <c r="P57" t="n">
-        <v>1.63</v>
+        <v>0.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="R57" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="S57" t="n">
-        <v>99.02</v>
+        <v>81.87</v>
       </c>
       <c r="T57" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U57" t="n">
-        <v>44.3</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>567.25</v>
+        <v>134.4</v>
       </c>
       <c r="D58" t="n">
-        <v>74.01000000000001</v>
+        <v>62.01</v>
       </c>
       <c r="E58" t="n">
-        <v>53.3</v>
+        <v>30.39</v>
       </c>
       <c r="F58" t="n">
-        <v>15.52</v>
+        <v>4.37</v>
       </c>
       <c r="G58" t="n">
-        <v>450373480000</v>
+        <v>3922540000</v>
       </c>
       <c r="H58" t="n">
-        <v>453.8</v>
+        <v>107.52</v>
       </c>
       <c r="I58" t="n">
-        <v>526.48</v>
+        <v>145.12</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.19</v>
+        <v>7.98</v>
       </c>
       <c r="L58" t="n">
-        <v>11.41</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>33.44</v>
+        <v>-28.33</v>
       </c>
       <c r="N58" t="n">
-        <v>48.96</v>
+        <v>41.37</v>
       </c>
       <c r="O58" t="n">
-        <v>29.31</v>
+        <v>14.56</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.6</v>
+        <v>0.66</v>
       </c>
       <c r="R58" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S58" t="n">
-        <v>81.87</v>
+        <v>108.11</v>
       </c>
       <c r="T58" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="U58" t="n">
-        <v>44.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>131.73</v>
+        <v>46.47</v>
       </c>
       <c r="D59" t="n">
-        <v>58.48</v>
-      </c>
-      <c r="E59" t="n">
-        <v>29.79</v>
+        <v>57.38</v>
       </c>
       <c r="F59" t="n">
-        <v>4.29</v>
+        <v>37.36</v>
       </c>
       <c r="G59" t="n">
-        <v>3844610000</v>
+        <v>13279710000</v>
       </c>
       <c r="H59" t="n">
-        <v>105.38</v>
+        <v>37.18</v>
       </c>
       <c r="I59" t="n">
-        <v>145.12</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
+        <v>70.75</v>
       </c>
       <c r="K59" t="n">
-        <v>10.16</v>
+        <v>52.25</v>
       </c>
       <c r="L59" t="n">
-        <v>-8.970000000000001</v>
+        <v>139.29</v>
       </c>
       <c r="M59" t="n">
-        <v>-28.33</v>
+        <v>-120.39</v>
       </c>
       <c r="N59" t="n">
-        <v>41.37</v>
+        <v>27.07</v>
       </c>
       <c r="O59" t="n">
-        <v>14.56</v>
+        <v>-54.12</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.66</v>
+        <v>5.66</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="S59" t="n">
-        <v>108.11</v>
+        <v>70.27</v>
       </c>
       <c r="T59" t="n">
-        <v>2.13</v>
+        <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>43.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="60">
@@ -4500,22 +4500,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>294.75</v>
+        <v>303.53</v>
       </c>
       <c r="D60" t="n">
-        <v>55</v>
+        <v>57.89</v>
       </c>
       <c r="E60" t="n">
-        <v>57.6</v>
+        <v>59.32</v>
       </c>
       <c r="F60" t="n">
-        <v>9.49</v>
+        <v>9.77</v>
       </c>
       <c r="G60" t="n">
-        <v>10738230000</v>
+        <v>11058100000</v>
       </c>
       <c r="H60" t="n">
-        <v>235.8</v>
+        <v>242.82</v>
       </c>
       <c r="I60" t="n">
         <v>289.17</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.89</v>
+        <v>-4.73</v>
       </c>
       <c r="L60" t="n">
         <v>6.45</v>
@@ -4554,7 +4554,7 @@
         <v>1.86</v>
       </c>
       <c r="U60" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -4569,25 +4569,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="D61" t="n">
-        <v>65.19</v>
+        <v>65.25</v>
       </c>
       <c r="F61" t="n">
-        <v>226.74</v>
+        <v>227.05</v>
       </c>
       <c r="G61" t="n">
-        <v>1319620000</v>
+        <v>1321400000</v>
       </c>
       <c r="H61" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="I61" t="n">
         <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.41</v>
+        <v>-5.53</v>
       </c>
       <c r="L61" t="n">
         <v>479.14</v>
@@ -4605,7 +4605,7 @@
         <v>0.02</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="R61" t="n">
         <v>32.13</v>
@@ -4632,22 +4632,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>279.62</v>
+        <v>284.54</v>
       </c>
       <c r="D62" t="n">
-        <v>64.84</v>
+        <v>66.58</v>
       </c>
       <c r="E62" t="n">
-        <v>230.01</v>
+        <v>234.05</v>
       </c>
       <c r="F62" t="n">
-        <v>21.49</v>
+        <v>21.86</v>
       </c>
       <c r="G62" t="n">
-        <v>227890300000</v>
+        <v>231900110000</v>
       </c>
       <c r="H62" t="n">
-        <v>223.7</v>
+        <v>227.63</v>
       </c>
       <c r="I62" t="n">
         <v>320.25</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>14.53</v>
+        <v>12.55</v>
       </c>
       <c r="L62" t="n">
         <v>31.15</v>
@@ -4686,7 +4686,7 @@
         <v>1.54</v>
       </c>
       <c r="U62" t="n">
-        <v>41.2</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="63">
@@ -4701,25 +4701,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23.71</v>
+        <v>24.18</v>
       </c>
       <c r="D63" t="n">
-        <v>54.66</v>
+        <v>55.58</v>
       </c>
       <c r="F63" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G63" t="n">
-        <v>4370010000</v>
+        <v>4456640000</v>
       </c>
       <c r="H63" t="n">
-        <v>18.97</v>
+        <v>19.34</v>
       </c>
       <c r="I63" t="n">
         <v>18.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-21.34</v>
+        <v>-22.87</v>
       </c>
       <c r="L63" t="n">
         <v>7.71</v>
@@ -4737,7 +4737,7 @@
         <v>1.09</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R63" t="n">
         <v>24.52</v>
@@ -4749,7 +4749,7 @@
         <v>2.86</v>
       </c>
       <c r="U63" t="n">
-        <v>40.5</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="64">
@@ -4764,22 +4764,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>220.31</v>
+        <v>227.41</v>
       </c>
       <c r="D64" t="n">
-        <v>49.47</v>
+        <v>55.21</v>
       </c>
       <c r="E64" t="n">
-        <v>31.23</v>
+        <v>32.24</v>
       </c>
       <c r="F64" t="n">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="G64" t="n">
-        <v>139600120000</v>
+        <v>144099060000</v>
       </c>
       <c r="H64" t="n">
-        <v>176.25</v>
+        <v>181.93</v>
       </c>
       <c r="I64" t="n">
         <v>251.87</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>14.33</v>
+        <v>10.76</v>
       </c>
       <c r="L64" t="n">
         <v>-6.9</v>
@@ -4818,7 +4818,7 @@
         <v>1.96</v>
       </c>
       <c r="U64" t="n">
-        <v>40.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="65">
@@ -4833,22 +4833,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>69.91</v>
+        <v>71.13</v>
       </c>
       <c r="D65" t="n">
-        <v>60.48</v>
+        <v>62.99</v>
       </c>
       <c r="E65" t="n">
-        <v>45.93</v>
+        <v>46.73</v>
       </c>
       <c r="F65" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G65" t="n">
-        <v>58065880000</v>
+        <v>59079180000</v>
       </c>
       <c r="H65" t="n">
-        <v>55.93</v>
+        <v>56.9</v>
       </c>
       <c r="I65" t="n">
         <v>76.40000000000001</v>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>9.279999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="L65" t="n">
         <v>2.36</v>
@@ -4875,7 +4875,7 @@
         <v>0.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R65" t="n">
         <v>4.74</v>
@@ -4887,7 +4887,7 @@
         <v>2.03</v>
       </c>
       <c r="U65" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="66">
@@ -4898,65 +4898,65 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>323.88</v>
+        <v>256.42</v>
       </c>
       <c r="D66" t="n">
-        <v>67.23</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>150.36</v>
+        <v>72.44</v>
       </c>
       <c r="F66" t="n">
-        <v>15.63</v>
+        <v>25.58</v>
       </c>
       <c r="G66" t="n">
-        <v>16110950000</v>
+        <v>334955110000</v>
       </c>
       <c r="H66" t="n">
-        <v>259.1</v>
+        <v>205.14</v>
       </c>
       <c r="I66" t="n">
-        <v>349.44</v>
+        <v>187.1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>7.89</v>
+        <v>-27.03</v>
       </c>
       <c r="L66" t="n">
-        <v>9.51</v>
+        <v>11.5</v>
       </c>
       <c r="M66" t="n">
-        <v>-47.97</v>
+        <v>11.8</v>
       </c>
       <c r="N66" t="n">
-        <v>49.26</v>
+        <v>61.4</v>
       </c>
       <c r="O66" t="n">
-        <v>10.33</v>
+        <v>35.7</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="R66" t="n">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
       <c r="S66" t="n">
-        <v>99.20999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="T66" t="n">
-        <v>1.1</v>
+        <v>2.03</v>
       </c>
       <c r="U66" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="67">
@@ -4967,203 +4967,203 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>ONTO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>81.38</v>
+        <v>335.96</v>
       </c>
       <c r="D67" t="n">
-        <v>57.57</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>58.46</v>
+        <v>155.96</v>
       </c>
       <c r="F67" t="n">
-        <v>6.52</v>
+        <v>16.22</v>
       </c>
       <c r="G67" t="n">
-        <v>44630130000</v>
+        <v>16711849999</v>
       </c>
       <c r="H67" t="n">
-        <v>65.09999999999999</v>
+        <v>268.77</v>
       </c>
       <c r="I67" t="n">
-        <v>80.7</v>
+        <v>351.6</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.84</v>
+        <v>4.66</v>
       </c>
       <c r="L67" t="n">
-        <v>3.09</v>
+        <v>9.51</v>
       </c>
       <c r="M67" t="n">
-        <v>-51.3</v>
+        <v>-47.97</v>
       </c>
       <c r="N67" t="n">
-        <v>26.11</v>
+        <v>49.26</v>
       </c>
       <c r="O67" t="n">
-        <v>11.37</v>
+        <v>10.33</v>
       </c>
       <c r="P67" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="R67" t="n">
-        <v>76.16</v>
+        <v>0.63</v>
       </c>
       <c r="S67" t="n">
-        <v>25.62</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="T67" t="n">
-        <v>2.12</v>
+        <v>1.09</v>
       </c>
       <c r="U67" t="n">
-        <v>38</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>279.7</v>
+        <v>83.98</v>
       </c>
       <c r="D68" t="n">
-        <v>62.99</v>
+        <v>60.34</v>
       </c>
       <c r="E68" t="n">
-        <v>95.58</v>
+        <v>60.33</v>
       </c>
       <c r="F68" t="n">
-        <v>28.07</v>
+        <v>6.73</v>
       </c>
       <c r="G68" t="n">
-        <v>244681570000</v>
+        <v>46056020000</v>
       </c>
       <c r="H68" t="n">
-        <v>223.76</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>244.35</v>
+        <v>80.7</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>-12.64</v>
+        <v>-3.91</v>
       </c>
       <c r="L68" t="n">
-        <v>27.57</v>
+        <v>3.09</v>
       </c>
       <c r="M68" t="n">
-        <v>-81</v>
+        <v>-51.3</v>
       </c>
       <c r="N68" t="n">
-        <v>50.64</v>
+        <v>26.11</v>
       </c>
       <c r="O68" t="n">
-        <v>28.99</v>
+        <v>11.37</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0.77</v>
+        <v>76.16</v>
       </c>
       <c r="S68" t="n">
-        <v>78.14</v>
+        <v>25.62</v>
       </c>
       <c r="T68" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="U68" t="n">
-        <v>37.9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>254.54</v>
+        <v>308.88</v>
       </c>
       <c r="D69" t="n">
-        <v>75.63</v>
+        <v>67.7</v>
       </c>
       <c r="E69" t="n">
-        <v>71.90000000000001</v>
+        <v>105.55</v>
       </c>
       <c r="F69" t="n">
-        <v>25.39</v>
+        <v>31</v>
       </c>
       <c r="G69" t="n">
-        <v>332499280000</v>
+        <v>270208229999</v>
       </c>
       <c r="H69" t="n">
-        <v>203.63</v>
+        <v>247.1</v>
       </c>
       <c r="I69" t="n">
-        <v>187.1</v>
+        <v>244.35</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>-26.49</v>
+        <v>-20.89</v>
       </c>
       <c r="L69" t="n">
-        <v>11.5</v>
+        <v>27.57</v>
       </c>
       <c r="M69" t="n">
-        <v>11.8</v>
+        <v>-81</v>
       </c>
       <c r="N69" t="n">
-        <v>61.4</v>
+        <v>50.64</v>
       </c>
       <c r="O69" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="S69" t="n">
+        <v>78.14</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U69" t="n">
         <v>35.7</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U69" t="n">
-        <v>37.4</v>
       </c>
     </row>
     <row r="70">
@@ -5178,22 +5178,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>180.12</v>
+        <v>191.6</v>
       </c>
       <c r="D70" t="n">
-        <v>65.06999999999999</v>
+        <v>69.28</v>
       </c>
       <c r="E70" t="n">
-        <v>56.12</v>
+        <v>59.69</v>
       </c>
       <c r="F70" t="n">
-        <v>6.55</v>
+        <v>6.97</v>
       </c>
       <c r="G70" t="n">
-        <v>5535790000</v>
+        <v>5888620000</v>
       </c>
       <c r="H70" t="n">
-        <v>144.1</v>
+        <v>153.28</v>
       </c>
       <c r="I70" t="n">
         <v>161</v>
@@ -5202,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-10.62</v>
+        <v>-15.97</v>
       </c>
       <c r="L70" t="n">
         <v>3.32</v>
@@ -5232,7 +5232,7 @@
         <v>2.67</v>
       </c>
       <c r="U70" t="n">
-        <v>37.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="71">
@@ -5247,25 +5247,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>124.57</v>
+        <v>127.86</v>
       </c>
       <c r="D71" t="n">
-        <v>62.43</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>11.65</v>
+        <v>11.95</v>
       </c>
       <c r="G71" t="n">
-        <v>626088820000</v>
+        <v>642624360000</v>
       </c>
       <c r="H71" t="n">
-        <v>99.66</v>
+        <v>102.29</v>
       </c>
       <c r="I71" t="n">
         <v>99.98</v>
       </c>
       <c r="K71" t="n">
-        <v>-19.74</v>
+        <v>-21.81</v>
       </c>
       <c r="L71" t="n">
         <v>7.18</v>
@@ -5283,7 +5283,7 @@
         <v>0.4</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R71" t="n">
         <v>15.51</v>
@@ -5295,7 +5295,7 @@
         <v>2.53</v>
       </c>
       <c r="U71" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="72">
@@ -5310,25 +5310,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9.890000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="D72" t="n">
-        <v>41.08</v>
+        <v>46.2</v>
       </c>
       <c r="F72" t="n">
-        <v>193.61</v>
+        <v>208.29</v>
       </c>
       <c r="G72" t="n">
-        <v>3614610000</v>
+        <v>3888720000</v>
       </c>
       <c r="H72" t="n">
-        <v>7.91</v>
+        <v>8.51</v>
       </c>
       <c r="I72" t="n">
         <v>15.64</v>
       </c>
       <c r="K72" t="n">
-        <v>58.14</v>
+        <v>46.99</v>
       </c>
       <c r="L72" t="n">
         <v>-95.78</v>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R72" t="n">
         <v>3.08</v>
@@ -5358,7 +5358,7 @@
         <v>2.4</v>
       </c>
       <c r="U72" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="73">
@@ -5373,25 +5373,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.9</v>
+        <v>11.03</v>
       </c>
       <c r="D73" t="n">
-        <v>59.74</v>
+        <v>61.05</v>
       </c>
       <c r="F73" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="G73" t="n">
-        <v>1583670000</v>
+        <v>1602560000</v>
       </c>
       <c r="H73" t="n">
-        <v>8.720000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="I73" t="n">
         <v>8.82</v>
       </c>
       <c r="K73" t="n">
-        <v>-19.08</v>
+        <v>-20.04</v>
       </c>
       <c r="L73" t="n">
         <v>-52.54</v>
@@ -5409,7 +5409,7 @@
         <v>0.01</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R73" t="n">
         <v>12.61</v>
@@ -5421,7 +5421,7 @@
         <v>3.4</v>
       </c>
       <c r="U73" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
     </row>
   </sheetData>
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1877.61</v>
+        <v>1952.02</v>
       </c>
       <c r="C2" t="n">
-        <v>53.21</v>
+        <v>58.09</v>
       </c>
       <c r="D2" t="n">
-        <v>54.19</v>
+        <v>56.34</v>
       </c>
       <c r="E2" t="n">
-        <v>6.52</v>
+        <v>6.78</v>
       </c>
       <c r="F2" t="n">
-        <v>66096429999</v>
+        <v>68715840000</v>
       </c>
       <c r="G2" t="n">
-        <v>1502.09</v>
+        <v>1561.62</v>
       </c>
       <c r="H2" t="n">
         <v>2115.29</v>
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12.66</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>56.47</v>
@@ -5601,7 +5601,7 @@
         <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="3">
@@ -5611,22 +5611,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>823.05</v>
+        <v>842.3</v>
       </c>
       <c r="C3" t="n">
-        <v>45.54</v>
+        <v>50.31</v>
       </c>
       <c r="D3" t="n">
-        <v>27.54</v>
+        <v>28.19</v>
       </c>
       <c r="E3" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="F3" t="n">
-        <v>36576570000</v>
+        <v>37432050000</v>
       </c>
       <c r="G3" t="n">
-        <v>658.4400000000001</v>
+        <v>673.84</v>
       </c>
       <c r="H3" t="n">
         <v>1000.14</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>21.52</v>
+        <v>18.74</v>
       </c>
       <c r="K3" t="n">
         <v>19.67</v>
@@ -5665,7 +5665,7 @@
         <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>52.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="4">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>858.99</v>
+        <v>866.67</v>
       </c>
       <c r="C4" t="n">
-        <v>55.67</v>
+        <v>56.29</v>
       </c>
       <c r="D4" t="n">
-        <v>76.8</v>
+        <v>77.48</v>
       </c>
       <c r="E4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>26358930000</v>
+        <v>26594600000</v>
       </c>
       <c r="G4" t="n">
-        <v>687.1900000000001</v>
+        <v>693.34</v>
       </c>
       <c r="H4" t="n">
         <v>956.4299999999999</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>11.34</v>
+        <v>10.36</v>
       </c>
       <c r="K4" t="n">
         <v>91.59</v>
@@ -5717,7 +5717,7 @@
         <v>0.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
         <v>2.43</v>
@@ -5729,7 +5729,7 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
     </row>
   </sheetData>
@@ -5855,25 +5855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>682.8</v>
+        <v>692.91</v>
       </c>
       <c r="C2" t="n">
-        <v>58.72</v>
+        <v>60.21</v>
       </c>
       <c r="E2" t="n">
-        <v>34.12</v>
+        <v>34.63</v>
       </c>
       <c r="F2" t="n">
-        <v>173816860000</v>
+        <v>176390510000</v>
       </c>
       <c r="G2" t="n">
-        <v>546.24</v>
+        <v>554.33</v>
       </c>
       <c r="H2" t="n">
         <v>720.9299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.58</v>
+        <v>4.04</v>
       </c>
       <c r="K2" t="n">
         <v>25.57</v>
@@ -5903,7 +5903,7 @@
         <v>1.57</v>
       </c>
       <c r="T2" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="3">
@@ -5913,22 +5913,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>279.62</v>
+        <v>284.54</v>
       </c>
       <c r="C3" t="n">
-        <v>64.84</v>
+        <v>66.58</v>
       </c>
       <c r="D3" t="n">
-        <v>230.01</v>
+        <v>234.05</v>
       </c>
       <c r="E3" t="n">
-        <v>21.49</v>
+        <v>21.86</v>
       </c>
       <c r="F3" t="n">
-        <v>227890300000</v>
+        <v>231900110000</v>
       </c>
       <c r="G3" t="n">
-        <v>223.7</v>
+        <v>227.63</v>
       </c>
       <c r="H3" t="n">
         <v>320.25</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14.53</v>
+        <v>12.55</v>
       </c>
       <c r="K3" t="n">
         <v>31.15</v>
@@ -5967,7 +5967,7 @@
         <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>41.2</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="4">
@@ -5977,25 +5977,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>129.52</v>
+        <v>130.42</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78</v>
+        <v>43.4</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="F4" t="n">
-        <v>20944620000</v>
+        <v>21090160000</v>
       </c>
       <c r="G4" t="n">
-        <v>103.62</v>
+        <v>104.34</v>
       </c>
       <c r="H4" t="n">
         <v>192.67</v>
       </c>
       <c r="J4" t="n">
-        <v>48.76</v>
+        <v>47.73</v>
       </c>
       <c r="K4" t="n">
         <v>25.43</v>
@@ -6013,7 +6013,7 @@
         <v>0.79</v>
       </c>
       <c r="P4" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="Q4" t="n">
         <v>35.18</v>
@@ -6025,7 +6025,7 @@
         <v>1.48</v>
       </c>
       <c r="T4" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="5">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>116.29</v>
+        <v>118.12</v>
       </c>
       <c r="C5" t="n">
-        <v>60.11</v>
+        <v>61.34</v>
       </c>
       <c r="D5" t="n">
-        <v>84.45999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="F5" t="n">
-        <v>20212060000</v>
+        <v>20530130000</v>
       </c>
       <c r="G5" t="n">
-        <v>93.03</v>
+        <v>94.5</v>
       </c>
       <c r="H5" t="n">
         <v>119.83</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.04</v>
+        <v>1.45</v>
       </c>
       <c r="K5" t="n">
         <v>11.19</v>
@@ -6089,7 +6089,7 @@
         <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="6">
@@ -6099,25 +6099,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.19</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>49.34</v>
+        <v>51.98</v>
       </c>
       <c r="E6" t="n">
-        <v>9.85</v>
+        <v>10.08</v>
       </c>
       <c r="F6" t="n">
-        <v>14035430000</v>
+        <v>14364750000</v>
       </c>
       <c r="G6" t="n">
-        <v>54.55</v>
+        <v>55.83</v>
       </c>
       <c r="H6" t="n">
         <v>94.37</v>
       </c>
       <c r="J6" t="n">
-        <v>38.39</v>
+        <v>35.22</v>
       </c>
       <c r="K6" t="n">
         <v>38.99</v>
@@ -6132,7 +6132,7 @@
         <v>-20.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>26.66</v>
@@ -6144,7 +6144,7 @@
         <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>55.9</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -6270,22 +6270,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>567.25</v>
+        <v>585.78</v>
       </c>
       <c r="C2" t="n">
-        <v>74.01000000000001</v>
+        <v>76.11</v>
       </c>
       <c r="D2" t="n">
-        <v>53.3</v>
+        <v>55.04</v>
       </c>
       <c r="E2" t="n">
-        <v>15.52</v>
+        <v>16.02</v>
       </c>
       <c r="F2" t="n">
-        <v>450373480000</v>
+        <v>465085570000</v>
       </c>
       <c r="G2" t="n">
-        <v>453.8</v>
+        <v>468.62</v>
       </c>
       <c r="H2" t="n">
         <v>526.48</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-7.19</v>
+        <v>-10.12</v>
       </c>
       <c r="K2" t="n">
         <v>11.41</v>
@@ -6324,7 +6324,7 @@
         <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>44.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="3">
@@ -6334,31 +6334,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>366.81</v>
+        <v>388.92</v>
       </c>
       <c r="C3" t="n">
-        <v>68.54000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="D3" t="n">
-        <v>69.23</v>
+        <v>73.41</v>
       </c>
       <c r="E3" t="n">
-        <v>21.16</v>
+        <v>22.43</v>
       </c>
       <c r="F3" t="n">
-        <v>458721960000</v>
+        <v>486372110000</v>
       </c>
       <c r="G3" t="n">
-        <v>293.45</v>
+        <v>311.14</v>
       </c>
       <c r="H3" t="n">
-        <v>330.97</v>
+        <v>333.38</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.77</v>
+        <v>-14.28</v>
       </c>
       <c r="K3" t="n">
         <v>23.76</v>
@@ -6376,7 +6376,7 @@
         <v>0.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
         <v>0.34</v>
@@ -6388,7 +6388,7 @@
         <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>44.9</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="4">
@@ -6398,22 +6398,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>254.54</v>
+        <v>256.42</v>
       </c>
       <c r="C4" t="n">
-        <v>75.63</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>71.90000000000001</v>
+        <v>72.44</v>
       </c>
       <c r="E4" t="n">
-        <v>25.39</v>
+        <v>25.58</v>
       </c>
       <c r="F4" t="n">
-        <v>332499280000</v>
+        <v>334955110000</v>
       </c>
       <c r="G4" t="n">
-        <v>203.63</v>
+        <v>205.14</v>
       </c>
       <c r="H4" t="n">
         <v>187.1</v>
@@ -6422,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-26.49</v>
+        <v>-27.03</v>
       </c>
       <c r="K4" t="n">
         <v>11.5</v>
@@ -6440,7 +6440,7 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0.1</v>
@@ -6452,7 +6452,7 @@
         <v>2.03</v>
       </c>
       <c r="T4" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="5">
@@ -6462,31 +6462,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>323.88</v>
+        <v>335.96</v>
       </c>
       <c r="C5" t="n">
-        <v>67.23</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>150.36</v>
+        <v>155.96</v>
       </c>
       <c r="E5" t="n">
-        <v>15.63</v>
+        <v>16.22</v>
       </c>
       <c r="F5" t="n">
-        <v>16110950000</v>
+        <v>16711849999</v>
       </c>
       <c r="G5" t="n">
-        <v>259.1</v>
+        <v>268.77</v>
       </c>
       <c r="H5" t="n">
-        <v>349.44</v>
+        <v>351.6</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7.89</v>
+        <v>4.66</v>
       </c>
       <c r="K5" t="n">
         <v>9.51</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
         <v>0.63</v>
@@ -6513,10 +6513,10 @@
         <v>99.20999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T5" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="6">
@@ -6526,22 +6526,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>180.12</v>
+        <v>191.6</v>
       </c>
       <c r="C6" t="n">
-        <v>65.06999999999999</v>
+        <v>69.28</v>
       </c>
       <c r="D6" t="n">
-        <v>56.12</v>
+        <v>59.69</v>
       </c>
       <c r="E6" t="n">
-        <v>6.55</v>
+        <v>6.97</v>
       </c>
       <c r="F6" t="n">
-        <v>5535790000</v>
+        <v>5888620000</v>
       </c>
       <c r="G6" t="n">
-        <v>144.1</v>
+        <v>153.28</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.62</v>
+        <v>-15.97</v>
       </c>
       <c r="K6" t="n">
         <v>3.32</v>
@@ -6580,7 +6580,7 @@
         <v>2.67</v>
       </c>
       <c r="T6" t="n">
-        <v>37.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="7">
@@ -6590,22 +6590,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.78</v>
+        <v>32.74</v>
       </c>
       <c r="C7" t="n">
-        <v>36.04</v>
+        <v>38.43</v>
       </c>
       <c r="D7" t="n">
-        <v>11.64</v>
+        <v>11.99</v>
       </c>
       <c r="E7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="F7" t="n">
-        <v>1873870000</v>
+        <v>1930480000</v>
       </c>
       <c r="G7" t="n">
-        <v>25.42</v>
+        <v>26.19</v>
       </c>
       <c r="H7" t="n">
         <v>43</v>
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>35.31</v>
+        <v>31.34</v>
       </c>
       <c r="K7" t="n">
         <v>-0.5</v>
@@ -6632,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
         <v>4.06</v>
@@ -6644,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8">
@@ -6654,22 +6654,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>423.93</v>
+        <v>441.4</v>
       </c>
       <c r="C8" t="n">
-        <v>53.77</v>
+        <v>59.42</v>
       </c>
       <c r="D8" t="n">
-        <v>35.23</v>
+        <v>36.69</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55</v>
+        <v>17.23</v>
       </c>
       <c r="F8" t="n">
-        <v>2198704430000</v>
+        <v>2289312240000</v>
       </c>
       <c r="G8" t="n">
-        <v>339.14</v>
+        <v>353.12</v>
       </c>
       <c r="H8" t="n">
         <v>460.4</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>40.49</v>
@@ -6705,10 +6705,10 @@
         <v>15.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="T8" t="n">
-        <v>59.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="9">
@@ -6718,22 +6718,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.38</v>
+        <v>83.98</v>
       </c>
       <c r="C9" t="n">
-        <v>57.57</v>
+        <v>60.34</v>
       </c>
       <c r="D9" t="n">
-        <v>58.46</v>
+        <v>60.33</v>
       </c>
       <c r="E9" t="n">
-        <v>6.52</v>
+        <v>6.73</v>
       </c>
       <c r="F9" t="n">
-        <v>44630130000</v>
+        <v>46056020000</v>
       </c>
       <c r="G9" t="n">
-        <v>65.09999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>80.7</v>
@@ -6742,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.84</v>
+        <v>-3.91</v>
       </c>
       <c r="K9" t="n">
         <v>3.09</v>
@@ -6772,7 +6772,7 @@
         <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6782,25 +6782,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.57</v>
+        <v>127.86</v>
       </c>
       <c r="C10" t="n">
-        <v>62.43</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>11.65</v>
+        <v>11.95</v>
       </c>
       <c r="F10" t="n">
-        <v>626088820000</v>
+        <v>642624360000</v>
       </c>
       <c r="G10" t="n">
-        <v>99.66</v>
+        <v>102.29</v>
       </c>
       <c r="H10" t="n">
         <v>99.98</v>
       </c>
       <c r="J10" t="n">
-        <v>-19.74</v>
+        <v>-21.81</v>
       </c>
       <c r="K10" t="n">
         <v>7.18</v>
@@ -6818,7 +6818,7 @@
         <v>0.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
         <v>15.51</v>
@@ -6830,7 +6830,7 @@
         <v>2.53</v>
       </c>
       <c r="T10" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="11">
@@ -6840,22 +6840,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>262.92</v>
+        <v>286.86</v>
       </c>
       <c r="C11" t="n">
-        <v>55.22</v>
+        <v>61.5</v>
       </c>
       <c r="D11" t="n">
-        <v>122.12</v>
+        <v>133.24</v>
       </c>
       <c r="E11" t="n">
-        <v>18.12</v>
+        <v>19.77</v>
       </c>
       <c r="F11" t="n">
-        <v>29383050000</v>
+        <v>32058500000</v>
       </c>
       <c r="G11" t="n">
-        <v>210.34</v>
+        <v>229.49</v>
       </c>
       <c r="H11" t="n">
         <v>313.83</v>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>19.36</v>
+        <v>9.4</v>
       </c>
       <c r="K11" t="n">
         <v>15.48</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>46.4</v>
+        <v>43.8</v>
       </c>
     </row>
   </sheetData>
@@ -7020,22 +7020,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.46</v>
+        <v>30.85</v>
       </c>
       <c r="C2" t="n">
-        <v>41.12</v>
+        <v>41.77</v>
       </c>
       <c r="D2" t="n">
-        <v>16.07</v>
+        <v>16.27</v>
       </c>
       <c r="E2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="F2" t="n">
-        <v>18319210000</v>
+        <v>18553760000</v>
       </c>
       <c r="G2" t="n">
-        <v>24.37</v>
+        <v>24.68</v>
       </c>
       <c r="H2" t="n">
         <v>35.87</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>17.76</v>
+        <v>16.27</v>
       </c>
       <c r="K2" t="n">
         <v>122.68</v>
@@ -7062,7 +7062,7 @@
         <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
         <v>13.87</v>
@@ -7074,7 +7074,7 @@
         <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>65.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -7084,28 +7084,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>395.57</v>
+        <v>409.07</v>
       </c>
       <c r="C3" t="n">
-        <v>64.53</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>31.43</v>
+        <v>32.51</v>
       </c>
       <c r="E3" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="F3" t="n">
-        <v>256372080000</v>
+        <v>265121539999</v>
       </c>
       <c r="G3" t="n">
-        <v>316.46</v>
+        <v>327.26</v>
       </c>
       <c r="H3" t="n">
         <v>496.76</v>
       </c>
       <c r="J3" t="n">
-        <v>25.58</v>
+        <v>21.44</v>
       </c>
       <c r="K3" t="n">
         <v>87.48999999999999</v>
@@ -7132,7 +7132,7 @@
         <v>1.73</v>
       </c>
       <c r="T3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -7142,22 +7142,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.17</v>
+        <v>49.02</v>
       </c>
       <c r="C4" t="n">
-        <v>63.46</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>46.18</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="F4" t="n">
-        <v>63786880000</v>
+        <v>64912460000</v>
       </c>
       <c r="G4" t="n">
-        <v>38.54</v>
+        <v>39.22</v>
       </c>
       <c r="H4" t="n">
         <v>68.59</v>
@@ -7166,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>42.39</v>
+        <v>39.92</v>
       </c>
       <c r="K4" t="n">
         <v>40.64</v>
@@ -7184,7 +7184,7 @@
         <v>0.84</v>
       </c>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0.38</v>
@@ -7196,7 +7196,7 @@
         <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>56</v>
+        <v>55.4</v>
       </c>
     </row>
   </sheetData>
@@ -7322,31 +7322,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102.15</v>
+        <v>104.15</v>
       </c>
       <c r="C2" t="n">
-        <v>46.25</v>
+        <v>48.1</v>
       </c>
       <c r="D2" t="n">
-        <v>60.76</v>
+        <v>61.95</v>
       </c>
       <c r="E2" t="n">
-        <v>7.55</v>
+        <v>7.69</v>
       </c>
       <c r="F2" t="n">
-        <v>105348110000</v>
+        <v>107410730000</v>
       </c>
       <c r="G2" t="n">
-        <v>81.72</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>140.63</v>
+        <v>140.76</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37.67</v>
+        <v>35.15</v>
       </c>
       <c r="K2" t="n">
         <v>22.09</v>
@@ -7364,7 +7364,7 @@
         <v>0.21</v>
       </c>
       <c r="P2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="Q2" t="n">
         <v>0.91</v>
@@ -7376,7 +7376,7 @@
         <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>54.8</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="3">
@@ -7386,31 +7386,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>229.9</v>
+        <v>233.09</v>
       </c>
       <c r="C3" t="n">
-        <v>57.63</v>
+        <v>59.08</v>
       </c>
       <c r="D3" t="n">
-        <v>613.5599999999999</v>
+        <v>622.0700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>22.29</v>
+        <v>22.6</v>
       </c>
       <c r="F3" t="n">
-        <v>81835250000</v>
+        <v>82970760000</v>
       </c>
       <c r="G3" t="n">
-        <v>183.92</v>
+        <v>186.47</v>
       </c>
       <c r="H3" t="n">
-        <v>236.41</v>
+        <v>238.91</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
         <v>32.15</v>
@@ -7437,10 +7437,10 @@
         <v>81.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="4">
@@ -7450,31 +7450,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.75</v>
+        <v>41.19</v>
       </c>
       <c r="C4" t="n">
-        <v>51.18</v>
+        <v>52.92</v>
       </c>
       <c r="D4" t="n">
-        <v>76.01000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="E4" t="n">
-        <v>5.88</v>
+        <v>5.95</v>
       </c>
       <c r="F4" t="n">
-        <v>11877640000</v>
+        <v>12005890000</v>
       </c>
       <c r="G4" t="n">
-        <v>32.6</v>
+        <v>32.95</v>
       </c>
       <c r="H4" t="n">
-        <v>43.91</v>
+        <v>43.97</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="K4" t="n">
         <v>19.44</v>
@@ -7492,7 +7492,7 @@
         <v>0.06</v>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="Q4" t="n">
         <v>1.1</v>
@@ -7504,7 +7504,7 @@
         <v>1.82</v>
       </c>
       <c r="T4" t="n">
-        <v>47.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="5">
@@ -7514,25 +7514,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.9</v>
+        <v>11.03</v>
       </c>
       <c r="C5" t="n">
-        <v>59.74</v>
+        <v>61.05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1583670000</v>
+        <v>1602560000</v>
       </c>
       <c r="G5" t="n">
-        <v>8.720000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H5" t="n">
         <v>8.82</v>
       </c>
       <c r="J5" t="n">
-        <v>-19.08</v>
+        <v>-20.04</v>
       </c>
       <c r="K5" t="n">
         <v>-52.54</v>
@@ -7550,7 +7550,7 @@
         <v>0.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
         <v>12.61</v>
@@ -7562,7 +7562,7 @@
         <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -7572,25 +7572,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>342.8</v>
+        <v>354.18</v>
       </c>
       <c r="C6" t="n">
-        <v>53.33</v>
+        <v>56.16</v>
       </c>
       <c r="E6" t="n">
-        <v>10.59</v>
+        <v>10.95</v>
       </c>
       <c r="F6" t="n">
-        <v>27572060000</v>
+        <v>28487380000</v>
       </c>
       <c r="G6" t="n">
-        <v>274.24</v>
+        <v>283.34</v>
       </c>
       <c r="H6" t="n">
         <v>399.82</v>
       </c>
       <c r="J6" t="n">
-        <v>16.63</v>
+        <v>12.89</v>
       </c>
       <c r="K6" t="n">
         <v>25.25</v>
@@ -7608,7 +7608,7 @@
         <v>0.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
         <v>4.01</v>
@@ -7620,7 +7620,7 @@
         <v>1.59</v>
       </c>
       <c r="T6" t="n">
-        <v>57.9</v>
+        <v>56.8</v>
       </c>
     </row>
   </sheetData>
@@ -7746,25 +7746,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260.22</v>
+        <v>274.5</v>
       </c>
       <c r="C2" t="n">
-        <v>48.3</v>
+        <v>52.3</v>
       </c>
       <c r="E2" t="n">
-        <v>30.22</v>
+        <v>31.88</v>
       </c>
       <c r="F2" t="n">
-        <v>74017990000</v>
+        <v>78079850000</v>
       </c>
       <c r="G2" t="n">
-        <v>208.18</v>
+        <v>219.6</v>
       </c>
       <c r="H2" t="n">
         <v>270.51</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>-1.45</v>
       </c>
       <c r="K2" t="n">
         <v>130.37</v>
@@ -7782,7 +7782,7 @@
         <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="Q2" t="n">
         <v>6.31</v>
@@ -7794,7 +7794,7 @@
         <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>51.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="3">
@@ -7804,25 +7804,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.71</v>
+        <v>24.18</v>
       </c>
       <c r="C3" t="n">
-        <v>54.66</v>
+        <v>55.58</v>
       </c>
       <c r="E3" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="F3" t="n">
-        <v>4370010000</v>
+        <v>4456640000</v>
       </c>
       <c r="G3" t="n">
-        <v>18.97</v>
+        <v>19.34</v>
       </c>
       <c r="H3" t="n">
         <v>18.65</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.34</v>
+        <v>-22.87</v>
       </c>
       <c r="K3" t="n">
         <v>7.71</v>
@@ -7840,7 +7840,7 @@
         <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="Q3" t="n">
         <v>24.52</v>
@@ -7852,7 +7852,7 @@
         <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>40.5</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="4">
@@ -7862,25 +7862,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="C4" t="n">
-        <v>65.19</v>
+        <v>65.25</v>
       </c>
       <c r="E4" t="n">
-        <v>226.74</v>
+        <v>227.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1319620000</v>
+        <v>1321400000</v>
       </c>
       <c r="G4" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.41</v>
+        <v>-5.53</v>
       </c>
       <c r="K4" t="n">
         <v>479.14</v>
@@ -7898,7 +7898,7 @@
         <v>0.02</v>
       </c>
       <c r="P4" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="Q4" t="n">
         <v>32.13</v>
@@ -8036,22 +8036,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390.74</v>
+        <v>399.76</v>
       </c>
       <c r="C2" t="n">
-        <v>37.09</v>
+        <v>42.72</v>
       </c>
       <c r="D2" t="n">
-        <v>23.27</v>
+        <v>23.81</v>
       </c>
       <c r="E2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="F2" t="n">
-        <v>2902586450000</v>
+        <v>2969591070000</v>
       </c>
       <c r="G2" t="n">
-        <v>312.59</v>
+        <v>319.81</v>
       </c>
       <c r="H2" t="n">
         <v>559.29</v>
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43.14</v>
+        <v>39.91</v>
       </c>
       <c r="K2" t="n">
         <v>18.3</v>
@@ -8090,7 +8090,7 @@
         <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>64.2</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="3">
@@ -8100,22 +8100,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238.55</v>
+        <v>246.02</v>
       </c>
       <c r="C3" t="n">
-        <v>34.76</v>
+        <v>43.22</v>
       </c>
       <c r="D3" t="n">
-        <v>28.51</v>
+        <v>29.4</v>
       </c>
       <c r="E3" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="F3" t="n">
-        <v>2566108470000</v>
+        <v>2646464090000</v>
       </c>
       <c r="G3" t="n">
-        <v>190.84</v>
+        <v>196.82</v>
       </c>
       <c r="H3" t="n">
         <v>317.34</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>33.03</v>
+        <v>28.99</v>
       </c>
       <c r="K3" t="n">
         <v>16.61</v>
@@ -8142,7 +8142,7 @@
         <v>0.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
         <v>8.949999999999999</v>
@@ -8154,7 +8154,7 @@
         <v>1.23</v>
       </c>
       <c r="T3" t="n">
-        <v>61.9</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="4">
@@ -8164,22 +8164,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184.13</v>
+        <v>192.64</v>
       </c>
       <c r="C4" t="n">
-        <v>42.09</v>
+        <v>46.65</v>
       </c>
       <c r="D4" t="n">
-        <v>31.6</v>
+        <v>33.07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.86</v>
+        <v>8.23</v>
       </c>
       <c r="F4" t="n">
-        <v>529566350000</v>
+        <v>554041490000</v>
       </c>
       <c r="G4" t="n">
-        <v>147.3</v>
+        <v>154.11</v>
       </c>
       <c r="H4" t="n">
         <v>255.87</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>38.96</v>
+        <v>32.82</v>
       </c>
       <c r="K4" t="n">
         <v>20.63</v>
@@ -8206,7 +8206,7 @@
         <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
         <v>40.54</v>
@@ -8218,7 +8218,7 @@
         <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>56.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="5">
@@ -8228,25 +8228,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100.55</v>
+        <v>106.71</v>
       </c>
       <c r="C5" t="n">
-        <v>45.24</v>
+        <v>50.51</v>
       </c>
       <c r="E5" t="n">
-        <v>8.81</v>
+        <v>9.35</v>
       </c>
       <c r="F5" t="n">
-        <v>54857100000</v>
+        <v>58217810000</v>
       </c>
       <c r="G5" t="n">
-        <v>80.44</v>
+        <v>85.37</v>
       </c>
       <c r="H5" t="n">
         <v>138.91</v>
       </c>
       <c r="J5" t="n">
-        <v>38.15</v>
+        <v>30.18</v>
       </c>
       <c r="K5" t="n">
         <v>111.69</v>
@@ -8264,7 +8264,7 @@
         <v>7.39</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="Q5" t="n">
         <v>38.09</v>
@@ -8276,7 +8276,7 @@
         <v>1.92</v>
       </c>
       <c r="T5" t="n">
-        <v>49</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="6">
@@ -8286,22 +8286,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232.36</v>
+        <v>260.07</v>
       </c>
       <c r="C6" t="n">
-        <v>56.99</v>
+        <v>64.11</v>
       </c>
       <c r="D6" t="n">
-        <v>77.52</v>
+        <v>86.77</v>
       </c>
       <c r="E6" t="n">
-        <v>66.61</v>
+        <v>74.55</v>
       </c>
       <c r="F6" t="n">
-        <v>58473500000</v>
+        <v>65446740000</v>
       </c>
       <c r="G6" t="n">
-        <v>185.89</v>
+        <v>208.06</v>
       </c>
       <c r="H6" t="n">
         <v>255.29</v>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9.869999999999999</v>
+        <v>-1.84</v>
       </c>
       <c r="K6" t="n">
         <v>621.52</v>
@@ -8328,7 +8328,7 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="Q6" t="n">
         <v>19.73</v>
@@ -8340,7 +8340,7 @@
         <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>55.1</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="7">
@@ -8350,22 +8350,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>359.68</v>
+        <v>369.35</v>
       </c>
       <c r="C7" t="n">
-        <v>42.37</v>
+        <v>49.84</v>
       </c>
       <c r="D7" t="n">
-        <v>27.44</v>
+        <v>28.18</v>
       </c>
       <c r="E7" t="n">
-        <v>10.28</v>
+        <v>10.56</v>
       </c>
       <c r="F7" t="n">
-        <v>4349630750000</v>
+        <v>4466570780000</v>
       </c>
       <c r="G7" t="n">
-        <v>287.74</v>
+        <v>295.48</v>
       </c>
       <c r="H7" t="n">
         <v>434.43</v>
@@ -8374,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>20.78</v>
+        <v>17.62</v>
       </c>
       <c r="K7" t="n">
         <v>22.34</v>
@@ -8404,7 +8404,7 @@
         <v>1.39</v>
       </c>
       <c r="T7" t="n">
-        <v>64</v>
+        <v>62.1</v>
       </c>
     </row>
   </sheetData>
@@ -8530,22 +8530,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>144.96</v>
+        <v>146.06</v>
       </c>
       <c r="C2" t="n">
-        <v>54.67</v>
+        <v>55.98</v>
       </c>
       <c r="D2" t="n">
-        <v>25.93</v>
+        <v>26.12</v>
       </c>
       <c r="E2" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="F2" t="n">
-        <v>88442360000</v>
+        <v>89113480000</v>
       </c>
       <c r="G2" t="n">
-        <v>115.97</v>
+        <v>116.85</v>
       </c>
       <c r="H2" t="n">
         <v>157.1</v>
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8.369999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="K2" t="n">
         <v>8.210000000000001</v>
@@ -8584,7 +8584,7 @@
         <v>2.19</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="3">
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.91</v>
+        <v>71.13</v>
       </c>
       <c r="C3" t="n">
-        <v>60.48</v>
+        <v>62.99</v>
       </c>
       <c r="D3" t="n">
-        <v>45.93</v>
+        <v>46.73</v>
       </c>
       <c r="E3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>58065880000</v>
+        <v>59079180000</v>
       </c>
       <c r="G3" t="n">
-        <v>55.93</v>
+        <v>56.9</v>
       </c>
       <c r="H3" t="n">
         <v>76.40000000000001</v>
@@ -8618,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9.279999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="K3" t="n">
         <v>2.36</v>
@@ -8636,7 +8636,7 @@
         <v>0.93</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q3" t="n">
         <v>4.74</v>
@@ -8648,7 +8648,7 @@
         <v>2.03</v>
       </c>
       <c r="T3" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="4">
@@ -8658,22 +8658,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220.31</v>
+        <v>227.41</v>
       </c>
       <c r="C4" t="n">
-        <v>49.47</v>
+        <v>55.21</v>
       </c>
       <c r="D4" t="n">
-        <v>31.23</v>
+        <v>32.24</v>
       </c>
       <c r="E4" t="n">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="F4" t="n">
-        <v>139600120000</v>
+        <v>144099060000</v>
       </c>
       <c r="G4" t="n">
-        <v>176.25</v>
+        <v>181.93</v>
       </c>
       <c r="H4" t="n">
         <v>251.87</v>
@@ -8682,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14.33</v>
+        <v>10.76</v>
       </c>
       <c r="K4" t="n">
         <v>-6.9</v>
@@ -8712,7 +8712,7 @@
         <v>1.96</v>
       </c>
       <c r="T4" t="n">
-        <v>40.2</v>
+        <v>38.7</v>
       </c>
     </row>
   </sheetData>
@@ -8838,22 +8838,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110.08</v>
+        <v>110.97</v>
       </c>
       <c r="C2" t="n">
-        <v>46.76</v>
+        <v>49.31</v>
       </c>
       <c r="D2" t="n">
-        <v>27.35</v>
+        <v>27.57</v>
       </c>
       <c r="E2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="F2" t="n">
-        <v>26165300000</v>
+        <v>26376850000</v>
       </c>
       <c r="G2" t="n">
-        <v>88.06</v>
+        <v>88.78</v>
       </c>
       <c r="H2" t="n">
         <v>152.31</v>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38.36</v>
+        <v>37.25</v>
       </c>
       <c r="K2" t="n">
         <v>2.71</v>
@@ -8892,7 +8892,7 @@
         <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -8902,22 +8902,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>131.73</v>
+        <v>134.4</v>
       </c>
       <c r="C3" t="n">
-        <v>58.48</v>
+        <v>62.01</v>
       </c>
       <c r="D3" t="n">
-        <v>29.79</v>
+        <v>30.39</v>
       </c>
       <c r="E3" t="n">
-        <v>4.29</v>
+        <v>4.37</v>
       </c>
       <c r="F3" t="n">
-        <v>3844610000</v>
+        <v>3922540000</v>
       </c>
       <c r="G3" t="n">
-        <v>105.38</v>
+        <v>107.52</v>
       </c>
       <c r="H3" t="n">
         <v>145.12</v>
@@ -8926,7 +8926,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10.16</v>
+        <v>7.98</v>
       </c>
       <c r="K3" t="n">
         <v>-8.970000000000001</v>
@@ -8956,7 +8956,7 @@
         <v>2.13</v>
       </c>
       <c r="T3" t="n">
-        <v>43.9</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="4">
@@ -8966,22 +8966,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.82</v>
+        <v>25.79</v>
       </c>
       <c r="C4" t="n">
-        <v>49.5</v>
+        <v>49.14</v>
       </c>
       <c r="D4" t="n">
-        <v>19.59</v>
+        <v>19.57</v>
       </c>
       <c r="E4" t="n">
         <v>2.76</v>
       </c>
       <c r="F4" t="n">
-        <v>4040080000</v>
+        <v>4035390000</v>
       </c>
       <c r="G4" t="n">
-        <v>20.66</v>
+        <v>20.63</v>
       </c>
       <c r="H4" t="n">
         <v>32.2</v>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>24.71</v>
+        <v>24.85</v>
       </c>
       <c r="K4" t="n">
         <v>5.52</v>
@@ -9146,22 +9146,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>218.69</v>
+        <v>215.74</v>
       </c>
       <c r="C2" t="n">
-        <v>60.69</v>
+        <v>56.51</v>
       </c>
       <c r="D2" t="n">
-        <v>35.29</v>
+        <v>34.82</v>
       </c>
       <c r="E2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="F2" t="n">
-        <v>56181460000</v>
+        <v>55423610000</v>
       </c>
       <c r="G2" t="n">
-        <v>174.95</v>
+        <v>172.59</v>
       </c>
       <c r="H2" t="n">
         <v>263.79</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>20.62</v>
+        <v>22.27</v>
       </c>
       <c r="K2" t="n">
         <v>27.65</v>
@@ -9188,7 +9188,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Q2" t="n">
         <v>1.92</v>
@@ -9200,7 +9200,7 @@
         <v>1.59</v>
       </c>
       <c r="T2" t="n">
-        <v>55.9</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="3">
@@ -9210,22 +9210,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.64</v>
+        <v>35.34</v>
       </c>
       <c r="C3" t="n">
-        <v>61.18</v>
+        <v>59.61</v>
       </c>
       <c r="D3" t="n">
-        <v>48.43</v>
+        <v>48.02</v>
       </c>
       <c r="E3" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="F3" t="n">
-        <v>9396820000</v>
+        <v>9317720000</v>
       </c>
       <c r="G3" t="n">
-        <v>28.51</v>
+        <v>28.27</v>
       </c>
       <c r="H3" t="n">
         <v>41.56</v>
@@ -9234,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16.61</v>
+        <v>17.6</v>
       </c>
       <c r="K3" t="n">
         <v>14.57</v>
@@ -9249,7 +9249,7 @@
         <v>5.88</v>
       </c>
       <c r="P3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="Q3" t="n">
         <v>12.64</v>
@@ -9261,7 +9261,7 @@
         <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
     </row>
   </sheetData>
@@ -9397,22 +9397,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.18</v>
+        <v>25.08</v>
       </c>
       <c r="D2" t="n">
-        <v>44.16</v>
+        <v>49.16</v>
       </c>
       <c r="G2" t="n">
-        <v>1207290000</v>
+        <v>1306250000</v>
       </c>
       <c r="H2" t="n">
-        <v>18.54</v>
+        <v>20.06</v>
       </c>
       <c r="I2" t="n">
         <v>45.75</v>
       </c>
       <c r="K2" t="n">
-        <v>97.37</v>
+        <v>82.42</v>
       </c>
       <c r="M2" t="n">
         <v>69.08</v>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="R2" t="n">
         <v>17.8</v>
@@ -9433,7 +9433,7 @@
         <v>1.4</v>
       </c>
       <c r="U2" t="n">
-        <v>76.5</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="3">
@@ -9448,25 +9448,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68.19</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>49.34</v>
+        <v>51.98</v>
       </c>
       <c r="F3" t="n">
-        <v>9.85</v>
+        <v>10.08</v>
       </c>
       <c r="G3" t="n">
-        <v>14035430000</v>
+        <v>14364750000</v>
       </c>
       <c r="H3" t="n">
-        <v>54.55</v>
+        <v>55.83</v>
       </c>
       <c r="I3" t="n">
         <v>94.37</v>
       </c>
       <c r="K3" t="n">
-        <v>38.39</v>
+        <v>35.22</v>
       </c>
       <c r="L3" t="n">
         <v>38.99</v>
@@ -9481,7 +9481,7 @@
         <v>-20.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="R3" t="n">
         <v>26.66</v>
@@ -9493,7 +9493,7 @@
         <v>1.1</v>
       </c>
       <c r="U3" t="n">
-        <v>55.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -9508,22 +9508,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57.49</v>
+        <v>60.74</v>
       </c>
       <c r="D4" t="n">
-        <v>42.92</v>
+        <v>47.16</v>
       </c>
       <c r="G4" t="n">
-        <v>10002740000</v>
+        <v>10568210000</v>
       </c>
       <c r="H4" t="n">
-        <v>45.99</v>
+        <v>48.59</v>
       </c>
       <c r="I4" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>53.52</v>
+        <v>45.31</v>
       </c>
       <c r="M4" t="n">
         <v>-173.38</v>
@@ -9544,7 +9544,7 @@
         <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>50.3</v>
+        <v>47.1</v>
       </c>
     </row>
   </sheetData>
@@ -9670,22 +9670,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>412.25</v>
+        <v>411.72</v>
       </c>
       <c r="C2" t="n">
-        <v>49.64</v>
+        <v>49.22</v>
       </c>
       <c r="D2" t="n">
-        <v>33.24</v>
+        <v>33.19</v>
       </c>
       <c r="E2" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="F2" t="n">
-        <v>68431679999</v>
+        <v>68343700000</v>
       </c>
       <c r="G2" t="n">
-        <v>329.8</v>
+        <v>329.38</v>
       </c>
       <c r="H2" t="n">
         <v>509.2</v>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>23.52</v>
+        <v>23.68</v>
       </c>
       <c r="K2" t="n">
         <v>7.36</v>
@@ -9724,7 +9724,7 @@
         <v>1.47</v>
       </c>
       <c r="T2" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="3">
@@ -9734,22 +9734,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.65</v>
+        <v>45.47</v>
       </c>
       <c r="C3" t="n">
-        <v>61.11</v>
+        <v>52.34</v>
       </c>
       <c r="D3" t="n">
-        <v>19.36</v>
+        <v>18.87</v>
       </c>
       <c r="E3" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="F3" t="n">
-        <v>2307340000</v>
+        <v>2248980000</v>
       </c>
       <c r="G3" t="n">
-        <v>37.32</v>
+        <v>36.38</v>
       </c>
       <c r="H3" t="n">
         <v>59</v>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>26.47</v>
+        <v>29.76</v>
       </c>
       <c r="K3" t="n">
         <v>11.04</v>
@@ -9788,7 +9788,7 @@
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>50.2</v>
+        <v>52.3</v>
       </c>
     </row>
   </sheetData>
@@ -9914,22 +9914,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205.19</v>
+        <v>212.45</v>
       </c>
       <c r="C2" t="n">
-        <v>45.24</v>
+        <v>51.29</v>
       </c>
       <c r="D2" t="n">
-        <v>31.42</v>
+        <v>32.54</v>
       </c>
       <c r="E2" t="n">
-        <v>19.59</v>
+        <v>20.28</v>
       </c>
       <c r="F2" t="n">
-        <v>4965598060000</v>
+        <v>5141289930000</v>
       </c>
       <c r="G2" t="n">
-        <v>164.15</v>
+        <v>169.96</v>
       </c>
       <c r="H2" t="n">
         <v>309.93</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>51.05</v>
+        <v>45.88</v>
       </c>
       <c r="K2" t="n">
         <v>85.23</v>
@@ -9968,7 +9968,7 @@
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>74.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -9978,22 +9978,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>511.57</v>
+        <v>547.26</v>
       </c>
       <c r="C3" t="n">
-        <v>60.45</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>167.9</v>
+        <v>179.61</v>
       </c>
       <c r="E3" t="n">
-        <v>22.27</v>
+        <v>23.83</v>
       </c>
       <c r="F3" t="n">
-        <v>834166350000</v>
+        <v>892362490000</v>
       </c>
       <c r="G3" t="n">
-        <v>409.26</v>
+        <v>437.81</v>
       </c>
       <c r="H3" t="n">
         <v>494.82</v>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.27</v>
+        <v>-9.58</v>
       </c>
       <c r="K3" t="n">
         <v>37.85</v>
@@ -10032,7 +10032,7 @@
         <v>1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>49.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="4">
@@ -10042,22 +10042,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>382.07</v>
+        <v>393.94</v>
       </c>
       <c r="C4" t="n">
-        <v>41.4</v>
+        <v>45.28</v>
       </c>
       <c r="D4" t="n">
-        <v>63.6</v>
+        <v>65.58</v>
       </c>
       <c r="E4" t="n">
-        <v>24.09</v>
+        <v>24.84</v>
       </c>
       <c r="F4" t="n">
-        <v>1817728660000</v>
+        <v>1874201110000</v>
       </c>
       <c r="G4" t="n">
-        <v>305.66</v>
+        <v>315.15</v>
       </c>
       <c r="H4" t="n">
         <v>524.1799999999999</v>
@@ -10066,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>37.19</v>
+        <v>33.06</v>
       </c>
       <c r="K4" t="n">
         <v>47.87</v>
@@ -10096,7 +10096,7 @@
         <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>61.7</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="5">
@@ -10106,22 +10106,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>279.7</v>
+        <v>308.88</v>
       </c>
       <c r="C5" t="n">
-        <v>62.99</v>
+        <v>67.7</v>
       </c>
       <c r="D5" t="n">
-        <v>95.58</v>
+        <v>105.55</v>
       </c>
       <c r="E5" t="n">
-        <v>28.07</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>244681570000</v>
+        <v>270208229999</v>
       </c>
       <c r="G5" t="n">
-        <v>223.76</v>
+        <v>247.1</v>
       </c>
       <c r="H5" t="n">
         <v>244.35</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.64</v>
+        <v>-20.89</v>
       </c>
       <c r="K5" t="n">
         <v>27.57</v>
@@ -10148,7 +10148,7 @@
         <v>0.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0.77</v>
@@ -10160,7 +10160,7 @@
         <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>37.9</v>
+        <v>35.7</v>
       </c>
     </row>
   </sheetData>
@@ -10286,31 +10286,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>253.76</v>
+        <v>262.35</v>
       </c>
       <c r="C2" t="n">
-        <v>39.88</v>
+        <v>45.06</v>
       </c>
       <c r="D2" t="n">
-        <v>22.04</v>
+        <v>22.78</v>
       </c>
       <c r="E2" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="F2" t="n">
-        <v>91655590000</v>
+        <v>94758220000</v>
       </c>
       <c r="G2" t="n">
-        <v>203.01</v>
+        <v>209.88</v>
       </c>
       <c r="H2" t="n">
-        <v>371.22</v>
+        <v>368.94</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>46.29</v>
+        <v>40.63</v>
       </c>
       <c r="K2" t="n">
         <v>23.45</v>
@@ -10328,7 +10328,7 @@
         <v>0.67</v>
       </c>
       <c r="P2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Q2" t="n">
         <v>6.48</v>
@@ -10340,7 +10340,7 @@
         <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>61.1</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="3">
@@ -10350,31 +10350,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>148.02</v>
+        <v>153.52</v>
       </c>
       <c r="C3" t="n">
-        <v>47.05</v>
+        <v>52.31</v>
       </c>
       <c r="D3" t="n">
-        <v>24.72</v>
+        <v>25.63</v>
       </c>
       <c r="E3" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="F3" t="n">
-        <v>49909750000</v>
+        <v>51764250000</v>
       </c>
       <c r="G3" t="n">
-        <v>118.42</v>
+        <v>122.82</v>
       </c>
       <c r="H3" t="n">
-        <v>233.19</v>
+        <v>233.38</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>57.54</v>
+        <v>52.02</v>
       </c>
       <c r="K3" t="n">
         <v>-10</v>
@@ -10392,7 +10392,7 @@
         <v>3.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0.97</v>
@@ -10404,7 +10404,7 @@
         <v>1.21</v>
       </c>
       <c r="T3" t="n">
-        <v>52.2</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="4">
@@ -10414,25 +10414,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>360.54</v>
+        <v>386.21</v>
       </c>
       <c r="C4" t="n">
-        <v>49.22</v>
+        <v>57.36</v>
       </c>
       <c r="E4" t="n">
-        <v>3.51</v>
+        <v>3.76</v>
       </c>
       <c r="F4" t="n">
-        <v>16366720000</v>
+        <v>17532010000</v>
       </c>
       <c r="G4" t="n">
-        <v>288.43</v>
+        <v>308.97</v>
       </c>
       <c r="H4" t="n">
         <v>478.62</v>
       </c>
       <c r="J4" t="n">
-        <v>32.75</v>
+        <v>23.93</v>
       </c>
       <c r="K4" t="n">
         <v>21.64</v>
@@ -10450,7 +10450,7 @@
         <v>6.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
         <v>1.84</v>
@@ -10462,7 +10462,7 @@
         <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>56.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="5">
@@ -10472,22 +10472,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.49</v>
+        <v>60.74</v>
       </c>
       <c r="C5" t="n">
-        <v>42.92</v>
+        <v>47.16</v>
       </c>
       <c r="F5" t="n">
-        <v>10002740000</v>
+        <v>10568210000</v>
       </c>
       <c r="G5" t="n">
-        <v>45.99</v>
+        <v>48.59</v>
       </c>
       <c r="H5" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>53.52</v>
+        <v>45.31</v>
       </c>
       <c r="L5" t="n">
         <v>-173.38</v>
@@ -10508,7 +10508,7 @@
         <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>50.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="6">
@@ -10518,25 +10518,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.890000000000001</v>
+        <v>10.64</v>
       </c>
       <c r="C6" t="n">
-        <v>41.08</v>
+        <v>46.2</v>
       </c>
       <c r="E6" t="n">
-        <v>193.61</v>
+        <v>208.29</v>
       </c>
       <c r="F6" t="n">
-        <v>3614610000</v>
+        <v>3888720000</v>
       </c>
       <c r="G6" t="n">
-        <v>7.91</v>
+        <v>8.51</v>
       </c>
       <c r="H6" t="n">
         <v>15.64</v>
       </c>
       <c r="J6" t="n">
-        <v>58.14</v>
+        <v>46.99</v>
       </c>
       <c r="K6" t="n">
         <v>-95.78</v>
@@ -10554,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
         <v>3.08</v>
@@ -10566,7 +10566,7 @@
         <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="7">
@@ -10576,22 +10576,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.18</v>
+        <v>25.08</v>
       </c>
       <c r="C7" t="n">
-        <v>44.16</v>
+        <v>49.16</v>
       </c>
       <c r="F7" t="n">
-        <v>1207290000</v>
+        <v>1306250000</v>
       </c>
       <c r="G7" t="n">
-        <v>18.54</v>
+        <v>20.06</v>
       </c>
       <c r="H7" t="n">
         <v>45.75</v>
       </c>
       <c r="J7" t="n">
-        <v>97.37</v>
+        <v>82.42</v>
       </c>
       <c r="L7" t="n">
         <v>69.08</v>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="Q7" t="n">
         <v>17.8</v>
@@ -10612,7 +10612,7 @@
         <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>76.5</v>
+        <v>71.7</v>
       </c>
     </row>
   </sheetData>
@@ -10738,22 +10738,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>163.24</v>
+        <v>169.09</v>
       </c>
       <c r="C2" t="n">
-        <v>55.54</v>
+        <v>59.42</v>
       </c>
       <c r="D2" t="n">
-        <v>55.9</v>
+        <v>57.9</v>
       </c>
       <c r="E2" t="n">
-        <v>21.17</v>
+        <v>21.93</v>
       </c>
       <c r="F2" t="n">
-        <v>205552250000</v>
+        <v>212918570000</v>
       </c>
       <c r="G2" t="n">
-        <v>130.59</v>
+        <v>135.27</v>
       </c>
       <c r="H2" t="n">
         <v>189.42</v>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>16.04</v>
+        <v>12.02</v>
       </c>
       <c r="K2" t="n">
         <v>35.13</v>
@@ -10780,7 +10780,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
         <v>17.09</v>
@@ -10792,7 +10792,7 @@
         <v>1.09</v>
       </c>
       <c r="T2" t="n">
-        <v>54.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="3">
@@ -10802,22 +10802,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.81</v>
+        <v>259.41</v>
       </c>
       <c r="C3" t="n">
-        <v>63.85</v>
+        <v>65.95</v>
       </c>
       <c r="D3" t="n">
-        <v>101.04</v>
+        <v>104.51</v>
       </c>
       <c r="E3" t="n">
-        <v>34.65</v>
+        <v>35.84</v>
       </c>
       <c r="F3" t="n">
-        <v>46261890000</v>
+        <v>47848160000</v>
       </c>
       <c r="G3" t="n">
-        <v>200.65</v>
+        <v>207.53</v>
       </c>
       <c r="H3" t="n">
         <v>266.44</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.23</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
         <v>157.02</v>
@@ -10844,7 +10844,7 @@
         <v>0.01</v>
       </c>
       <c r="P3" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="Q3" t="n">
         <v>10.33</v>
@@ -10856,7 +10856,7 @@
         <v>1.15</v>
       </c>
       <c r="T3" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="4">
@@ -10866,22 +10866,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>367.15</v>
+        <v>389.2</v>
       </c>
       <c r="C4" t="n">
-        <v>66.63</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>247.47</v>
+        <v>262.33</v>
       </c>
       <c r="E4" t="n">
-        <v>62.84</v>
+        <v>66.62</v>
       </c>
       <c r="F4" t="n">
-        <v>62932430000</v>
+        <v>66711979999</v>
       </c>
       <c r="G4" t="n">
-        <v>293.72</v>
+        <v>311.36</v>
       </c>
       <c r="H4" t="n">
         <v>253.06</v>
@@ -10890,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-31.07</v>
+        <v>-34.98</v>
       </c>
       <c r="K4" t="n">
         <v>93.40000000000001</v>
@@ -10908,7 +10908,7 @@
         <v>0.03</v>
       </c>
       <c r="P4" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="Q4" t="n">
         <v>18.28</v>
@@ -10920,7 +10920,7 @@
         <v>1.81</v>
       </c>
       <c r="T4" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="5">
@@ -10930,22 +10930,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>385.03</v>
+        <v>413.84</v>
       </c>
       <c r="C5" t="n">
-        <v>53.61</v>
+        <v>59.02</v>
       </c>
       <c r="D5" t="n">
-        <v>183.82</v>
+        <v>197.57</v>
       </c>
       <c r="E5" t="n">
-        <v>11.41</v>
+        <v>12.26</v>
       </c>
       <c r="F5" t="n">
-        <v>75327010000</v>
+        <v>80963380000</v>
       </c>
       <c r="G5" t="n">
-        <v>308.02</v>
+        <v>331.07</v>
       </c>
       <c r="H5" t="n">
         <v>388.09</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.79</v>
+        <v>-6.22</v>
       </c>
       <c r="K5" t="n">
         <v>20.55</v>
@@ -10972,7 +10972,7 @@
         <v>0.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
         <v>4.45</v>
@@ -10984,7 +10984,7 @@
         <v>1.65</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="6">
@@ -10994,22 +10994,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>921.5599999999999</v>
+        <v>957.24</v>
       </c>
       <c r="C6" t="n">
-        <v>51.7</v>
+        <v>54.43</v>
       </c>
       <c r="D6" t="n">
-        <v>171.04</v>
+        <v>177.66</v>
       </c>
       <c r="E6" t="n">
-        <v>28.81</v>
+        <v>29.93</v>
       </c>
       <c r="F6" t="n">
-        <v>71697370000</v>
+        <v>74473270000</v>
       </c>
       <c r="G6" t="n">
-        <v>737.25</v>
+        <v>765.79</v>
       </c>
       <c r="H6" t="n">
         <v>1132.81</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>22.92</v>
+        <v>18.34</v>
       </c>
       <c r="K6" t="n">
         <v>90.12</v>
@@ -11036,7 +11036,7 @@
         <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q6" t="n">
         <v>2.57</v>
@@ -11048,7 +11048,7 @@
         <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>56.1</v>
+        <v>54.9</v>
       </c>
     </row>
   </sheetData>
@@ -11174,31 +11174,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>981.61</v>
+        <v>1087.99</v>
       </c>
       <c r="C2" t="n">
-        <v>60.77</v>
+        <v>66.56</v>
       </c>
       <c r="D2" t="n">
-        <v>46.34</v>
+        <v>51.37</v>
       </c>
       <c r="E2" t="n">
-        <v>19.05</v>
+        <v>21.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1106994960000</v>
+        <v>1226963310000</v>
       </c>
       <c r="G2" t="n">
-        <v>785.29</v>
+        <v>870.39</v>
       </c>
       <c r="H2" t="n">
-        <v>921.02</v>
+        <v>942.02</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.17</v>
+        <v>-13.42</v>
       </c>
       <c r="K2" t="n">
         <v>196.29</v>
@@ -11216,7 +11216,7 @@
         <v>0.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0.44</v>
@@ -11228,7 +11228,7 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>65.59999999999999</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="3">
@@ -11238,31 +11238,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>562.92</v>
+        <v>653.53</v>
       </c>
       <c r="C3" t="n">
-        <v>61.39</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>33.6</v>
+        <v>39.01</v>
       </c>
       <c r="E3" t="n">
-        <v>16.48</v>
+        <v>19.13</v>
       </c>
       <c r="F3" t="n">
-        <v>194030180000</v>
+        <v>225260120000</v>
       </c>
       <c r="G3" t="n">
-        <v>450.34</v>
+        <v>522.8200000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>552.96</v>
+        <v>560</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.77</v>
+        <v>-14.31</v>
       </c>
       <c r="K3" t="n">
         <v>45.47</v>
@@ -11280,7 +11280,7 @@
         <v>0.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
         <v>0.95</v>
@@ -11292,7 +11292,7 @@
         <v>1.69</v>
       </c>
       <c r="T3" t="n">
-        <v>58.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="4">
@@ -11302,31 +11302,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>931.04</v>
+        <v>1018.8</v>
       </c>
       <c r="C4" t="n">
-        <v>64.28</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>88.38</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>18.96</v>
+        <v>20.75</v>
       </c>
       <c r="F4" t="n">
-        <v>208766150000</v>
+        <v>228444490000</v>
       </c>
       <c r="G4" t="n">
-        <v>744.83</v>
+        <v>815.04</v>
       </c>
       <c r="H4" t="n">
-        <v>891.36</v>
+        <v>903.55</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.26</v>
+        <v>-11.31</v>
       </c>
       <c r="K4" t="n">
         <v>44.07</v>
@@ -11344,7 +11344,7 @@
         <v>3.82</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
         <v>0.27</v>
@@ -11356,7 +11356,7 @@
         <v>1.59</v>
       </c>
       <c r="T4" t="n">
-        <v>46.7</v>
+        <v>44.2</v>
       </c>
     </row>
   </sheetData>
@@ -11482,22 +11482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>184.2</v>
+        <v>184.9</v>
       </c>
       <c r="C2" t="n">
-        <v>44.09</v>
+        <v>45.23</v>
       </c>
       <c r="D2" t="n">
-        <v>48.72</v>
+        <v>48.91</v>
       </c>
       <c r="E2" t="n">
-        <v>10.09</v>
+        <v>10.12</v>
       </c>
       <c r="F2" t="n">
-        <v>64729000000</v>
+        <v>64974980000</v>
       </c>
       <c r="G2" t="n">
-        <v>147.36</v>
+        <v>147.92</v>
       </c>
       <c r="H2" t="n">
         <v>219.17</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18.98</v>
+        <v>18.53</v>
       </c>
       <c r="K2" t="n">
         <v>16.16</v>
@@ -11536,7 +11536,7 @@
         <v>1.61</v>
       </c>
       <c r="T2" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="3">
@@ -11546,22 +11546,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1055.85</v>
+        <v>1064.38</v>
       </c>
       <c r="C3" t="n">
-        <v>46.94</v>
+        <v>50.18</v>
       </c>
       <c r="D3" t="n">
-        <v>73.02</v>
+        <v>73.61</v>
       </c>
       <c r="E3" t="n">
-        <v>11.04</v>
+        <v>11.12</v>
       </c>
       <c r="F3" t="n">
-        <v>104132410000</v>
+        <v>104973680000</v>
       </c>
       <c r="G3" t="n">
-        <v>844.6799999999999</v>
+        <v>851.5</v>
       </c>
       <c r="H3" t="n">
         <v>1204.61</v>
@@ -11570,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14.09</v>
+        <v>13.17</v>
       </c>
       <c r="K3" t="n">
         <v>9.84</v>
@@ -11600,7 +11600,7 @@
         <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>44.3</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="4">
@@ -11610,25 +11610,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.7</v>
+        <v>46.47</v>
       </c>
       <c r="C4" t="n">
-        <v>51.53</v>
+        <v>57.38</v>
       </c>
       <c r="E4" t="n">
-        <v>34.33</v>
+        <v>37.36</v>
       </c>
       <c r="F4" t="n">
-        <v>12202360000</v>
+        <v>13279710000</v>
       </c>
       <c r="G4" t="n">
-        <v>34.16</v>
+        <v>37.18</v>
       </c>
       <c r="H4" t="n">
         <v>70.75</v>
       </c>
       <c r="J4" t="n">
-        <v>65.69</v>
+        <v>52.25</v>
       </c>
       <c r="K4" t="n">
         <v>139.29</v>
@@ -11658,7 +11658,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>45.2</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="5">
@@ -11668,28 +11668,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.24</v>
+        <v>126.28</v>
       </c>
       <c r="C5" t="n">
-        <v>54.3</v>
+        <v>52.38</v>
       </c>
       <c r="D5" t="n">
-        <v>139.72</v>
+        <v>138.66</v>
       </c>
       <c r="E5" t="n">
-        <v>5.23</v>
+        <v>5.19</v>
       </c>
       <c r="F5" t="n">
-        <v>37857040000</v>
+        <v>37571420000</v>
       </c>
       <c r="G5" t="n">
-        <v>101.79</v>
+        <v>101.02</v>
       </c>
       <c r="H5" t="n">
         <v>131.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.39</v>
+        <v>4.17</v>
       </c>
       <c r="K5" t="n">
         <v>21.58</v>
@@ -11716,7 +11716,7 @@
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
     </row>
   </sheetData>
@@ -11842,22 +11842,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>302.87</v>
+        <v>311.93</v>
       </c>
       <c r="C2" t="n">
-        <v>44.67</v>
+        <v>48.7</v>
       </c>
       <c r="D2" t="n">
-        <v>76.03</v>
+        <v>78.31</v>
       </c>
       <c r="E2" t="n">
-        <v>10.73</v>
+        <v>11.05</v>
       </c>
       <c r="F2" t="n">
-        <v>116335040000</v>
+        <v>119815070000</v>
       </c>
       <c r="G2" t="n">
-        <v>242.3</v>
+        <v>249.54</v>
       </c>
       <c r="H2" t="n">
         <v>380.63</v>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25.67</v>
+        <v>22.02</v>
       </c>
       <c r="K2" t="n">
         <v>30.13</v>
@@ -11896,7 +11896,7 @@
         <v>1.56</v>
       </c>
       <c r="T2" t="n">
-        <v>55.7</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="3">
@@ -11906,22 +11906,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274.5</v>
+        <v>285.72</v>
       </c>
       <c r="C3" t="n">
-        <v>50.88</v>
+        <v>54.63</v>
       </c>
       <c r="D3" t="n">
-        <v>122.63</v>
+        <v>127.64</v>
       </c>
       <c r="E3" t="n">
-        <v>4.56</v>
+        <v>4.74</v>
       </c>
       <c r="F3" t="n">
-        <v>14497930000</v>
+        <v>15090520000</v>
       </c>
       <c r="G3" t="n">
-        <v>219.6</v>
+        <v>228.58</v>
       </c>
       <c r="H3" t="n">
         <v>351.75</v>
@@ -11930,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>28.14</v>
+        <v>23.11</v>
       </c>
       <c r="K3" t="n">
         <v>47.47</v>
@@ -11960,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>53.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="4">
@@ -11970,22 +11970,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>127.19</v>
+        <v>131.26</v>
       </c>
       <c r="C4" t="n">
-        <v>48.93</v>
+        <v>52.38</v>
       </c>
       <c r="D4" t="n">
-        <v>89.47</v>
+        <v>92.33</v>
       </c>
       <c r="E4" t="n">
-        <v>6.44</v>
+        <v>6.65</v>
       </c>
       <c r="F4" t="n">
-        <v>10418350000</v>
+        <v>10751730000</v>
       </c>
       <c r="G4" t="n">
-        <v>101.75</v>
+        <v>105.01</v>
       </c>
       <c r="H4" t="n">
         <v>149.75</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>17.74</v>
+        <v>14.09</v>
       </c>
       <c r="K4" t="n">
         <v>54.3</v>
@@ -12012,7 +12012,7 @@
         <v>0.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q4" t="n">
         <v>16.68</v>
@@ -12024,7 +12024,7 @@
         <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>52.7</v>
+        <v>51.7</v>
       </c>
     </row>
   </sheetData>
@@ -12150,22 +12150,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>707.74</v>
+        <v>724.35</v>
       </c>
       <c r="C2" t="n">
-        <v>51.59</v>
+        <v>55.05</v>
       </c>
       <c r="D2" t="n">
-        <v>97.09999999999999</v>
+        <v>99.38</v>
       </c>
       <c r="E2" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="F2" t="n">
-        <v>106203570000</v>
+        <v>108696070000</v>
       </c>
       <c r="G2" t="n">
-        <v>566.1900000000001</v>
+        <v>579.48</v>
       </c>
       <c r="H2" t="n">
         <v>802.79</v>
@@ -12174,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>13.43</v>
+        <v>10.83</v>
       </c>
       <c r="K2" t="n">
         <v>26.33</v>
@@ -12204,7 +12204,7 @@
         <v>1.68</v>
       </c>
       <c r="T2" t="n">
-        <v>48.1</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="3">
@@ -12214,22 +12214,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>940.66</v>
+        <v>979.0700000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>44.11</v>
+        <v>50.19</v>
       </c>
       <c r="D3" t="n">
-        <v>27.41</v>
+        <v>28.53</v>
       </c>
       <c r="E3" t="n">
-        <v>6.42</v>
+        <v>6.69</v>
       </c>
       <c r="F3" t="n">
-        <v>252774150000</v>
+        <v>263095690000</v>
       </c>
       <c r="G3" t="n">
-        <v>752.53</v>
+        <v>783.26</v>
       </c>
       <c r="H3" t="n">
         <v>1245.84</v>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>32.44</v>
+        <v>27.25</v>
       </c>
       <c r="K3" t="n">
         <v>15.98</v>
@@ -12256,7 +12256,7 @@
         <v>0.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Q3" t="n">
         <v>0.15</v>
@@ -12268,7 +12268,7 @@
         <v>1.6</v>
       </c>
       <c r="T3" t="n">
-        <v>59.6</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="4">
@@ -12278,22 +12278,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165.84</v>
+        <v>169</v>
       </c>
       <c r="C4" t="n">
-        <v>53.27</v>
+        <v>56.17</v>
       </c>
       <c r="D4" t="n">
-        <v>55.77</v>
+        <v>56.83</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2</v>
+        <v>6.32</v>
       </c>
       <c r="F4" t="n">
-        <v>26819720000</v>
+        <v>27330760000</v>
       </c>
       <c r="G4" t="n">
-        <v>132.67</v>
+        <v>135.2</v>
       </c>
       <c r="H4" t="n">
         <v>193.29</v>
@@ -12302,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16.55</v>
+        <v>14.37</v>
       </c>
       <c r="K4" t="n">
         <v>53.47</v>
@@ -12332,7 +12332,7 @@
         <v>1.56</v>
       </c>
       <c r="T4" t="n">
-        <v>48.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="5">
@@ -12342,22 +12342,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>294.75</v>
+        <v>303.53</v>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>57.89</v>
       </c>
       <c r="D5" t="n">
-        <v>57.6</v>
+        <v>59.32</v>
       </c>
       <c r="E5" t="n">
-        <v>9.49</v>
+        <v>9.77</v>
       </c>
       <c r="F5" t="n">
-        <v>10738230000</v>
+        <v>11058100000</v>
       </c>
       <c r="G5" t="n">
-        <v>235.8</v>
+        <v>242.82</v>
       </c>
       <c r="H5" t="n">
         <v>289.17</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.89</v>
+        <v>-4.73</v>
       </c>
       <c r="K5" t="n">
         <v>6.45</v>
@@ -12396,7 +12396,7 @@
         <v>1.86</v>
       </c>
       <c r="T5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -12522,22 +12522,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>391.39</v>
+        <v>407.06</v>
       </c>
       <c r="C2" t="n">
-        <v>46.69</v>
+        <v>52.88</v>
       </c>
       <c r="D2" t="n">
-        <v>38.26</v>
+        <v>39.79</v>
       </c>
       <c r="E2" t="n">
-        <v>5.33</v>
+        <v>5.54</v>
       </c>
       <c r="F2" t="n">
-        <v>151976740000</v>
+        <v>158061390000</v>
       </c>
       <c r="G2" t="n">
-        <v>313.11</v>
+        <v>325.65</v>
       </c>
       <c r="H2" t="n">
         <v>463.71</v>
@@ -12546,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18.48</v>
+        <v>13.92</v>
       </c>
       <c r="K2" t="n">
         <v>16.84</v>
@@ -12576,7 +12576,7 @@
         <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>48.7</v>
+        <v>46.9</v>
       </c>
     </row>
   </sheetData>
